--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3353,6 +3353,4158 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130671341</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>557029</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6710414</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130671365</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>557193</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6710076</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130671370</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>557076</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6710421</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130671368</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>557270</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6710338</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130671343</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>557327</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6710227</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130671332</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91759</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>556970</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6710400</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130671357</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>557304</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6710306</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130671363</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>557265</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6710358</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130671359</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>557278</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6710338</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130671360</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>557294</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6710342</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130671327</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91723</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>556951</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6710395</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130671328</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92130</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>556973</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6710401</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130671362</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>557271</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6710350</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130671356</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>557307</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6710299</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130671345</v>
+      </c>
+      <c r="B38" t="n">
+        <v>81194</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>557189</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6710461</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130671338</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>557146</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6710445</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130671342</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>557118</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6710289</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130671339</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>557178</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6710135</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130671344</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92212</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>556959</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6710396</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130671361</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>557273</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6710349</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130671336</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>556993</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6710383</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130671335</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91780</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>557382</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6710266</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130671355</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>557310</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6710293</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130671324</v>
+      </c>
+      <c r="B47" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>557043</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6710389</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130671334</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58011</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>557212</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6710081</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130671337</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>557203</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6710208</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130671340</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>557079</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6710383</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130671347</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91779</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>557185</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6710142</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130671325</v>
+      </c>
+      <c r="B52" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>557029</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6710414</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>130671330</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91759</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>557102</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6710446</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130671372</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>557068</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6710403</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130671329</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91759</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>557322</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6710273</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>130671373</v>
+      </c>
+      <c r="B56" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>557193</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6710075</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>130671358</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>557300</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6710292</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>130671367</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>557187</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6710451</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>130671371</v>
+      </c>
+      <c r="B59" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>557184</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6710457</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>130671326</v>
+      </c>
+      <c r="B60" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>557081</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6710301</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>130671331</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91759</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>556976</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6710393</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -4124,7 +4124,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130671363</v>
+        <v>130671360</v>
       </c>
       <c r="B31" t="n">
         <v>79209</v>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557265</v>
+        <v>557294</v>
       </c>
       <c r="R31" t="n">
-        <v>6710358</v>
+        <v>6710342</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4338,7 +4338,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130671360</v>
+        <v>130671363</v>
       </c>
       <c r="B33" t="n">
         <v>79209</v>
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557294</v>
+        <v>557265</v>
       </c>
       <c r="R33" t="n">
-        <v>6710342</v>
+        <v>6710358</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4552,32 +4552,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130671328</v>
+        <v>130671356</v>
       </c>
       <c r="B35" t="n">
-        <v>92130</v>
+        <v>79209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556973</v>
+        <v>557307</v>
       </c>
       <c r="R35" t="n">
-        <v>6710401</v>
+        <v>6710299</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4766,32 +4766,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130671356</v>
+        <v>130671328</v>
       </c>
       <c r="B37" t="n">
-        <v>79209</v>
+        <v>92130</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557307</v>
+        <v>556973</v>
       </c>
       <c r="R37" t="n">
-        <v>6710299</v>
+        <v>6710401</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4980,7 +4980,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130671338</v>
+        <v>130671342</v>
       </c>
       <c r="B39" t="n">
         <v>57849</v>
@@ -5011,7 +5011,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557146</v>
+        <v>557118</v>
       </c>
       <c r="R39" t="n">
-        <v>6710445</v>
+        <v>6710289</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5092,7 +5092,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130671342</v>
+        <v>130671339</v>
       </c>
       <c r="B40" t="n">
         <v>57849</v>
@@ -5123,7 +5123,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557118</v>
+        <v>557178</v>
       </c>
       <c r="R40" t="n">
-        <v>6710289</v>
+        <v>6710135</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5204,7 +5204,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130671339</v>
+        <v>130671338</v>
       </c>
       <c r="B41" t="n">
         <v>57849</v>
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557178</v>
+        <v>557146</v>
       </c>
       <c r="R41" t="n">
-        <v>6710135</v>
+        <v>6710445</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5423,10 +5423,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130671361</v>
+        <v>130671336</v>
       </c>
       <c r="B43" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5434,34 +5434,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557273</v>
+        <v>556993</v>
       </c>
       <c r="R43" t="n">
-        <v>6710349</v>
+        <v>6710383</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5493,7 +5498,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5503,7 +5508,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5530,10 +5535,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130671336</v>
+        <v>130671361</v>
       </c>
       <c r="B44" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5541,39 +5546,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556993</v>
+        <v>557273</v>
       </c>
       <c r="R44" t="n">
-        <v>6710383</v>
+        <v>6710349</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5642,10 +5642,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130671335</v>
+        <v>130671355</v>
       </c>
       <c r="B45" t="n">
-        <v>91780</v>
+        <v>79209</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5653,21 +5653,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557382</v>
+        <v>557310</v>
       </c>
       <c r="R45" t="n">
-        <v>6710266</v>
+        <v>6710293</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5749,10 +5749,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130671355</v>
+        <v>130671335</v>
       </c>
       <c r="B46" t="n">
-        <v>79209</v>
+        <v>91780</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557310</v>
+        <v>557382</v>
       </c>
       <c r="R46" t="n">
-        <v>6710293</v>
+        <v>6710266</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6192,10 +6192,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130671340</v>
+        <v>130671347</v>
       </c>
       <c r="B50" t="n">
-        <v>57849</v>
+        <v>91779</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6203,39 +6203,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557079</v>
+        <v>557185</v>
       </c>
       <c r="R50" t="n">
-        <v>6710383</v>
+        <v>6710142</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6267,7 +6258,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6277,7 +6268,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6304,10 +6295,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130671347</v>
+        <v>130671340</v>
       </c>
       <c r="B51" t="n">
-        <v>91779</v>
+        <v>57849</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6315,30 +6306,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557185</v>
+        <v>557079</v>
       </c>
       <c r="R51" t="n">
-        <v>6710142</v>
+        <v>6710383</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6407,10 +6407,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130671325</v>
+        <v>130671372</v>
       </c>
       <c r="B52" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6418,21 +6418,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6447,10 +6447,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557029</v>
+        <v>557068</v>
       </c>
       <c r="R52" t="n">
-        <v>6710414</v>
+        <v>6710403</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6626,10 +6626,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130671372</v>
+        <v>130671325</v>
       </c>
       <c r="B54" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6637,21 +6637,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557068</v>
+        <v>557029</v>
       </c>
       <c r="R54" t="n">
-        <v>6710403</v>
+        <v>6710414</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6738,45 +6738,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130671329</v>
+        <v>130671373</v>
       </c>
       <c r="B55" t="n">
-        <v>91759</v>
+        <v>5177</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557322</v>
+        <v>557193</v>
       </c>
       <c r="R55" t="n">
-        <v>6710273</v>
+        <v>6710075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6808,7 +6813,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6818,7 +6823,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6845,50 +6850,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130671373</v>
+        <v>130671329</v>
       </c>
       <c r="B56" t="n">
-        <v>5177</v>
+        <v>91759</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>557193</v>
+        <v>557322</v>
       </c>
       <c r="R56" t="n">
-        <v>6710075</v>
+        <v>6710273</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -3358,7 +3358,7 @@
         <v>130671341</v>
       </c>
       <c r="B24" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>130671365</v>
       </c>
       <c r="B25" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>130671343</v>
       </c>
       <c r="B28" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130671332</v>
+        <v>130671357</v>
       </c>
       <c r="B29" t="n">
-        <v>91759</v>
+        <v>79211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,21 +3921,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556970</v>
+        <v>557304</v>
       </c>
       <c r="R29" t="n">
-        <v>6710400</v>
+        <v>6710306</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4017,10 +4017,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130671357</v>
+        <v>130671332</v>
       </c>
       <c r="B30" t="n">
-        <v>79209</v>
+        <v>91761</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,21 +4028,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>557304</v>
+        <v>556970</v>
       </c>
       <c r="R30" t="n">
-        <v>6710306</v>
+        <v>6710400</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4124,10 +4124,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130671360</v>
+        <v>130671363</v>
       </c>
       <c r="B31" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557294</v>
+        <v>557265</v>
       </c>
       <c r="R31" t="n">
-        <v>6710342</v>
+        <v>6710358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4231,10 +4231,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130671359</v>
+        <v>130671360</v>
       </c>
       <c r="B32" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557278</v>
+        <v>557294</v>
       </c>
       <c r="R32" t="n">
-        <v>6710338</v>
+        <v>6710342</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4338,10 +4338,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130671363</v>
+        <v>130671359</v>
       </c>
       <c r="B33" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557265</v>
+        <v>557278</v>
       </c>
       <c r="R33" t="n">
-        <v>6710358</v>
+        <v>6710338</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4448,7 +4448,7 @@
         <v>130671327</v>
       </c>
       <c r="B34" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4552,10 +4552,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130671356</v>
+        <v>130671362</v>
       </c>
       <c r="B35" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557307</v>
+        <v>557271</v>
       </c>
       <c r="R35" t="n">
-        <v>6710299</v>
+        <v>6710350</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4659,10 +4659,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130671362</v>
+        <v>130671356</v>
       </c>
       <c r="B36" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4694,10 +4694,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557271</v>
+        <v>557307</v>
       </c>
       <c r="R36" t="n">
-        <v>6710350</v>
+        <v>6710299</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4769,7 +4769,7 @@
         <v>130671328</v>
       </c>
       <c r="B37" t="n">
-        <v>92130</v>
+        <v>92132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>130671345</v>
       </c>
       <c r="B38" t="n">
-        <v>81194</v>
+        <v>81196</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4980,50 +4980,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130671342</v>
+        <v>130671344</v>
       </c>
       <c r="B39" t="n">
-        <v>57849</v>
+        <v>92214</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557118</v>
+        <v>556959</v>
       </c>
       <c r="R39" t="n">
-        <v>6710289</v>
+        <v>6710396</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5055,7 +5050,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5065,7 +5060,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5092,10 +5087,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130671339</v>
+        <v>130671342</v>
       </c>
       <c r="B40" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5123,7 +5118,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5132,10 +5127,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557178</v>
+        <v>557118</v>
       </c>
       <c r="R40" t="n">
-        <v>6710135</v>
+        <v>6710289</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5167,7 +5162,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5177,7 +5172,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5207,7 +5202,7 @@
         <v>130671338</v>
       </c>
       <c r="B41" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5316,45 +5311,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130671344</v>
+        <v>130671339</v>
       </c>
       <c r="B42" t="n">
-        <v>92212</v>
+        <v>57851</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556959</v>
+        <v>557178</v>
       </c>
       <c r="R42" t="n">
-        <v>6710396</v>
+        <v>6710135</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5423,10 +5423,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130671336</v>
+        <v>130671361</v>
       </c>
       <c r="B43" t="n">
-        <v>57849</v>
+        <v>79211</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5434,39 +5434,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556993</v>
+        <v>557273</v>
       </c>
       <c r="R43" t="n">
-        <v>6710383</v>
+        <v>6710349</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5498,7 +5493,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5508,7 +5503,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5535,10 +5530,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130671361</v>
+        <v>130671336</v>
       </c>
       <c r="B44" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5546,34 +5541,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557273</v>
+        <v>556993</v>
       </c>
       <c r="R44" t="n">
-        <v>6710349</v>
+        <v>6710383</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5645,7 +5645,7 @@
         <v>130671355</v>
       </c>
       <c r="B45" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>130671335</v>
       </c>
       <c r="B46" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5968,10 +5968,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130671334</v>
+        <v>130671337</v>
       </c>
       <c r="B48" t="n">
-        <v>58011</v>
+        <v>57851</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5979,27 +5979,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557212</v>
+        <v>557203</v>
       </c>
       <c r="R48" t="n">
-        <v>6710081</v>
+        <v>6710208</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6080,10 +6080,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130671337</v>
+        <v>130671334</v>
       </c>
       <c r="B49" t="n">
-        <v>57849</v>
+        <v>58013</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6091,27 +6091,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557203</v>
+        <v>557212</v>
       </c>
       <c r="R49" t="n">
-        <v>6710208</v>
+        <v>6710081</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6195,7 +6195,7 @@
         <v>130671347</v>
       </c>
       <c r="B50" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>130671340</v>
       </c>
       <c r="B51" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6407,50 +6407,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130671372</v>
+        <v>130671330</v>
       </c>
       <c r="B52" t="n">
-        <v>5177</v>
+        <v>91761</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557068</v>
+        <v>557102</v>
       </c>
       <c r="R52" t="n">
-        <v>6710403</v>
+        <v>6710446</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6482,7 +6477,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6492,7 +6487,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6519,45 +6514,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130671330</v>
+        <v>130671372</v>
       </c>
       <c r="B53" t="n">
-        <v>91759</v>
+        <v>5177</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557102</v>
+        <v>557068</v>
       </c>
       <c r="R53" t="n">
-        <v>6710446</v>
+        <v>6710403</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6738,50 +6738,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130671373</v>
+        <v>130671358</v>
       </c>
       <c r="B55" t="n">
-        <v>5177</v>
+        <v>79211</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557193</v>
+        <v>557300</v>
       </c>
       <c r="R55" t="n">
-        <v>6710075</v>
+        <v>6710292</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6813,7 +6808,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6823,7 +6818,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6853,7 +6848,7 @@
         <v>130671329</v>
       </c>
       <c r="B56" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6957,45 +6952,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130671358</v>
+        <v>130671373</v>
       </c>
       <c r="B57" t="n">
-        <v>79209</v>
+        <v>5177</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557300</v>
+        <v>557193</v>
       </c>
       <c r="R57" t="n">
-        <v>6710292</v>
+        <v>6710075</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7403,7 +7403,7 @@
         <v>130671331</v>
       </c>
       <c r="B61" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -3910,10 +3910,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130671357</v>
+        <v>130671332</v>
       </c>
       <c r="B29" t="n">
-        <v>79211</v>
+        <v>91761</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,21 +3921,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557304</v>
+        <v>556970</v>
       </c>
       <c r="R29" t="n">
-        <v>6710306</v>
+        <v>6710400</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4017,10 +4017,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130671332</v>
+        <v>130671357</v>
       </c>
       <c r="B30" t="n">
-        <v>91761</v>
+        <v>79211</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,21 +4028,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556970</v>
+        <v>557304</v>
       </c>
       <c r="R30" t="n">
-        <v>6710400</v>
+        <v>6710306</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4445,32 +4445,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130671327</v>
+        <v>130671328</v>
       </c>
       <c r="B34" t="n">
-        <v>91725</v>
+        <v>92132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556951</v>
+        <v>556973</v>
       </c>
       <c r="R34" t="n">
-        <v>6710395</v>
+        <v>6710401</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,32 +4552,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130671362</v>
+        <v>130671327</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>91725</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557271</v>
+        <v>556951</v>
       </c>
       <c r="R35" t="n">
-        <v>6710350</v>
+        <v>6710395</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4659,7 +4659,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130671356</v>
+        <v>130671362</v>
       </c>
       <c r="B36" t="n">
         <v>79211</v>
@@ -4694,10 +4694,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557307</v>
+        <v>557271</v>
       </c>
       <c r="R36" t="n">
-        <v>6710299</v>
+        <v>6710350</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4766,32 +4766,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130671328</v>
+        <v>130671356</v>
       </c>
       <c r="B37" t="n">
-        <v>92132</v>
+        <v>79211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556973</v>
+        <v>557307</v>
       </c>
       <c r="R37" t="n">
-        <v>6710401</v>
+        <v>6710299</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4983,7 +4983,7 @@
         <v>130671344</v>
       </c>
       <c r="B39" t="n">
-        <v>92214</v>
+        <v>92220</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5968,10 +5968,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130671337</v>
+        <v>130671334</v>
       </c>
       <c r="B48" t="n">
-        <v>57851</v>
+        <v>58013</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5979,27 +5979,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557203</v>
+        <v>557212</v>
       </c>
       <c r="R48" t="n">
-        <v>6710208</v>
+        <v>6710081</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6080,10 +6080,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130671334</v>
+        <v>130671337</v>
       </c>
       <c r="B49" t="n">
-        <v>58013</v>
+        <v>57851</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6091,27 +6091,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557212</v>
+        <v>557203</v>
       </c>
       <c r="R49" t="n">
-        <v>6710081</v>
+        <v>6710208</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -6514,10 +6514,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130671372</v>
+        <v>130671325</v>
       </c>
       <c r="B53" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6525,21 +6525,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6554,10 +6554,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557068</v>
+        <v>557029</v>
       </c>
       <c r="R53" t="n">
-        <v>6710403</v>
+        <v>6710414</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6626,10 +6626,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130671325</v>
+        <v>130671372</v>
       </c>
       <c r="B54" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6637,21 +6637,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557029</v>
+        <v>557068</v>
       </c>
       <c r="R54" t="n">
-        <v>6710414</v>
+        <v>6710403</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6738,45 +6738,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130671358</v>
+        <v>130671373</v>
       </c>
       <c r="B55" t="n">
-        <v>79211</v>
+        <v>5177</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557300</v>
+        <v>557193</v>
       </c>
       <c r="R55" t="n">
-        <v>6710292</v>
+        <v>6710075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6808,7 +6813,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6818,7 +6823,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6952,50 +6957,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130671373</v>
+        <v>130671358</v>
       </c>
       <c r="B57" t="n">
-        <v>5177</v>
+        <v>79211</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557193</v>
+        <v>557300</v>
       </c>
       <c r="R57" t="n">
-        <v>6710075</v>
+        <v>6710292</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7288,50 +7288,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130671326</v>
+        <v>130671331</v>
       </c>
       <c r="B60" t="n">
-        <v>5197</v>
+        <v>91761</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>557081</v>
+        <v>556976</v>
       </c>
       <c r="R60" t="n">
-        <v>6710301</v>
+        <v>6710393</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7363,7 +7358,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7373,7 +7368,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7400,45 +7395,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130671331</v>
+        <v>130671326</v>
       </c>
       <c r="B61" t="n">
-        <v>91761</v>
+        <v>5197</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556976</v>
+        <v>557081</v>
       </c>
       <c r="R61" t="n">
-        <v>6710393</v>
+        <v>6710301</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -4124,7 +4124,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130671363</v>
+        <v>130671360</v>
       </c>
       <c r="B31" t="n">
         <v>79211</v>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557265</v>
+        <v>557294</v>
       </c>
       <c r="R31" t="n">
-        <v>6710358</v>
+        <v>6710342</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4231,7 +4231,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130671360</v>
+        <v>130671359</v>
       </c>
       <c r="B32" t="n">
         <v>79211</v>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557294</v>
+        <v>557278</v>
       </c>
       <c r="R32" t="n">
-        <v>6710342</v>
+        <v>6710338</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4338,7 +4338,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130671359</v>
+        <v>130671363</v>
       </c>
       <c r="B33" t="n">
         <v>79211</v>
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557278</v>
+        <v>557265</v>
       </c>
       <c r="R33" t="n">
-        <v>6710338</v>
+        <v>6710358</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4445,32 +4445,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130671328</v>
+        <v>130671327</v>
       </c>
       <c r="B34" t="n">
-        <v>92132</v>
+        <v>91725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556973</v>
+        <v>556951</v>
       </c>
       <c r="R34" t="n">
-        <v>6710401</v>
+        <v>6710395</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,32 +4552,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130671327</v>
+        <v>130671356</v>
       </c>
       <c r="B35" t="n">
-        <v>91725</v>
+        <v>79211</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556951</v>
+        <v>557307</v>
       </c>
       <c r="R35" t="n">
-        <v>6710395</v>
+        <v>6710299</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4766,32 +4766,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130671356</v>
+        <v>130671328</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>92132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557307</v>
+        <v>556973</v>
       </c>
       <c r="R37" t="n">
-        <v>6710299</v>
+        <v>6710401</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5423,10 +5423,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130671361</v>
+        <v>130671336</v>
       </c>
       <c r="B43" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5434,34 +5434,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557273</v>
+        <v>556993</v>
       </c>
       <c r="R43" t="n">
-        <v>6710349</v>
+        <v>6710383</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5493,7 +5498,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5503,7 +5508,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5530,10 +5535,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130671336</v>
+        <v>130671361</v>
       </c>
       <c r="B44" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5541,39 +5546,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556993</v>
+        <v>557273</v>
       </c>
       <c r="R44" t="n">
-        <v>6710383</v>
+        <v>6710349</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5642,10 +5642,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130671355</v>
+        <v>130671335</v>
       </c>
       <c r="B45" t="n">
-        <v>79211</v>
+        <v>91782</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5653,21 +5653,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557310</v>
+        <v>557382</v>
       </c>
       <c r="R45" t="n">
-        <v>6710293</v>
+        <v>6710266</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5749,10 +5749,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130671335</v>
+        <v>130671355</v>
       </c>
       <c r="B46" t="n">
-        <v>91782</v>
+        <v>79211</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557382</v>
+        <v>557310</v>
       </c>
       <c r="R46" t="n">
-        <v>6710266</v>
+        <v>6710293</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5968,10 +5968,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130671334</v>
+        <v>130671337</v>
       </c>
       <c r="B48" t="n">
-        <v>58013</v>
+        <v>57851</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5979,27 +5979,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557212</v>
+        <v>557203</v>
       </c>
       <c r="R48" t="n">
-        <v>6710081</v>
+        <v>6710208</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6080,10 +6080,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130671337</v>
+        <v>130671334</v>
       </c>
       <c r="B49" t="n">
-        <v>57851</v>
+        <v>58013</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6091,27 +6091,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557203</v>
+        <v>557212</v>
       </c>
       <c r="R49" t="n">
-        <v>6710208</v>
+        <v>6710081</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6407,45 +6407,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130671330</v>
+        <v>130671325</v>
       </c>
       <c r="B52" t="n">
-        <v>91761</v>
+        <v>5197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557102</v>
+        <v>557029</v>
       </c>
       <c r="R52" t="n">
-        <v>6710446</v>
+        <v>6710414</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6477,7 +6482,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6487,7 +6492,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6514,50 +6519,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130671325</v>
+        <v>130671330</v>
       </c>
       <c r="B53" t="n">
-        <v>5197</v>
+        <v>91761</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557029</v>
+        <v>557102</v>
       </c>
       <c r="R53" t="n">
-        <v>6710414</v>
+        <v>6710446</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6738,50 +6738,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130671373</v>
+        <v>130671329</v>
       </c>
       <c r="B55" t="n">
-        <v>5177</v>
+        <v>91761</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557193</v>
+        <v>557322</v>
       </c>
       <c r="R55" t="n">
-        <v>6710075</v>
+        <v>6710273</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6813,7 +6808,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6823,7 +6818,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6850,45 +6845,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130671329</v>
+        <v>130671373</v>
       </c>
       <c r="B56" t="n">
-        <v>91761</v>
+        <v>5177</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>557322</v>
+        <v>557193</v>
       </c>
       <c r="R56" t="n">
-        <v>6710273</v>
+        <v>6710075</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -4124,7 +4124,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130671360</v>
+        <v>130671363</v>
       </c>
       <c r="B31" t="n">
         <v>79211</v>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557294</v>
+        <v>557265</v>
       </c>
       <c r="R31" t="n">
-        <v>6710342</v>
+        <v>6710358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4231,7 +4231,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130671359</v>
+        <v>130671360</v>
       </c>
       <c r="B32" t="n">
         <v>79211</v>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557278</v>
+        <v>557294</v>
       </c>
       <c r="R32" t="n">
-        <v>6710338</v>
+        <v>6710342</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4338,7 +4338,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130671363</v>
+        <v>130671359</v>
       </c>
       <c r="B33" t="n">
         <v>79211</v>
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557265</v>
+        <v>557278</v>
       </c>
       <c r="R33" t="n">
-        <v>6710358</v>
+        <v>6710338</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4445,32 +4445,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130671327</v>
+        <v>130671328</v>
       </c>
       <c r="B34" t="n">
-        <v>91725</v>
+        <v>92132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556951</v>
+        <v>556973</v>
       </c>
       <c r="R34" t="n">
-        <v>6710395</v>
+        <v>6710401</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,32 +4552,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130671356</v>
+        <v>130671327</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>91725</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557307</v>
+        <v>556951</v>
       </c>
       <c r="R35" t="n">
-        <v>6710299</v>
+        <v>6710395</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4766,32 +4766,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130671328</v>
+        <v>130671356</v>
       </c>
       <c r="B37" t="n">
-        <v>92132</v>
+        <v>79211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556973</v>
+        <v>557307</v>
       </c>
       <c r="R37" t="n">
-        <v>6710401</v>
+        <v>6710299</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4980,45 +4980,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130671344</v>
+        <v>130671342</v>
       </c>
       <c r="B39" t="n">
-        <v>92220</v>
+        <v>57851</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556959</v>
+        <v>557118</v>
       </c>
       <c r="R39" t="n">
-        <v>6710396</v>
+        <v>6710289</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5050,7 +5055,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5060,7 +5065,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5087,7 +5092,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130671342</v>
+        <v>130671338</v>
       </c>
       <c r="B40" t="n">
         <v>57851</v>
@@ -5118,7 +5123,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5127,10 +5132,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557118</v>
+        <v>557146</v>
       </c>
       <c r="R40" t="n">
-        <v>6710289</v>
+        <v>6710445</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5162,7 +5167,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5172,7 +5177,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,7 +5204,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130671338</v>
+        <v>130671339</v>
       </c>
       <c r="B41" t="n">
         <v>57851</v>
@@ -5239,10 +5244,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557146</v>
+        <v>557178</v>
       </c>
       <c r="R41" t="n">
-        <v>6710445</v>
+        <v>6710135</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5274,7 +5279,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,7 +5289,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5311,50 +5316,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130671339</v>
+        <v>130671344</v>
       </c>
       <c r="B42" t="n">
-        <v>57851</v>
+        <v>92220</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557178</v>
+        <v>556959</v>
       </c>
       <c r="R42" t="n">
-        <v>6710135</v>
+        <v>6710396</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5642,10 +5642,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130671335</v>
+        <v>130671355</v>
       </c>
       <c r="B45" t="n">
-        <v>91782</v>
+        <v>79211</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5653,21 +5653,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557382</v>
+        <v>557310</v>
       </c>
       <c r="R45" t="n">
-        <v>6710266</v>
+        <v>6710293</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5749,10 +5749,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130671355</v>
+        <v>130671335</v>
       </c>
       <c r="B46" t="n">
-        <v>79211</v>
+        <v>91782</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557310</v>
+        <v>557382</v>
       </c>
       <c r="R46" t="n">
-        <v>6710293</v>
+        <v>6710266</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6192,10 +6192,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130671347</v>
+        <v>130671340</v>
       </c>
       <c r="B50" t="n">
-        <v>91781</v>
+        <v>57851</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6203,30 +6203,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557185</v>
+        <v>557079</v>
       </c>
       <c r="R50" t="n">
-        <v>6710142</v>
+        <v>6710383</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6258,7 +6267,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6268,7 +6277,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6295,10 +6304,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130671340</v>
+        <v>130671347</v>
       </c>
       <c r="B51" t="n">
-        <v>57851</v>
+        <v>91781</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6306,39 +6315,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557079</v>
+        <v>557185</v>
       </c>
       <c r="R51" t="n">
-        <v>6710383</v>
+        <v>6710142</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6407,50 +6407,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130671325</v>
+        <v>130671330</v>
       </c>
       <c r="B52" t="n">
-        <v>5197</v>
+        <v>91761</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557029</v>
+        <v>557102</v>
       </c>
       <c r="R52" t="n">
-        <v>6710414</v>
+        <v>6710446</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6482,7 +6477,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6492,7 +6487,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6519,45 +6514,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130671330</v>
+        <v>130671372</v>
       </c>
       <c r="B53" t="n">
-        <v>91761</v>
+        <v>5177</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557102</v>
+        <v>557068</v>
       </c>
       <c r="R53" t="n">
-        <v>6710446</v>
+        <v>6710403</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6626,10 +6626,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130671372</v>
+        <v>130671325</v>
       </c>
       <c r="B54" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6637,21 +6637,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557068</v>
+        <v>557029</v>
       </c>
       <c r="R54" t="n">
-        <v>6710403</v>
+        <v>6710414</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6738,10 +6738,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130671329</v>
+        <v>130671358</v>
       </c>
       <c r="B55" t="n">
-        <v>91761</v>
+        <v>79211</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6749,21 +6749,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6773,10 +6773,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557322</v>
+        <v>557300</v>
       </c>
       <c r="R55" t="n">
-        <v>6710273</v>
+        <v>6710292</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6957,10 +6957,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130671358</v>
+        <v>130671329</v>
       </c>
       <c r="B57" t="n">
-        <v>79211</v>
+        <v>91761</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6968,21 +6968,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557300</v>
+        <v>557322</v>
       </c>
       <c r="R57" t="n">
-        <v>6710292</v>
+        <v>6710273</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -3358,7 +3358,7 @@
         <v>130671341</v>
       </c>
       <c r="B24" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>130671365</v>
       </c>
       <c r="B25" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>130671343</v>
       </c>
       <c r="B28" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130671332</v>
+        <v>130671357</v>
       </c>
       <c r="B29" t="n">
-        <v>91761</v>
+        <v>79219</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,21 +3921,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556970</v>
+        <v>557304</v>
       </c>
       <c r="R29" t="n">
-        <v>6710400</v>
+        <v>6710306</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4017,10 +4017,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130671357</v>
+        <v>130671332</v>
       </c>
       <c r="B30" t="n">
-        <v>79211</v>
+        <v>91774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,21 +4028,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>557304</v>
+        <v>556970</v>
       </c>
       <c r="R30" t="n">
-        <v>6710306</v>
+        <v>6710400</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4127,7 +4127,7 @@
         <v>130671363</v>
       </c>
       <c r="B31" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>130671360</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>130671359</v>
       </c>
       <c r="B33" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4445,32 +4445,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130671328</v>
+        <v>130671327</v>
       </c>
       <c r="B34" t="n">
-        <v>92132</v>
+        <v>91737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556973</v>
+        <v>556951</v>
       </c>
       <c r="R34" t="n">
-        <v>6710401</v>
+        <v>6710395</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,32 +4552,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130671327</v>
+        <v>130671362</v>
       </c>
       <c r="B35" t="n">
-        <v>91725</v>
+        <v>79219</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556951</v>
+        <v>557271</v>
       </c>
       <c r="R35" t="n">
-        <v>6710395</v>
+        <v>6710350</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4659,10 +4659,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130671362</v>
+        <v>130671356</v>
       </c>
       <c r="B36" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4694,10 +4694,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557271</v>
+        <v>557307</v>
       </c>
       <c r="R36" t="n">
-        <v>6710350</v>
+        <v>6710299</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4766,32 +4766,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130671356</v>
+        <v>130671328</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>92145</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557307</v>
+        <v>556973</v>
       </c>
       <c r="R37" t="n">
-        <v>6710299</v>
+        <v>6710401</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4876,7 +4876,7 @@
         <v>130671345</v>
       </c>
       <c r="B38" t="n">
-        <v>81196</v>
+        <v>81204</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4980,50 +4980,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130671342</v>
+        <v>130671344</v>
       </c>
       <c r="B39" t="n">
-        <v>57851</v>
+        <v>92233</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557118</v>
+        <v>556959</v>
       </c>
       <c r="R39" t="n">
-        <v>6710289</v>
+        <v>6710396</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5055,7 +5050,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5065,7 +5060,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5092,10 +5087,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130671338</v>
+        <v>130671342</v>
       </c>
       <c r="B40" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5123,7 +5118,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5132,10 +5127,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557146</v>
+        <v>557118</v>
       </c>
       <c r="R40" t="n">
-        <v>6710445</v>
+        <v>6710289</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5167,7 +5162,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5177,7 +5172,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5204,10 +5199,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130671339</v>
+        <v>130671338</v>
       </c>
       <c r="B41" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5244,10 +5239,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557178</v>
+        <v>557146</v>
       </c>
       <c r="R41" t="n">
-        <v>6710135</v>
+        <v>6710445</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5279,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5289,7 +5284,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5316,45 +5311,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130671344</v>
+        <v>130671339</v>
       </c>
       <c r="B42" t="n">
-        <v>92220</v>
+        <v>57859</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556959</v>
+        <v>557178</v>
       </c>
       <c r="R42" t="n">
-        <v>6710396</v>
+        <v>6710135</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5423,10 +5423,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130671336</v>
+        <v>130671361</v>
       </c>
       <c r="B43" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5434,39 +5434,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556993</v>
+        <v>557273</v>
       </c>
       <c r="R43" t="n">
-        <v>6710383</v>
+        <v>6710349</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5498,7 +5493,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5508,7 +5503,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5535,10 +5530,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130671361</v>
+        <v>130671336</v>
       </c>
       <c r="B44" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5546,34 +5541,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557273</v>
+        <v>556993</v>
       </c>
       <c r="R44" t="n">
-        <v>6710349</v>
+        <v>6710383</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5645,7 +5645,7 @@
         <v>130671355</v>
       </c>
       <c r="B45" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>130671335</v>
       </c>
       <c r="B46" t="n">
-        <v>91782</v>
+        <v>91795</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>130671337</v>
       </c>
       <c r="B48" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>130671334</v>
       </c>
       <c r="B49" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>130671340</v>
       </c>
       <c r="B50" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>130671347</v>
       </c>
       <c r="B51" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6407,45 +6407,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130671330</v>
+        <v>130671372</v>
       </c>
       <c r="B52" t="n">
-        <v>91761</v>
+        <v>5177</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557102</v>
+        <v>557068</v>
       </c>
       <c r="R52" t="n">
-        <v>6710446</v>
+        <v>6710403</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6477,7 +6482,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6487,7 +6492,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6514,50 +6519,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130671372</v>
+        <v>130671330</v>
       </c>
       <c r="B53" t="n">
-        <v>5177</v>
+        <v>91774</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557068</v>
+        <v>557102</v>
       </c>
       <c r="R53" t="n">
-        <v>6710403</v>
+        <v>6710446</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6741,7 +6741,7 @@
         <v>130671358</v>
       </c>
       <c r="B55" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6845,50 +6845,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130671373</v>
+        <v>130671329</v>
       </c>
       <c r="B56" t="n">
-        <v>5177</v>
+        <v>91774</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>557193</v>
+        <v>557322</v>
       </c>
       <c r="R56" t="n">
-        <v>6710075</v>
+        <v>6710273</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6920,7 +6915,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6930,7 +6925,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6957,45 +6952,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130671329</v>
+        <v>130671373</v>
       </c>
       <c r="B57" t="n">
-        <v>91761</v>
+        <v>5177</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557322</v>
+        <v>557193</v>
       </c>
       <c r="R57" t="n">
-        <v>6710273</v>
+        <v>6710075</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7291,7 +7291,7 @@
         <v>130671331</v>
       </c>
       <c r="B60" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -3358,7 +3358,7 @@
         <v>130671341</v>
       </c>
       <c r="B24" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>130671365</v>
       </c>
       <c r="B25" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>130671343</v>
       </c>
       <c r="B28" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>130671357</v>
       </c>
       <c r="B29" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>130671332</v>
       </c>
       <c r="B30" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4124,10 +4124,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130671363</v>
+        <v>130671359</v>
       </c>
       <c r="B31" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557265</v>
+        <v>557278</v>
       </c>
       <c r="R31" t="n">
-        <v>6710358</v>
+        <v>6710338</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4231,10 +4231,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130671360</v>
+        <v>130671363</v>
       </c>
       <c r="B32" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557294</v>
+        <v>557265</v>
       </c>
       <c r="R32" t="n">
-        <v>6710342</v>
+        <v>6710358</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4338,10 +4338,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130671359</v>
+        <v>130671360</v>
       </c>
       <c r="B33" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557278</v>
+        <v>557294</v>
       </c>
       <c r="R33" t="n">
-        <v>6710338</v>
+        <v>6710342</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4445,32 +4445,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130671327</v>
+        <v>130671328</v>
       </c>
       <c r="B34" t="n">
-        <v>91737</v>
+        <v>92146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556951</v>
+        <v>556973</v>
       </c>
       <c r="R34" t="n">
-        <v>6710395</v>
+        <v>6710401</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,32 +4552,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130671362</v>
+        <v>130671327</v>
       </c>
       <c r="B35" t="n">
-        <v>79219</v>
+        <v>91738</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557271</v>
+        <v>556951</v>
       </c>
       <c r="R35" t="n">
-        <v>6710350</v>
+        <v>6710395</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4659,10 +4659,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130671356</v>
+        <v>130671362</v>
       </c>
       <c r="B36" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4694,10 +4694,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557307</v>
+        <v>557271</v>
       </c>
       <c r="R36" t="n">
-        <v>6710299</v>
+        <v>6710350</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4766,32 +4766,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130671328</v>
+        <v>130671356</v>
       </c>
       <c r="B37" t="n">
-        <v>92145</v>
+        <v>79220</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556973</v>
+        <v>557307</v>
       </c>
       <c r="R37" t="n">
-        <v>6710401</v>
+        <v>6710299</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4876,7 +4876,7 @@
         <v>130671345</v>
       </c>
       <c r="B38" t="n">
-        <v>81204</v>
+        <v>81205</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4980,45 +4980,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130671344</v>
+        <v>130671342</v>
       </c>
       <c r="B39" t="n">
-        <v>92233</v>
+        <v>57860</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556959</v>
+        <v>557118</v>
       </c>
       <c r="R39" t="n">
-        <v>6710396</v>
+        <v>6710289</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5050,7 +5055,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5060,7 +5065,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5087,10 +5092,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130671342</v>
+        <v>130671338</v>
       </c>
       <c r="B40" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5118,7 +5123,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5127,10 +5132,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557118</v>
+        <v>557146</v>
       </c>
       <c r="R40" t="n">
-        <v>6710289</v>
+        <v>6710445</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5162,7 +5167,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5172,7 +5177,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,10 +5204,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130671338</v>
+        <v>130671339</v>
       </c>
       <c r="B41" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5239,10 +5244,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557146</v>
+        <v>557178</v>
       </c>
       <c r="R41" t="n">
-        <v>6710445</v>
+        <v>6710135</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5274,7 +5279,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,7 +5289,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5311,50 +5316,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130671339</v>
+        <v>130671344</v>
       </c>
       <c r="B42" t="n">
-        <v>57859</v>
+        <v>92234</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557178</v>
+        <v>556959</v>
       </c>
       <c r="R42" t="n">
-        <v>6710135</v>
+        <v>6710396</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5426,7 +5426,7 @@
         <v>130671361</v>
       </c>
       <c r="B43" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>130671336</v>
       </c>
       <c r="B44" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>130671355</v>
       </c>
       <c r="B45" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>130671335</v>
       </c>
       <c r="B46" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>130671337</v>
       </c>
       <c r="B48" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>130671334</v>
       </c>
       <c r="B49" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>130671340</v>
       </c>
       <c r="B50" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>130671347</v>
       </c>
       <c r="B51" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6407,50 +6407,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130671372</v>
+        <v>130671330</v>
       </c>
       <c r="B52" t="n">
-        <v>5177</v>
+        <v>91775</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557068</v>
+        <v>557102</v>
       </c>
       <c r="R52" t="n">
-        <v>6710403</v>
+        <v>6710446</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6482,7 +6477,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6492,7 +6487,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6519,45 +6514,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130671330</v>
+        <v>130671372</v>
       </c>
       <c r="B53" t="n">
-        <v>91774</v>
+        <v>5177</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557102</v>
+        <v>557068</v>
       </c>
       <c r="R53" t="n">
-        <v>6710446</v>
+        <v>6710403</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6738,45 +6738,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130671358</v>
+        <v>130671373</v>
       </c>
       <c r="B55" t="n">
-        <v>79219</v>
+        <v>5177</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557300</v>
+        <v>557193</v>
       </c>
       <c r="R55" t="n">
-        <v>6710292</v>
+        <v>6710075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6808,7 +6813,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6818,7 +6823,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6848,7 +6853,7 @@
         <v>130671329</v>
       </c>
       <c r="B56" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6952,50 +6957,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130671373</v>
+        <v>130671358</v>
       </c>
       <c r="B57" t="n">
-        <v>5177</v>
+        <v>79220</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557193</v>
+        <v>557300</v>
       </c>
       <c r="R57" t="n">
-        <v>6710075</v>
+        <v>6710292</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7291,7 +7291,7 @@
         <v>130671331</v>
       </c>
       <c r="B60" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -3358,7 +3358,7 @@
         <v>130671341</v>
       </c>
       <c r="B24" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>130671365</v>
       </c>
       <c r="B25" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>130671343</v>
       </c>
       <c r="B28" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130671357</v>
+        <v>130671332</v>
       </c>
       <c r="B29" t="n">
-        <v>79220</v>
+        <v>91776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,21 +3921,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557304</v>
+        <v>556970</v>
       </c>
       <c r="R29" t="n">
-        <v>6710306</v>
+        <v>6710400</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4017,10 +4017,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130671332</v>
+        <v>130671357</v>
       </c>
       <c r="B30" t="n">
-        <v>91775</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,21 +4028,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556970</v>
+        <v>557304</v>
       </c>
       <c r="R30" t="n">
-        <v>6710400</v>
+        <v>6710306</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4124,10 +4124,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130671359</v>
+        <v>130671363</v>
       </c>
       <c r="B31" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557278</v>
+        <v>557265</v>
       </c>
       <c r="R31" t="n">
-        <v>6710338</v>
+        <v>6710358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4231,10 +4231,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130671363</v>
+        <v>130671360</v>
       </c>
       <c r="B32" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557265</v>
+        <v>557294</v>
       </c>
       <c r="R32" t="n">
-        <v>6710358</v>
+        <v>6710342</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4338,10 +4338,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130671360</v>
+        <v>130671359</v>
       </c>
       <c r="B33" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557294</v>
+        <v>557278</v>
       </c>
       <c r="R33" t="n">
-        <v>6710342</v>
+        <v>6710338</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4448,7 +4448,7 @@
         <v>130671328</v>
       </c>
       <c r="B34" t="n">
-        <v>92146</v>
+        <v>92147</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>130671327</v>
       </c>
       <c r="B35" t="n">
-        <v>91738</v>
+        <v>91739</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>130671362</v>
       </c>
       <c r="B36" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>130671356</v>
       </c>
       <c r="B37" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>130671345</v>
       </c>
       <c r="B38" t="n">
-        <v>81205</v>
+        <v>81206</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4980,50 +4980,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130671342</v>
+        <v>130671344</v>
       </c>
       <c r="B39" t="n">
-        <v>57860</v>
+        <v>92235</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557118</v>
+        <v>556959</v>
       </c>
       <c r="R39" t="n">
-        <v>6710289</v>
+        <v>6710396</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5055,7 +5050,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5065,7 +5060,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5092,10 +5087,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130671338</v>
+        <v>130671342</v>
       </c>
       <c r="B40" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5123,7 +5118,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5132,10 +5127,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557146</v>
+        <v>557118</v>
       </c>
       <c r="R40" t="n">
-        <v>6710445</v>
+        <v>6710289</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5167,7 +5162,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5177,7 +5172,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5204,10 +5199,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130671339</v>
+        <v>130671338</v>
       </c>
       <c r="B41" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5244,10 +5239,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557178</v>
+        <v>557146</v>
       </c>
       <c r="R41" t="n">
-        <v>6710135</v>
+        <v>6710445</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5279,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5289,7 +5284,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5316,45 +5311,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130671344</v>
+        <v>130671339</v>
       </c>
       <c r="B42" t="n">
-        <v>92234</v>
+        <v>57861</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556959</v>
+        <v>557178</v>
       </c>
       <c r="R42" t="n">
-        <v>6710396</v>
+        <v>6710135</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5426,7 +5426,7 @@
         <v>130671361</v>
       </c>
       <c r="B43" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>130671336</v>
       </c>
       <c r="B44" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>130671355</v>
       </c>
       <c r="B45" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>130671335</v>
       </c>
       <c r="B46" t="n">
-        <v>91796</v>
+        <v>91797</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>130671337</v>
       </c>
       <c r="B48" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>130671334</v>
       </c>
       <c r="B49" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130671340</v>
+        <v>130671347</v>
       </c>
       <c r="B50" t="n">
-        <v>57860</v>
+        <v>91796</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6203,39 +6203,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557079</v>
+        <v>557185</v>
       </c>
       <c r="R50" t="n">
-        <v>6710383</v>
+        <v>6710142</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6267,7 +6258,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6277,7 +6268,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6304,10 +6295,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130671347</v>
+        <v>130671340</v>
       </c>
       <c r="B51" t="n">
-        <v>91795</v>
+        <v>57861</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6315,30 +6306,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557185</v>
+        <v>557079</v>
       </c>
       <c r="R51" t="n">
-        <v>6710142</v>
+        <v>6710383</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6410,7 +6410,7 @@
         <v>130671330</v>
       </c>
       <c r="B52" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6514,10 +6514,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130671372</v>
+        <v>130671325</v>
       </c>
       <c r="B53" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6525,21 +6525,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6554,10 +6554,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557068</v>
+        <v>557029</v>
       </c>
       <c r="R53" t="n">
-        <v>6710403</v>
+        <v>6710414</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6626,10 +6626,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130671325</v>
+        <v>130671372</v>
       </c>
       <c r="B54" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6637,21 +6637,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557029</v>
+        <v>557068</v>
       </c>
       <c r="R54" t="n">
-        <v>6710414</v>
+        <v>6710403</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6738,50 +6738,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130671373</v>
+        <v>130671358</v>
       </c>
       <c r="B55" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557193</v>
+        <v>557300</v>
       </c>
       <c r="R55" t="n">
-        <v>6710075</v>
+        <v>6710292</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6813,7 +6808,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6823,7 +6818,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6853,7 +6848,7 @@
         <v>130671329</v>
       </c>
       <c r="B56" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6957,45 +6952,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130671358</v>
+        <v>130671373</v>
       </c>
       <c r="B57" t="n">
-        <v>79220</v>
+        <v>5177</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557300</v>
+        <v>557193</v>
       </c>
       <c r="R57" t="n">
-        <v>6710292</v>
+        <v>6710075</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7291,7 +7291,7 @@
         <v>130671331</v>
       </c>
       <c r="B60" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -3910,10 +3910,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130671332</v>
+        <v>130671357</v>
       </c>
       <c r="B29" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,21 +3921,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556970</v>
+        <v>557304</v>
       </c>
       <c r="R29" t="n">
-        <v>6710400</v>
+        <v>6710306</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4017,10 +4017,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130671357</v>
+        <v>130671332</v>
       </c>
       <c r="B30" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,21 +4028,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>557304</v>
+        <v>556970</v>
       </c>
       <c r="R30" t="n">
-        <v>6710306</v>
+        <v>6710400</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4124,7 +4124,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130671363</v>
+        <v>130671360</v>
       </c>
       <c r="B31" t="n">
         <v>79221</v>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557265</v>
+        <v>557294</v>
       </c>
       <c r="R31" t="n">
-        <v>6710358</v>
+        <v>6710342</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4231,7 +4231,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130671360</v>
+        <v>130671359</v>
       </c>
       <c r="B32" t="n">
         <v>79221</v>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557294</v>
+        <v>557278</v>
       </c>
       <c r="R32" t="n">
-        <v>6710342</v>
+        <v>6710338</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4338,7 +4338,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130671359</v>
+        <v>130671363</v>
       </c>
       <c r="B33" t="n">
         <v>79221</v>
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557278</v>
+        <v>557265</v>
       </c>
       <c r="R33" t="n">
-        <v>6710338</v>
+        <v>6710358</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4445,32 +4445,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130671328</v>
+        <v>130671327</v>
       </c>
       <c r="B34" t="n">
-        <v>92147</v>
+        <v>91739</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556973</v>
+        <v>556951</v>
       </c>
       <c r="R34" t="n">
-        <v>6710401</v>
+        <v>6710395</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,32 +4552,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130671327</v>
+        <v>130671328</v>
       </c>
       <c r="B35" t="n">
-        <v>91739</v>
+        <v>92147</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556951</v>
+        <v>556973</v>
       </c>
       <c r="R35" t="n">
-        <v>6710395</v>
+        <v>6710401</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5642,10 +5642,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130671355</v>
+        <v>130671335</v>
       </c>
       <c r="B45" t="n">
-        <v>79221</v>
+        <v>91797</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5653,21 +5653,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557310</v>
+        <v>557382</v>
       </c>
       <c r="R45" t="n">
-        <v>6710293</v>
+        <v>6710266</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5749,10 +5749,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130671335</v>
+        <v>130671355</v>
       </c>
       <c r="B46" t="n">
-        <v>91797</v>
+        <v>79221</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557382</v>
+        <v>557310</v>
       </c>
       <c r="R46" t="n">
-        <v>6710266</v>
+        <v>6710293</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6407,45 +6407,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130671330</v>
+        <v>130671325</v>
       </c>
       <c r="B52" t="n">
-        <v>91776</v>
+        <v>5197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557102</v>
+        <v>557029</v>
       </c>
       <c r="R52" t="n">
-        <v>6710446</v>
+        <v>6710414</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6477,7 +6482,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6487,7 +6492,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6514,50 +6519,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130671325</v>
+        <v>130671330</v>
       </c>
       <c r="B53" t="n">
-        <v>5197</v>
+        <v>91776</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557029</v>
+        <v>557102</v>
       </c>
       <c r="R53" t="n">
-        <v>6710414</v>
+        <v>6710446</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6738,10 +6738,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130671358</v>
+        <v>130671329</v>
       </c>
       <c r="B55" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6749,21 +6749,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6773,10 +6773,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557300</v>
+        <v>557322</v>
       </c>
       <c r="R55" t="n">
-        <v>6710292</v>
+        <v>6710273</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6845,10 +6845,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130671329</v>
+        <v>130671358</v>
       </c>
       <c r="B56" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6856,21 +6856,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>557322</v>
+        <v>557300</v>
       </c>
       <c r="R56" t="n">
-        <v>6710273</v>
+        <v>6710292</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -3910,10 +3910,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130671357</v>
+        <v>130671332</v>
       </c>
       <c r="B29" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,21 +3921,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557304</v>
+        <v>556970</v>
       </c>
       <c r="R29" t="n">
-        <v>6710306</v>
+        <v>6710400</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4017,10 +4017,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130671332</v>
+        <v>130671357</v>
       </c>
       <c r="B30" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,21 +4028,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556970</v>
+        <v>557304</v>
       </c>
       <c r="R30" t="n">
-        <v>6710400</v>
+        <v>6710306</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4124,7 +4124,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130671360</v>
+        <v>130671363</v>
       </c>
       <c r="B31" t="n">
         <v>79221</v>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557294</v>
+        <v>557265</v>
       </c>
       <c r="R31" t="n">
-        <v>6710342</v>
+        <v>6710358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4231,7 +4231,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130671359</v>
+        <v>130671360</v>
       </c>
       <c r="B32" t="n">
         <v>79221</v>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557278</v>
+        <v>557294</v>
       </c>
       <c r="R32" t="n">
-        <v>6710338</v>
+        <v>6710342</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4338,7 +4338,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130671363</v>
+        <v>130671359</v>
       </c>
       <c r="B33" t="n">
         <v>79221</v>
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557265</v>
+        <v>557278</v>
       </c>
       <c r="R33" t="n">
-        <v>6710358</v>
+        <v>6710338</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4445,32 +4445,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130671327</v>
+        <v>130671328</v>
       </c>
       <c r="B34" t="n">
-        <v>91739</v>
+        <v>92147</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556951</v>
+        <v>556973</v>
       </c>
       <c r="R34" t="n">
-        <v>6710395</v>
+        <v>6710401</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,32 +4552,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130671328</v>
+        <v>130671327</v>
       </c>
       <c r="B35" t="n">
-        <v>92147</v>
+        <v>91739</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556973</v>
+        <v>556951</v>
       </c>
       <c r="R35" t="n">
-        <v>6710401</v>
+        <v>6710395</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4980,45 +4980,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130671344</v>
+        <v>130671342</v>
       </c>
       <c r="B39" t="n">
-        <v>92235</v>
+        <v>57861</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556959</v>
+        <v>557118</v>
       </c>
       <c r="R39" t="n">
-        <v>6710396</v>
+        <v>6710289</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5050,7 +5055,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5060,7 +5065,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5087,50 +5092,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130671342</v>
+        <v>130671344</v>
       </c>
       <c r="B40" t="n">
-        <v>57861</v>
+        <v>92235</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557118</v>
+        <v>556959</v>
       </c>
       <c r="R40" t="n">
-        <v>6710289</v>
+        <v>6710396</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5423,10 +5423,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130671361</v>
+        <v>130671336</v>
       </c>
       <c r="B43" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5434,34 +5434,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557273</v>
+        <v>556993</v>
       </c>
       <c r="R43" t="n">
-        <v>6710349</v>
+        <v>6710383</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5493,7 +5498,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5503,7 +5508,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5530,10 +5535,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130671336</v>
+        <v>130671361</v>
       </c>
       <c r="B44" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5541,39 +5546,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556993</v>
+        <v>557273</v>
       </c>
       <c r="R44" t="n">
-        <v>6710383</v>
+        <v>6710349</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5642,10 +5642,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130671335</v>
+        <v>130671355</v>
       </c>
       <c r="B45" t="n">
-        <v>91797</v>
+        <v>79221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5653,21 +5653,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557382</v>
+        <v>557310</v>
       </c>
       <c r="R45" t="n">
-        <v>6710266</v>
+        <v>6710293</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5749,10 +5749,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130671355</v>
+        <v>130671335</v>
       </c>
       <c r="B46" t="n">
-        <v>79221</v>
+        <v>91797</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557310</v>
+        <v>557382</v>
       </c>
       <c r="R46" t="n">
-        <v>6710293</v>
+        <v>6710266</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5968,10 +5968,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130671337</v>
+        <v>130671334</v>
       </c>
       <c r="B48" t="n">
-        <v>57861</v>
+        <v>58023</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5979,27 +5979,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557203</v>
+        <v>557212</v>
       </c>
       <c r="R48" t="n">
-        <v>6710208</v>
+        <v>6710081</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6080,10 +6080,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130671334</v>
+        <v>130671337</v>
       </c>
       <c r="B49" t="n">
-        <v>58023</v>
+        <v>57861</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6091,27 +6091,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557212</v>
+        <v>557203</v>
       </c>
       <c r="R49" t="n">
-        <v>6710081</v>
+        <v>6710208</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6192,10 +6192,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130671347</v>
+        <v>130671340</v>
       </c>
       <c r="B50" t="n">
-        <v>91796</v>
+        <v>57861</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6203,30 +6203,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557185</v>
+        <v>557079</v>
       </c>
       <c r="R50" t="n">
-        <v>6710142</v>
+        <v>6710383</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6258,7 +6267,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6268,7 +6277,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6295,10 +6304,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130671340</v>
+        <v>130671347</v>
       </c>
       <c r="B51" t="n">
-        <v>57861</v>
+        <v>91796</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6306,39 +6315,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557079</v>
+        <v>557185</v>
       </c>
       <c r="R51" t="n">
-        <v>6710383</v>
+        <v>6710142</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6407,50 +6407,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130671325</v>
+        <v>130671330</v>
       </c>
       <c r="B52" t="n">
-        <v>5197</v>
+        <v>91776</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557029</v>
+        <v>557102</v>
       </c>
       <c r="R52" t="n">
-        <v>6710414</v>
+        <v>6710446</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6482,7 +6477,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6492,7 +6487,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6519,45 +6514,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130671330</v>
+        <v>130671372</v>
       </c>
       <c r="B53" t="n">
-        <v>91776</v>
+        <v>5177</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557102</v>
+        <v>557068</v>
       </c>
       <c r="R53" t="n">
-        <v>6710446</v>
+        <v>6710403</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6626,10 +6626,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130671372</v>
+        <v>130671325</v>
       </c>
       <c r="B54" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6637,21 +6637,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557068</v>
+        <v>557029</v>
       </c>
       <c r="R54" t="n">
-        <v>6710403</v>
+        <v>6710414</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6845,45 +6845,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130671358</v>
+        <v>130671373</v>
       </c>
       <c r="B56" t="n">
-        <v>79221</v>
+        <v>5177</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>557300</v>
+        <v>557193</v>
       </c>
       <c r="R56" t="n">
-        <v>6710292</v>
+        <v>6710075</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6915,7 +6920,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6925,7 +6930,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6952,50 +6957,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130671373</v>
+        <v>130671358</v>
       </c>
       <c r="B57" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557193</v>
+        <v>557300</v>
       </c>
       <c r="R57" t="n">
-        <v>6710075</v>
+        <v>6710292</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7064,7 +7064,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130671367</v>
+        <v>130671371</v>
       </c>
       <c r="B58" t="n">
         <v>5177</v>
@@ -7095,7 +7095,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557187</v>
+        <v>557184</v>
       </c>
       <c r="R58" t="n">
-        <v>6710451</v>
+        <v>6710457</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7176,7 +7176,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130671371</v>
+        <v>130671367</v>
       </c>
       <c r="B59" t="n">
         <v>5177</v>
@@ -7207,7 +7207,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557184</v>
+        <v>557187</v>
       </c>
       <c r="R59" t="n">
-        <v>6710457</v>
+        <v>6710451</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -5092,45 +5092,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130671344</v>
+        <v>130671338</v>
       </c>
       <c r="B40" t="n">
-        <v>92235</v>
+        <v>57861</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>556959</v>
+        <v>557146</v>
       </c>
       <c r="R40" t="n">
-        <v>6710396</v>
+        <v>6710445</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5162,7 +5167,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5172,7 +5177,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,7 +5204,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130671338</v>
+        <v>130671339</v>
       </c>
       <c r="B41" t="n">
         <v>57861</v>
@@ -5239,10 +5244,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557146</v>
+        <v>557178</v>
       </c>
       <c r="R41" t="n">
-        <v>6710445</v>
+        <v>6710135</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5274,7 +5279,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,7 +5289,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5311,50 +5316,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130671339</v>
+        <v>130671344</v>
       </c>
       <c r="B42" t="n">
-        <v>57861</v>
+        <v>92235</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557178</v>
+        <v>556959</v>
       </c>
       <c r="R42" t="n">
-        <v>6710135</v>
+        <v>6710396</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5423,10 +5423,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130671336</v>
+        <v>130671361</v>
       </c>
       <c r="B43" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5434,39 +5434,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556993</v>
+        <v>557273</v>
       </c>
       <c r="R43" t="n">
-        <v>6710383</v>
+        <v>6710349</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5498,7 +5493,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5508,7 +5503,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5535,10 +5530,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130671361</v>
+        <v>130671336</v>
       </c>
       <c r="B44" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5546,34 +5541,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557273</v>
+        <v>556993</v>
       </c>
       <c r="R44" t="n">
-        <v>6710349</v>
+        <v>6710383</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5968,10 +5968,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130671334</v>
+        <v>130671337</v>
       </c>
       <c r="B48" t="n">
-        <v>58023</v>
+        <v>57861</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5979,27 +5979,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557212</v>
+        <v>557203</v>
       </c>
       <c r="R48" t="n">
-        <v>6710081</v>
+        <v>6710208</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6080,10 +6080,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130671337</v>
+        <v>130671334</v>
       </c>
       <c r="B49" t="n">
-        <v>57861</v>
+        <v>58023</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6091,27 +6091,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557203</v>
+        <v>557212</v>
       </c>
       <c r="R49" t="n">
-        <v>6710208</v>
+        <v>6710081</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7064,7 +7064,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130671371</v>
+        <v>130671367</v>
       </c>
       <c r="B58" t="n">
         <v>5177</v>
@@ -7095,7 +7095,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557184</v>
+        <v>557187</v>
       </c>
       <c r="R58" t="n">
-        <v>6710457</v>
+        <v>6710451</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7176,7 +7176,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130671367</v>
+        <v>130671371</v>
       </c>
       <c r="B59" t="n">
         <v>5177</v>
@@ -7207,7 +7207,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557187</v>
+        <v>557184</v>
       </c>
       <c r="R59" t="n">
-        <v>6710451</v>
+        <v>6710457</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -4445,32 +4445,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130671328</v>
+        <v>130671327</v>
       </c>
       <c r="B34" t="n">
-        <v>92147</v>
+        <v>91739</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556973</v>
+        <v>556951</v>
       </c>
       <c r="R34" t="n">
-        <v>6710401</v>
+        <v>6710395</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,32 +4552,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130671327</v>
+        <v>130671362</v>
       </c>
       <c r="B35" t="n">
-        <v>91739</v>
+        <v>79221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556951</v>
+        <v>557271</v>
       </c>
       <c r="R35" t="n">
-        <v>6710395</v>
+        <v>6710350</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4659,7 +4659,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130671362</v>
+        <v>130671356</v>
       </c>
       <c r="B36" t="n">
         <v>79221</v>
@@ -4694,10 +4694,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557271</v>
+        <v>557307</v>
       </c>
       <c r="R36" t="n">
-        <v>6710350</v>
+        <v>6710299</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4766,32 +4766,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130671356</v>
+        <v>130671328</v>
       </c>
       <c r="B37" t="n">
-        <v>79221</v>
+        <v>92147</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557307</v>
+        <v>556973</v>
       </c>
       <c r="R37" t="n">
-        <v>6710299</v>
+        <v>6710401</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4980,50 +4980,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130671342</v>
+        <v>130671344</v>
       </c>
       <c r="B39" t="n">
-        <v>57861</v>
+        <v>92235</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557118</v>
+        <v>556959</v>
       </c>
       <c r="R39" t="n">
-        <v>6710289</v>
+        <v>6710396</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5055,7 +5050,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5065,7 +5060,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5092,7 +5087,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130671338</v>
+        <v>130671342</v>
       </c>
       <c r="B40" t="n">
         <v>57861</v>
@@ -5123,7 +5118,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5132,10 +5127,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557146</v>
+        <v>557118</v>
       </c>
       <c r="R40" t="n">
-        <v>6710445</v>
+        <v>6710289</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5167,7 +5162,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5177,7 +5172,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5204,7 +5199,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130671339</v>
+        <v>130671338</v>
       </c>
       <c r="B41" t="n">
         <v>57861</v>
@@ -5244,10 +5239,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557178</v>
+        <v>557146</v>
       </c>
       <c r="R41" t="n">
-        <v>6710135</v>
+        <v>6710445</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5279,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5289,7 +5284,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5316,45 +5311,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130671344</v>
+        <v>130671339</v>
       </c>
       <c r="B42" t="n">
-        <v>92235</v>
+        <v>57861</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556959</v>
+        <v>557178</v>
       </c>
       <c r="R42" t="n">
-        <v>6710396</v>
+        <v>6710135</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6192,10 +6192,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130671340</v>
+        <v>130671347</v>
       </c>
       <c r="B50" t="n">
-        <v>57861</v>
+        <v>91796</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6203,39 +6203,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557079</v>
+        <v>557185</v>
       </c>
       <c r="R50" t="n">
-        <v>6710383</v>
+        <v>6710142</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6267,7 +6258,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6277,7 +6268,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6304,10 +6295,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130671347</v>
+        <v>130671340</v>
       </c>
       <c r="B51" t="n">
-        <v>91796</v>
+        <v>57861</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6315,30 +6306,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557185</v>
+        <v>557079</v>
       </c>
       <c r="R51" t="n">
-        <v>6710142</v>
+        <v>6710383</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6738,45 +6738,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130671329</v>
+        <v>130671373</v>
       </c>
       <c r="B55" t="n">
-        <v>91776</v>
+        <v>5177</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557322</v>
+        <v>557193</v>
       </c>
       <c r="R55" t="n">
-        <v>6710273</v>
+        <v>6710075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6808,7 +6813,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6818,7 +6823,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6845,50 +6850,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130671373</v>
+        <v>130671358</v>
       </c>
       <c r="B56" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>557193</v>
+        <v>557300</v>
       </c>
       <c r="R56" t="n">
-        <v>6710075</v>
+        <v>6710292</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6957,10 +6957,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130671358</v>
+        <v>130671329</v>
       </c>
       <c r="B57" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6968,21 +6968,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557300</v>
+        <v>557322</v>
       </c>
       <c r="R57" t="n">
-        <v>6710292</v>
+        <v>6710273</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7288,45 +7288,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130671331</v>
+        <v>130671326</v>
       </c>
       <c r="B60" t="n">
-        <v>91776</v>
+        <v>5197</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556976</v>
+        <v>557081</v>
       </c>
       <c r="R60" t="n">
-        <v>6710393</v>
+        <v>6710301</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7358,7 +7363,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7368,7 +7373,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7395,50 +7400,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130671326</v>
+        <v>130671331</v>
       </c>
       <c r="B61" t="n">
-        <v>5197</v>
+        <v>91776</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>557081</v>
+        <v>556976</v>
       </c>
       <c r="R61" t="n">
-        <v>6710301</v>
+        <v>6710393</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -4980,45 +4980,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130671344</v>
+        <v>130671342</v>
       </c>
       <c r="B39" t="n">
-        <v>92235</v>
+        <v>57861</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556959</v>
+        <v>557118</v>
       </c>
       <c r="R39" t="n">
-        <v>6710396</v>
+        <v>6710289</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5050,7 +5055,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5060,7 +5065,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5087,7 +5092,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130671342</v>
+        <v>130671338</v>
       </c>
       <c r="B40" t="n">
         <v>57861</v>
@@ -5118,7 +5123,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5127,10 +5132,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557118</v>
+        <v>557146</v>
       </c>
       <c r="R40" t="n">
-        <v>6710289</v>
+        <v>6710445</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5162,7 +5167,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5172,7 +5177,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,7 +5204,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130671338</v>
+        <v>130671339</v>
       </c>
       <c r="B41" t="n">
         <v>57861</v>
@@ -5239,10 +5244,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557146</v>
+        <v>557178</v>
       </c>
       <c r="R41" t="n">
-        <v>6710445</v>
+        <v>6710135</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5274,7 +5279,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,7 +5289,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5311,50 +5316,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130671339</v>
+        <v>130671344</v>
       </c>
       <c r="B42" t="n">
-        <v>57861</v>
+        <v>92235</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557178</v>
+        <v>556959</v>
       </c>
       <c r="R42" t="n">
-        <v>6710135</v>
+        <v>6710396</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5423,10 +5423,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130671361</v>
+        <v>130671336</v>
       </c>
       <c r="B43" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5434,34 +5434,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557273</v>
+        <v>556993</v>
       </c>
       <c r="R43" t="n">
-        <v>6710349</v>
+        <v>6710383</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5493,7 +5498,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5503,7 +5508,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5530,10 +5535,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130671336</v>
+        <v>130671361</v>
       </c>
       <c r="B44" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5541,39 +5546,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556993</v>
+        <v>557273</v>
       </c>
       <c r="R44" t="n">
-        <v>6710383</v>
+        <v>6710349</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6738,50 +6738,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130671373</v>
+        <v>130671329</v>
       </c>
       <c r="B55" t="n">
-        <v>5177</v>
+        <v>91776</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557193</v>
+        <v>557322</v>
       </c>
       <c r="R55" t="n">
-        <v>6710075</v>
+        <v>6710273</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6813,7 +6808,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6823,7 +6818,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6957,45 +6952,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130671329</v>
+        <v>130671373</v>
       </c>
       <c r="B57" t="n">
-        <v>91776</v>
+        <v>5177</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557322</v>
+        <v>557193</v>
       </c>
       <c r="R57" t="n">
-        <v>6710273</v>
+        <v>6710075</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7064,7 +7064,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130671367</v>
+        <v>130671371</v>
       </c>
       <c r="B58" t="n">
         <v>5177</v>
@@ -7095,7 +7095,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557187</v>
+        <v>557184</v>
       </c>
       <c r="R58" t="n">
-        <v>6710451</v>
+        <v>6710457</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7176,7 +7176,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130671371</v>
+        <v>130671367</v>
       </c>
       <c r="B59" t="n">
         <v>5177</v>
@@ -7207,7 +7207,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557184</v>
+        <v>557187</v>
       </c>
       <c r="R59" t="n">
-        <v>6710457</v>
+        <v>6710451</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7288,50 +7288,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130671326</v>
+        <v>130671331</v>
       </c>
       <c r="B60" t="n">
-        <v>5197</v>
+        <v>91776</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>557081</v>
+        <v>556976</v>
       </c>
       <c r="R60" t="n">
-        <v>6710301</v>
+        <v>6710393</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7363,7 +7358,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7373,7 +7368,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7400,45 +7395,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130671331</v>
+        <v>130671326</v>
       </c>
       <c r="B61" t="n">
-        <v>91776</v>
+        <v>5197</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556976</v>
+        <v>557081</v>
       </c>
       <c r="R61" t="n">
-        <v>6710393</v>
+        <v>6710301</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -3913,7 +3913,7 @@
         <v>130671332</v>
       </c>
       <c r="B29" t="n">
-        <v>91776</v>
+        <v>91784</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130671363</v>
+        <v>130671360</v>
       </c>
       <c r="B31" t="n">
         <v>79221</v>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557265</v>
+        <v>557294</v>
       </c>
       <c r="R31" t="n">
-        <v>6710358</v>
+        <v>6710342</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4231,7 +4231,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130671360</v>
+        <v>130671363</v>
       </c>
       <c r="B32" t="n">
         <v>79221</v>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557294</v>
+        <v>557265</v>
       </c>
       <c r="R32" t="n">
-        <v>6710342</v>
+        <v>6710358</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4448,7 +4448,7 @@
         <v>130671327</v>
       </c>
       <c r="B34" t="n">
-        <v>91739</v>
+        <v>91747</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4659,32 +4659,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130671356</v>
+        <v>130671328</v>
       </c>
       <c r="B36" t="n">
-        <v>79221</v>
+        <v>92155</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4694,10 +4694,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557307</v>
+        <v>556973</v>
       </c>
       <c r="R36" t="n">
-        <v>6710299</v>
+        <v>6710401</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4766,32 +4766,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130671328</v>
+        <v>130671356</v>
       </c>
       <c r="B37" t="n">
-        <v>92147</v>
+        <v>79221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556973</v>
+        <v>557307</v>
       </c>
       <c r="R37" t="n">
-        <v>6710401</v>
+        <v>6710299</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4980,50 +4980,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130671342</v>
+        <v>130671344</v>
       </c>
       <c r="B39" t="n">
-        <v>57861</v>
+        <v>92243</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557118</v>
+        <v>556959</v>
       </c>
       <c r="R39" t="n">
-        <v>6710289</v>
+        <v>6710396</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5055,7 +5050,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5065,7 +5060,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5092,7 +5087,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130671338</v>
+        <v>130671342</v>
       </c>
       <c r="B40" t="n">
         <v>57861</v>
@@ -5123,7 +5118,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5132,10 +5127,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557146</v>
+        <v>557118</v>
       </c>
       <c r="R40" t="n">
-        <v>6710445</v>
+        <v>6710289</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5167,7 +5162,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5177,7 +5172,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5204,7 +5199,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130671339</v>
+        <v>130671338</v>
       </c>
       <c r="B41" t="n">
         <v>57861</v>
@@ -5244,10 +5239,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557178</v>
+        <v>557146</v>
       </c>
       <c r="R41" t="n">
-        <v>6710135</v>
+        <v>6710445</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5279,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5289,7 +5284,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5316,45 +5311,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130671344</v>
+        <v>130671339</v>
       </c>
       <c r="B42" t="n">
-        <v>92235</v>
+        <v>57861</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556959</v>
+        <v>557178</v>
       </c>
       <c r="R42" t="n">
-        <v>6710396</v>
+        <v>6710135</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5642,10 +5642,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130671355</v>
+        <v>130671335</v>
       </c>
       <c r="B45" t="n">
-        <v>79221</v>
+        <v>91805</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5653,21 +5653,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557310</v>
+        <v>557382</v>
       </c>
       <c r="R45" t="n">
-        <v>6710293</v>
+        <v>6710266</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5749,10 +5749,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130671335</v>
+        <v>130671355</v>
       </c>
       <c r="B46" t="n">
-        <v>91797</v>
+        <v>79221</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557382</v>
+        <v>557310</v>
       </c>
       <c r="R46" t="n">
-        <v>6710266</v>
+        <v>6710293</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5968,10 +5968,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130671337</v>
+        <v>130671334</v>
       </c>
       <c r="B48" t="n">
-        <v>57861</v>
+        <v>58023</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5979,27 +5979,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557203</v>
+        <v>557212</v>
       </c>
       <c r="R48" t="n">
-        <v>6710208</v>
+        <v>6710081</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6080,10 +6080,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130671334</v>
+        <v>130671337</v>
       </c>
       <c r="B49" t="n">
-        <v>58023</v>
+        <v>57861</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6091,27 +6091,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557212</v>
+        <v>557203</v>
       </c>
       <c r="R49" t="n">
-        <v>6710081</v>
+        <v>6710208</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6195,7 +6195,7 @@
         <v>130671347</v>
       </c>
       <c r="B50" t="n">
-        <v>91796</v>
+        <v>91804</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>130671330</v>
       </c>
       <c r="B52" t="n">
-        <v>91776</v>
+        <v>91784</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>130671329</v>
       </c>
       <c r="B55" t="n">
-        <v>91776</v>
+        <v>91784</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130671371</v>
+        <v>130671367</v>
       </c>
       <c r="B58" t="n">
         <v>5177</v>
@@ -7095,7 +7095,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557184</v>
+        <v>557187</v>
       </c>
       <c r="R58" t="n">
-        <v>6710457</v>
+        <v>6710451</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7176,7 +7176,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130671367</v>
+        <v>130671371</v>
       </c>
       <c r="B59" t="n">
         <v>5177</v>
@@ -7207,7 +7207,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557187</v>
+        <v>557184</v>
       </c>
       <c r="R59" t="n">
-        <v>6710451</v>
+        <v>6710457</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,7 +7291,7 @@
         <v>130671331</v>
       </c>
       <c r="B60" t="n">
-        <v>91776</v>
+        <v>91784</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -4124,7 +4124,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130671360</v>
+        <v>130671363</v>
       </c>
       <c r="B31" t="n">
         <v>79221</v>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557294</v>
+        <v>557265</v>
       </c>
       <c r="R31" t="n">
-        <v>6710342</v>
+        <v>6710358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4231,7 +4231,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130671363</v>
+        <v>130671360</v>
       </c>
       <c r="B32" t="n">
         <v>79221</v>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557265</v>
+        <v>557294</v>
       </c>
       <c r="R32" t="n">
-        <v>6710358</v>
+        <v>6710342</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4445,32 +4445,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130671327</v>
+        <v>130671328</v>
       </c>
       <c r="B34" t="n">
-        <v>91747</v>
+        <v>92155</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556951</v>
+        <v>556973</v>
       </c>
       <c r="R34" t="n">
-        <v>6710395</v>
+        <v>6710401</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,32 +4552,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130671362</v>
+        <v>130671327</v>
       </c>
       <c r="B35" t="n">
-        <v>79221</v>
+        <v>91747</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557271</v>
+        <v>556951</v>
       </c>
       <c r="R35" t="n">
-        <v>6710350</v>
+        <v>6710395</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4659,32 +4659,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130671328</v>
+        <v>130671362</v>
       </c>
       <c r="B36" t="n">
-        <v>92155</v>
+        <v>79221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4694,10 +4694,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556973</v>
+        <v>557271</v>
       </c>
       <c r="R36" t="n">
-        <v>6710401</v>
+        <v>6710350</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5423,10 +5423,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130671336</v>
+        <v>130671361</v>
       </c>
       <c r="B43" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5434,39 +5434,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556993</v>
+        <v>557273</v>
       </c>
       <c r="R43" t="n">
-        <v>6710383</v>
+        <v>6710349</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5498,7 +5493,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5508,7 +5503,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5535,10 +5530,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130671361</v>
+        <v>130671336</v>
       </c>
       <c r="B44" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5546,34 +5541,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557273</v>
+        <v>556993</v>
       </c>
       <c r="R44" t="n">
-        <v>6710349</v>
+        <v>6710383</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6407,45 +6407,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130671330</v>
+        <v>130671372</v>
       </c>
       <c r="B52" t="n">
-        <v>91784</v>
+        <v>5177</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557102</v>
+        <v>557068</v>
       </c>
       <c r="R52" t="n">
-        <v>6710446</v>
+        <v>6710403</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6477,7 +6482,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6487,7 +6492,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6514,50 +6519,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130671372</v>
+        <v>130671330</v>
       </c>
       <c r="B53" t="n">
-        <v>5177</v>
+        <v>91784</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557068</v>
+        <v>557102</v>
       </c>
       <c r="R53" t="n">
-        <v>6710403</v>
+        <v>6710446</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -7510,7 +7510,7 @@
         <v>131134870</v>
       </c>
       <c r="B62" t="n">
-        <v>56748</v>
+        <v>56750</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>131134868</v>
       </c>
       <c r="B63" t="n">
-        <v>56755</v>
+        <v>56757</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>131134867</v>
       </c>
       <c r="B64" t="n">
-        <v>56769</v>
+        <v>56771</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -7510,7 +7510,7 @@
         <v>131134870</v>
       </c>
       <c r="B62" t="n">
-        <v>56750</v>
+        <v>56751</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>131134868</v>
       </c>
       <c r="B63" t="n">
-        <v>56757</v>
+        <v>56758</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>131134867</v>
       </c>
       <c r="B64" t="n">
-        <v>56771</v>
+        <v>56772</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -7510,7 +7510,7 @@
         <v>131134870</v>
       </c>
       <c r="B62" t="n">
-        <v>56751</v>
+        <v>56752</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>131134868</v>
       </c>
       <c r="B63" t="n">
-        <v>56758</v>
+        <v>56759</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>131134867</v>
       </c>
       <c r="B64" t="n">
-        <v>56772</v>
+        <v>56773</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -7510,7 +7510,7 @@
         <v>131134870</v>
       </c>
       <c r="B62" t="n">
-        <v>56752</v>
+        <v>56755</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>131134868</v>
       </c>
       <c r="B63" t="n">
-        <v>56759</v>
+        <v>56762</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>131134867</v>
       </c>
       <c r="B64" t="n">
-        <v>56773</v>
+        <v>56776</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -7510,7 +7510,7 @@
         <v>131134870</v>
       </c>
       <c r="B62" t="n">
-        <v>56755</v>
+        <v>56756</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>131134868</v>
       </c>
       <c r="B63" t="n">
-        <v>56762</v>
+        <v>56763</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>131134867</v>
       </c>
       <c r="B64" t="n">
-        <v>56776</v>
+        <v>56777</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -7510,7 +7510,7 @@
         <v>131134870</v>
       </c>
       <c r="B62" t="n">
-        <v>56756</v>
+        <v>56762</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>131134868</v>
       </c>
       <c r="B63" t="n">
-        <v>56763</v>
+        <v>56769</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>131134867</v>
       </c>
       <c r="B64" t="n">
-        <v>56777</v>
+        <v>56783</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7814,6 +7814,5375 @@
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>132059915</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>557255</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6710412</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>132059903</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>557183</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6710096</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>132059917</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>557303</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6710369</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>132059913</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>557094</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6710335</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>132059846</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91841</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>557268</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6710324</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>132059914</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>556941</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6710405</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>132059845</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91841</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>557066</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6710417</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>132059909</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>557110</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6710241</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>132059911</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>557115</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6710327</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>132059908</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>557176</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6710298</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>132059934</v>
+      </c>
+      <c r="B75" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>557044</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6710462</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>132059924</v>
+      </c>
+      <c r="B76" t="n">
+        <v>93129</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>557139</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6710146</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>132059884</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99047</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>557378</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6710276</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>132059920</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>557294</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6710338</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>132059918</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>557304</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6710354</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>132059881</v>
+      </c>
+      <c r="B80" t="n">
+        <v>97912</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>556939</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6710405</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>132059900</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>557283</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6710151</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>132059858</v>
+      </c>
+      <c r="B82" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>557066</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6710417</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>132059912</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>557108</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6710330</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>132059937</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57907</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>557086</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6710307</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>132059887</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99047</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>556973</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6710417</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>5 m från kallkälla</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>132059862</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57904</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>557268</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6710406</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>132059841</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91841</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>557246</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6710104</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>132059907</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>557205</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6710189</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>132059931</v>
+      </c>
+      <c r="B89" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>557086</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6710307</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>132059922</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57907</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>556923</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6710425</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>132059916</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>557268</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6710406</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>132059902</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>557178</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6710089</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>132059837</v>
+      </c>
+      <c r="B93" t="n">
+        <v>91804</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>556964</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6710397</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>132059885</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99047</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>557308</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6710165</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>132059928</v>
+      </c>
+      <c r="B95" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>557196</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6710215</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>132059936</v>
+      </c>
+      <c r="B96" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>557271</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6710331</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>132059886</v>
+      </c>
+      <c r="B97" t="n">
+        <v>99047</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>557312</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6710224</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>132059901</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>557218</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6710093</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>132059842</v>
+      </c>
+      <c r="B99" t="n">
+        <v>91841</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>557050</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6710330</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>132059865</v>
+      </c>
+      <c r="B100" t="n">
+        <v>92301</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>557190</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6710236</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>132059904</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>557202</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6710100</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>132059921</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>557288</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6710334</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>132059866</v>
+      </c>
+      <c r="B103" t="n">
+        <v>92301</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>557001</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6710392</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>132059840</v>
+      </c>
+      <c r="B104" t="n">
+        <v>91841</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>557352</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6710228</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>132059929</v>
+      </c>
+      <c r="B105" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>557206</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6710235</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>132059919</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>557299</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6710339</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>132059899</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>557291</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6710161</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>132059935</v>
+      </c>
+      <c r="B108" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>557267</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6710406</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>132059888</v>
+      </c>
+      <c r="B109" t="n">
+        <v>99047</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>557286</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6710159</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>132059854</v>
+      </c>
+      <c r="B110" t="n">
+        <v>57095</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>557049</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6710317</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>132059906</v>
+      </c>
+      <c r="B111" t="n">
+        <v>79269</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>557164</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6710175</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>132059843</v>
+      </c>
+      <c r="B112" t="n">
+        <v>91841</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>557007</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6710401</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>132059932</v>
+      </c>
+      <c r="B113" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Högåsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>556934</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6710433</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -7816,7 +7816,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132059915</v>
+        <v>132059903</v>
       </c>
       <c r="B65" t="n">
         <v>79269</v>
@@ -7851,10 +7851,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557255</v>
+        <v>557183</v>
       </c>
       <c r="R65" t="n">
-        <v>6710412</v>
+        <v>6710096</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7923,7 +7923,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132059903</v>
+        <v>132059915</v>
       </c>
       <c r="B66" t="n">
         <v>79269</v>
@@ -7958,10 +7958,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557183</v>
+        <v>557255</v>
       </c>
       <c r="R66" t="n">
-        <v>6710096</v>
+        <v>6710412</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8030,7 +8030,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132059917</v>
+        <v>132059913</v>
       </c>
       <c r="B67" t="n">
         <v>79269</v>
@@ -8065,10 +8065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557303</v>
+        <v>557094</v>
       </c>
       <c r="R67" t="n">
-        <v>6710369</v>
+        <v>6710335</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8137,7 +8137,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132059913</v>
+        <v>132059917</v>
       </c>
       <c r="B68" t="n">
         <v>79269</v>
@@ -8172,10 +8172,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>557094</v>
+        <v>557303</v>
       </c>
       <c r="R68" t="n">
-        <v>6710335</v>
+        <v>6710369</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8351,10 +8351,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132059914</v>
+        <v>132059845</v>
       </c>
       <c r="B70" t="n">
-        <v>79269</v>
+        <v>91841</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8362,21 +8362,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556941</v>
+        <v>557066</v>
       </c>
       <c r="R70" t="n">
-        <v>6710405</v>
+        <v>6710417</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8458,10 +8458,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132059845</v>
+        <v>132059908</v>
       </c>
       <c r="B71" t="n">
-        <v>91841</v>
+        <v>79269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8469,21 +8469,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>557066</v>
+        <v>557176</v>
       </c>
       <c r="R71" t="n">
-        <v>6710417</v>
+        <v>6710298</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8672,7 +8672,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132059911</v>
+        <v>132059914</v>
       </c>
       <c r="B73" t="n">
         <v>79269</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>557115</v>
+        <v>556941</v>
       </c>
       <c r="R73" t="n">
-        <v>6710327</v>
+        <v>6710405</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8779,7 +8779,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132059908</v>
+        <v>132059911</v>
       </c>
       <c r="B74" t="n">
         <v>79269</v>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>557176</v>
+        <v>557115</v>
       </c>
       <c r="R74" t="n">
-        <v>6710298</v>
+        <v>6710327</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8886,50 +8886,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132059934</v>
+        <v>132059920</v>
       </c>
       <c r="B75" t="n">
-        <v>5179</v>
+        <v>79269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557044</v>
+        <v>557294</v>
       </c>
       <c r="R75" t="n">
-        <v>6710462</v>
+        <v>6710338</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8961,7 +8956,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8971,7 +8966,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9105,42 +9100,38 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132059884</v>
+        <v>132059934</v>
       </c>
       <c r="B77" t="n">
-        <v>99047</v>
+        <v>5179</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9149,10 +9140,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557378</v>
+        <v>557044</v>
       </c>
       <c r="R77" t="n">
-        <v>6710276</v>
+        <v>6710462</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9184,7 +9175,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9194,7 +9185,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9221,45 +9212,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132059920</v>
+        <v>132059884</v>
       </c>
       <c r="B78" t="n">
-        <v>79269</v>
+        <v>99047</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>557294</v>
+        <v>557378</v>
       </c>
       <c r="R78" t="n">
-        <v>6710338</v>
+        <v>6710276</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9328,32 +9328,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132059918</v>
+        <v>132059881</v>
       </c>
       <c r="B79" t="n">
-        <v>79269</v>
+        <v>97912</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>557304</v>
+        <v>556939</v>
       </c>
       <c r="R79" t="n">
-        <v>6710354</v>
+        <v>6710405</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9435,32 +9435,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132059881</v>
+        <v>132059918</v>
       </c>
       <c r="B80" t="n">
-        <v>97912</v>
+        <v>79269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>556939</v>
+        <v>557304</v>
       </c>
       <c r="R80" t="n">
-        <v>6710405</v>
+        <v>6710354</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9761,45 +9761,54 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132059912</v>
+        <v>132059887</v>
       </c>
       <c r="B83" t="n">
-        <v>79269</v>
+        <v>99047</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>557108</v>
+        <v>556973</v>
       </c>
       <c r="R83" t="n">
-        <v>6710330</v>
+        <v>6710417</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9831,7 +9840,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9841,7 +9850,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>5 m från kallkälla</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9980,54 +9994,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132059887</v>
+        <v>132059912</v>
       </c>
       <c r="B85" t="n">
-        <v>99047</v>
+        <v>79269</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>556973</v>
+        <v>557108</v>
       </c>
       <c r="R85" t="n">
-        <v>6710417</v>
+        <v>6710330</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10059,7 +10064,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10069,12 +10074,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>5 m från kallkälla</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10101,10 +10101,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132059862</v>
+        <v>132059841</v>
       </c>
       <c r="B86" t="n">
-        <v>57904</v>
+        <v>91841</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10112,39 +10112,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>557268</v>
+        <v>557246</v>
       </c>
       <c r="R86" t="n">
-        <v>6710406</v>
+        <v>6710104</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10176,7 +10171,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10186,7 +10181,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10213,10 +10208,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132059841</v>
+        <v>132059862</v>
       </c>
       <c r="B87" t="n">
-        <v>91841</v>
+        <v>57904</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10224,34 +10219,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>557246</v>
+        <v>557268</v>
       </c>
       <c r="R87" t="n">
-        <v>6710104</v>
+        <v>6710406</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10651,32 +10651,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132059916</v>
+        <v>132059837</v>
       </c>
       <c r="B91" t="n">
-        <v>79269</v>
+        <v>91804</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10686,10 +10686,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>557268</v>
+        <v>556964</v>
       </c>
       <c r="R91" t="n">
-        <v>6710406</v>
+        <v>6710397</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10758,7 +10758,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132059902</v>
+        <v>132059916</v>
       </c>
       <c r="B92" t="n">
         <v>79269</v>
@@ -10793,10 +10793,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>557178</v>
+        <v>557268</v>
       </c>
       <c r="R92" t="n">
-        <v>6710089</v>
+        <v>6710406</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10865,45 +10865,54 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132059837</v>
+        <v>132059885</v>
       </c>
       <c r="B93" t="n">
-        <v>91804</v>
+        <v>99047</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>556964</v>
+        <v>557308</v>
       </c>
       <c r="R93" t="n">
-        <v>6710397</v>
+        <v>6710165</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10935,7 +10944,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10945,7 +10954,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10972,54 +10981,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132059885</v>
+        <v>132059902</v>
       </c>
       <c r="B94" t="n">
-        <v>99047</v>
+        <v>79269</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>557308</v>
+        <v>557178</v>
       </c>
       <c r="R94" t="n">
-        <v>6710165</v>
+        <v>6710089</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11088,7 +11088,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132059928</v>
+        <v>132059936</v>
       </c>
       <c r="B95" t="n">
         <v>5179</v>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>557196</v>
+        <v>557271</v>
       </c>
       <c r="R95" t="n">
-        <v>6710215</v>
+        <v>6710331</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11200,7 +11200,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132059936</v>
+        <v>132059928</v>
       </c>
       <c r="B96" t="n">
         <v>5179</v>
@@ -11240,10 +11240,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>557271</v>
+        <v>557196</v>
       </c>
       <c r="R96" t="n">
-        <v>6710331</v>
+        <v>6710215</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11312,54 +11312,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132059886</v>
+        <v>132059842</v>
       </c>
       <c r="B97" t="n">
-        <v>99047</v>
+        <v>91841</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>557312</v>
+        <v>557050</v>
       </c>
       <c r="R97" t="n">
-        <v>6710224</v>
+        <v>6710330</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11391,7 +11382,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11401,7 +11392,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11428,32 +11419,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132059901</v>
+        <v>132059865</v>
       </c>
       <c r="B98" t="n">
-        <v>79269</v>
+        <v>92301</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11463,10 +11454,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>557218</v>
+        <v>557190</v>
       </c>
       <c r="R98" t="n">
-        <v>6710093</v>
+        <v>6710236</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11498,7 +11489,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11508,7 +11499,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11517,6 +11508,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11535,45 +11527,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132059842</v>
+        <v>132059886</v>
       </c>
       <c r="B99" t="n">
-        <v>91841</v>
+        <v>99047</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>557050</v>
+        <v>557312</v>
       </c>
       <c r="R99" t="n">
-        <v>6710330</v>
+        <v>6710224</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11605,7 +11606,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11615,7 +11616,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11642,32 +11643,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132059865</v>
+        <v>132059901</v>
       </c>
       <c r="B100" t="n">
-        <v>92301</v>
+        <v>79269</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11677,10 +11678,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>557190</v>
+        <v>557218</v>
       </c>
       <c r="R100" t="n">
-        <v>6710236</v>
+        <v>6710093</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11712,7 +11713,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11722,7 +11723,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11731,7 +11732,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -12179,7 +12179,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132059929</v>
+        <v>132059935</v>
       </c>
       <c r="B105" t="n">
         <v>5179</v>
@@ -12219,10 +12219,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>557206</v>
+        <v>557267</v>
       </c>
       <c r="R105" t="n">
-        <v>6710235</v>
+        <v>6710406</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12291,7 +12291,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132059919</v>
+        <v>132059899</v>
       </c>
       <c r="B106" t="n">
         <v>79269</v>
@@ -12326,10 +12326,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>557299</v>
+        <v>557291</v>
       </c>
       <c r="R106" t="n">
-        <v>6710339</v>
+        <v>6710161</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12361,7 +12361,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12398,45 +12398,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132059899</v>
+        <v>132059888</v>
       </c>
       <c r="B107" t="n">
-        <v>79269</v>
+        <v>99047</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>557291</v>
+        <v>557286</v>
       </c>
       <c r="R107" t="n">
-        <v>6710161</v>
+        <v>6710159</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12505,50 +12514,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132059935</v>
+        <v>132059919</v>
       </c>
       <c r="B108" t="n">
-        <v>5179</v>
+        <v>79269</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>557267</v>
+        <v>557299</v>
       </c>
       <c r="R108" t="n">
-        <v>6710406</v>
+        <v>6710339</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12580,7 +12584,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12590,7 +12594,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12617,42 +12621,38 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132059888</v>
+        <v>132059929</v>
       </c>
       <c r="B109" t="n">
-        <v>99047</v>
+        <v>5179</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -12661,10 +12661,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>557286</v>
+        <v>557206</v>
       </c>
       <c r="R109" t="n">
-        <v>6710159</v>
+        <v>6710235</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -7819,7 +7819,7 @@
         <v>132059903</v>
       </c>
       <c r="B65" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>132059915</v>
       </c>
       <c r="B66" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>132059913</v>
       </c>
       <c r="B67" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>132059917</v>
       </c>
       <c r="B68" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>132059846</v>
       </c>
       <c r="B69" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8351,10 +8351,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132059845</v>
+        <v>132059909</v>
       </c>
       <c r="B70" t="n">
-        <v>91841</v>
+        <v>79274</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8362,21 +8362,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>557066</v>
+        <v>557110</v>
       </c>
       <c r="R70" t="n">
-        <v>6710417</v>
+        <v>6710241</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8458,10 +8458,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132059908</v>
+        <v>132059914</v>
       </c>
       <c r="B71" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>557176</v>
+        <v>556941</v>
       </c>
       <c r="R71" t="n">
-        <v>6710298</v>
+        <v>6710405</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8565,10 +8565,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132059909</v>
+        <v>132059908</v>
       </c>
       <c r="B72" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>557110</v>
+        <v>557176</v>
       </c>
       <c r="R72" t="n">
-        <v>6710241</v>
+        <v>6710298</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8672,10 +8672,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132059914</v>
+        <v>132059911</v>
       </c>
       <c r="B73" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>556941</v>
+        <v>557115</v>
       </c>
       <c r="R73" t="n">
-        <v>6710405</v>
+        <v>6710327</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132059911</v>
+        <v>132059845</v>
       </c>
       <c r="B74" t="n">
-        <v>79269</v>
+        <v>91846</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8790,21 +8790,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>557115</v>
+        <v>557066</v>
       </c>
       <c r="R74" t="n">
-        <v>6710327</v>
+        <v>6710417</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8889,7 +8889,7 @@
         <v>132059920</v>
       </c>
       <c r="B75" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>132059924</v>
       </c>
       <c r="B76" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9100,38 +9100,42 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132059934</v>
+        <v>132059884</v>
       </c>
       <c r="B77" t="n">
-        <v>5179</v>
+        <v>99052</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9140,10 +9144,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557044</v>
+        <v>557378</v>
       </c>
       <c r="R77" t="n">
-        <v>6710462</v>
+        <v>6710276</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9175,7 +9179,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9185,7 +9189,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9212,42 +9216,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132059884</v>
+        <v>132059934</v>
       </c>
       <c r="B78" t="n">
-        <v>99047</v>
+        <v>5179</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>557378</v>
+        <v>557044</v>
       </c>
       <c r="R78" t="n">
-        <v>6710276</v>
+        <v>6710462</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9331,7 +9331,7 @@
         <v>132059881</v>
       </c>
       <c r="B79" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>132059918</v>
       </c>
       <c r="B80" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>132059900</v>
       </c>
       <c r="B81" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9649,38 +9649,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132059858</v>
+        <v>132059937</v>
       </c>
       <c r="B82" t="n">
-        <v>4775</v>
+        <v>57912</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9689,10 +9689,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>557066</v>
+        <v>557086</v>
       </c>
       <c r="R82" t="n">
-        <v>6710417</v>
+        <v>6710307</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9734,14 +9734,14 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG82" t="b">
         <v>0</v>
@@ -9761,42 +9761,38 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132059887</v>
+        <v>132059858</v>
       </c>
       <c r="B83" t="n">
-        <v>99047</v>
+        <v>4775</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9805,7 +9801,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>556973</v>
+        <v>557066</v>
       </c>
       <c r="R83" t="n">
         <v>6710417</v>
@@ -9840,7 +9836,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9850,12 +9846,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>5 m från kallkälla</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9882,10 +9873,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132059937</v>
+        <v>132059912</v>
       </c>
       <c r="B84" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9893,39 +9884,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>557086</v>
+        <v>557108</v>
       </c>
       <c r="R84" t="n">
-        <v>6710307</v>
+        <v>6710330</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9957,7 +9943,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9967,14 +9953,14 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="b">
         <v>0</v>
@@ -9994,45 +9980,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132059912</v>
+        <v>132059887</v>
       </c>
       <c r="B85" t="n">
-        <v>79269</v>
+        <v>99052</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>557108</v>
+        <v>556973</v>
       </c>
       <c r="R85" t="n">
-        <v>6710330</v>
+        <v>6710417</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10064,7 +10059,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10074,7 +10069,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>5 m från kallkälla</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10104,7 +10104,7 @@
         <v>132059841</v>
       </c>
       <c r="B86" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>132059862</v>
       </c>
       <c r="B87" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>132059907</v>
       </c>
       <c r="B88" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10427,38 +10427,38 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132059931</v>
+        <v>132059922</v>
       </c>
       <c r="B89" t="n">
-        <v>5179</v>
+        <v>57912</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10467,10 +10467,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>557086</v>
+        <v>556923</v>
       </c>
       <c r="R89" t="n">
-        <v>6710307</v>
+        <v>6710425</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10512,14 +10512,14 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
@@ -10539,38 +10539,38 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132059922</v>
+        <v>132059931</v>
       </c>
       <c r="B90" t="n">
-        <v>57907</v>
+        <v>5179</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10579,10 +10579,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>556923</v>
+        <v>557086</v>
       </c>
       <c r="R90" t="n">
-        <v>6710425</v>
+        <v>6710307</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10624,14 +10624,14 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="b">
         <v>0</v>
@@ -10651,32 +10651,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132059837</v>
+        <v>132059916</v>
       </c>
       <c r="B91" t="n">
-        <v>91804</v>
+        <v>79274</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10686,10 +10686,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>556964</v>
+        <v>557268</v>
       </c>
       <c r="R91" t="n">
-        <v>6710397</v>
+        <v>6710406</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10758,10 +10758,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132059916</v>
+        <v>132059902</v>
       </c>
       <c r="B92" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10793,10 +10793,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>557268</v>
+        <v>557178</v>
       </c>
       <c r="R92" t="n">
-        <v>6710406</v>
+        <v>6710089</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10865,54 +10865,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132059885</v>
+        <v>132059837</v>
       </c>
       <c r="B93" t="n">
-        <v>99047</v>
+        <v>91809</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>557308</v>
+        <v>556964</v>
       </c>
       <c r="R93" t="n">
-        <v>6710165</v>
+        <v>6710397</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10944,7 +10935,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10954,7 +10945,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10981,45 +10972,54 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132059902</v>
+        <v>132059885</v>
       </c>
       <c r="B94" t="n">
-        <v>79269</v>
+        <v>99052</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>557178</v>
+        <v>557308</v>
       </c>
       <c r="R94" t="n">
-        <v>6710089</v>
+        <v>6710165</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11312,10 +11312,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132059842</v>
+        <v>132059901</v>
       </c>
       <c r="B97" t="n">
-        <v>91841</v>
+        <v>79274</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11323,21 +11323,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11347,10 +11347,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>557050</v>
+        <v>557218</v>
       </c>
       <c r="R97" t="n">
-        <v>6710330</v>
+        <v>6710093</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11419,32 +11419,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132059865</v>
+        <v>132059842</v>
       </c>
       <c r="B98" t="n">
-        <v>92301</v>
+        <v>91846</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11454,10 +11454,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>557190</v>
+        <v>557050</v>
       </c>
       <c r="R98" t="n">
-        <v>6710236</v>
+        <v>6710330</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11508,7 +11508,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11527,10 +11526,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132059886</v>
+        <v>132059865</v>
       </c>
       <c r="B99" t="n">
-        <v>99047</v>
+        <v>92306</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11538,43 +11537,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>557312</v>
+        <v>557190</v>
       </c>
       <c r="R99" t="n">
-        <v>6710224</v>
+        <v>6710236</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11606,7 +11596,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11616,7 +11606,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11625,6 +11615,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11643,45 +11634,54 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132059901</v>
+        <v>132059886</v>
       </c>
       <c r="B100" t="n">
-        <v>79269</v>
+        <v>99052</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>557218</v>
+        <v>557312</v>
       </c>
       <c r="R100" t="n">
-        <v>6710093</v>
+        <v>6710224</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11753,7 +11753,7 @@
         <v>132059904</v>
       </c>
       <c r="B101" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>132059921</v>
       </c>
       <c r="B102" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>132059866</v>
       </c>
       <c r="B103" t="n">
-        <v>92301</v>
+        <v>92306</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>132059840</v>
       </c>
       <c r="B104" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12291,45 +12291,50 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132059899</v>
+        <v>132059929</v>
       </c>
       <c r="B106" t="n">
-        <v>79269</v>
+        <v>5179</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>557291</v>
+        <v>557206</v>
       </c>
       <c r="R106" t="n">
-        <v>6710161</v>
+        <v>6710235</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12361,7 +12366,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12371,7 +12376,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12398,54 +12403,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132059888</v>
+        <v>132059899</v>
       </c>
       <c r="B107" t="n">
-        <v>99047</v>
+        <v>79274</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>557286</v>
+        <v>557291</v>
       </c>
       <c r="R107" t="n">
-        <v>6710159</v>
+        <v>6710161</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12517,7 +12513,7 @@
         <v>132059919</v>
       </c>
       <c r="B108" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12621,38 +12617,42 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132059929</v>
+        <v>132059888</v>
       </c>
       <c r="B109" t="n">
-        <v>5179</v>
+        <v>99052</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -12661,10 +12661,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>557206</v>
+        <v>557286</v>
       </c>
       <c r="R109" t="n">
-        <v>6710235</v>
+        <v>6710159</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12733,64 +12733,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132059854</v>
+        <v>132059906</v>
       </c>
       <c r="B110" t="n">
-        <v>57095</v>
+        <v>79274</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>557049</v>
+        <v>557164</v>
       </c>
       <c r="R110" t="n">
-        <v>6710317</v>
+        <v>6710175</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12822,7 +12803,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12832,7 +12813,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12859,45 +12840,64 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132059906</v>
+        <v>132059854</v>
       </c>
       <c r="B111" t="n">
-        <v>79269</v>
+        <v>57100</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>557164</v>
+        <v>557049</v>
       </c>
       <c r="R111" t="n">
-        <v>6710175</v>
+        <v>6710317</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12969,7 +12969,7 @@
         <v>132059843</v>
       </c>
       <c r="B112" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -9649,10 +9649,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132059937</v>
+        <v>132059912</v>
       </c>
       <c r="B82" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9660,39 +9660,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>557086</v>
+        <v>557108</v>
       </c>
       <c r="R82" t="n">
-        <v>6710307</v>
+        <v>6710330</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9724,7 +9719,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9734,14 +9729,14 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="b">
         <v>0</v>
@@ -9761,38 +9756,42 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132059858</v>
+        <v>132059887</v>
       </c>
       <c r="B83" t="n">
-        <v>4775</v>
+        <v>99052</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9801,7 +9800,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>557066</v>
+        <v>556973</v>
       </c>
       <c r="R83" t="n">
         <v>6710417</v>
@@ -9836,7 +9835,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9846,7 +9845,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>5 m från kallkälla</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9873,10 +9877,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132059912</v>
+        <v>132059937</v>
       </c>
       <c r="B84" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9884,34 +9888,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>557108</v>
+        <v>557086</v>
       </c>
       <c r="R84" t="n">
-        <v>6710330</v>
+        <v>6710307</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9943,7 +9952,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9953,14 +9962,14 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG84" t="b">
         <v>0</v>
@@ -9980,42 +9989,38 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132059887</v>
+        <v>132059858</v>
       </c>
       <c r="B85" t="n">
-        <v>99052</v>
+        <v>4775</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10024,7 +10029,7 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>556973</v>
+        <v>557066</v>
       </c>
       <c r="R85" t="n">
         <v>6710417</v>
@@ -10059,7 +10064,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10069,12 +10074,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>5 m från kallkälla</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10427,38 +10427,38 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132059922</v>
+        <v>132059931</v>
       </c>
       <c r="B89" t="n">
-        <v>57912</v>
+        <v>5179</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10467,10 +10467,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>556923</v>
+        <v>557086</v>
       </c>
       <c r="R89" t="n">
-        <v>6710425</v>
+        <v>6710307</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10512,14 +10512,14 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
@@ -10539,38 +10539,38 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132059931</v>
+        <v>132059922</v>
       </c>
       <c r="B90" t="n">
-        <v>5179</v>
+        <v>57912</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10579,10 +10579,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>557086</v>
+        <v>556923</v>
       </c>
       <c r="R90" t="n">
-        <v>6710307</v>
+        <v>6710425</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10624,14 +10624,14 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG90" t="b">
         <v>0</v>
@@ -10651,7 +10651,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132059916</v>
+        <v>132059902</v>
       </c>
       <c r="B91" t="n">
         <v>79274</v>
@@ -10686,10 +10686,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>557268</v>
+        <v>557178</v>
       </c>
       <c r="R91" t="n">
-        <v>6710406</v>
+        <v>6710089</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10758,7 +10758,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132059902</v>
+        <v>132059916</v>
       </c>
       <c r="B92" t="n">
         <v>79274</v>
@@ -10793,10 +10793,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>557178</v>
+        <v>557268</v>
       </c>
       <c r="R92" t="n">
-        <v>6710089</v>
+        <v>6710406</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12179,50 +12179,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132059935</v>
+        <v>132059899</v>
       </c>
       <c r="B105" t="n">
-        <v>5179</v>
+        <v>79274</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>557267</v>
+        <v>557291</v>
       </c>
       <c r="R105" t="n">
-        <v>6710406</v>
+        <v>6710161</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12254,7 +12249,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12264,7 +12259,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12403,45 +12398,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132059899</v>
+        <v>132059888</v>
       </c>
       <c r="B107" t="n">
-        <v>79274</v>
+        <v>99052</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>557291</v>
+        <v>557286</v>
       </c>
       <c r="R107" t="n">
-        <v>6710161</v>
+        <v>6710159</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12617,42 +12621,38 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132059888</v>
+        <v>132059935</v>
       </c>
       <c r="B109" t="n">
-        <v>99052</v>
+        <v>5179</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -12661,10 +12661,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>557286</v>
+        <v>557267</v>
       </c>
       <c r="R109" t="n">
-        <v>6710159</v>
+        <v>6710406</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -7819,7 +7819,7 @@
         <v>132059903</v>
       </c>
       <c r="B65" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>132059915</v>
       </c>
       <c r="B66" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>132059913</v>
       </c>
       <c r="B67" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>132059917</v>
       </c>
       <c r="B68" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>132059846</v>
       </c>
       <c r="B69" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>132059845</v>
       </c>
       <c r="B70" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>132059908</v>
       </c>
       <c r="B71" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>132059909</v>
       </c>
       <c r="B72" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>132059914</v>
       </c>
       <c r="B73" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>132059911</v>
       </c>
       <c r="B74" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8886,50 +8886,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132059934</v>
+        <v>132059920</v>
       </c>
       <c r="B75" t="n">
-        <v>5179</v>
+        <v>79317</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557044</v>
+        <v>557294</v>
       </c>
       <c r="R75" t="n">
-        <v>6710462</v>
+        <v>6710338</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8961,7 +8956,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8971,7 +8966,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8998,54 +8993,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132059884</v>
+        <v>132059924</v>
       </c>
       <c r="B76" t="n">
-        <v>99095</v>
+        <v>93180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>557378</v>
+        <v>557139</v>
       </c>
       <c r="R76" t="n">
-        <v>6710276</v>
+        <v>6710146</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9077,7 +9063,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9087,7 +9073,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9114,45 +9100,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132059920</v>
+        <v>132059884</v>
       </c>
       <c r="B77" t="n">
-        <v>79315</v>
+        <v>99098</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557294</v>
+        <v>557378</v>
       </c>
       <c r="R77" t="n">
-        <v>6710338</v>
+        <v>6710276</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9184,7 +9179,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9194,7 +9189,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9221,10 +9216,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132059924</v>
+        <v>132059934</v>
       </c>
       <c r="B78" t="n">
-        <v>93177</v>
+        <v>5179</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9232,34 +9227,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>557139</v>
+        <v>557044</v>
       </c>
       <c r="R78" t="n">
-        <v>6710146</v>
+        <v>6710462</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9331,7 +9331,7 @@
         <v>132059918</v>
       </c>
       <c r="B79" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>132059900</v>
       </c>
       <c r="B80" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>132059881</v>
       </c>
       <c r="B81" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9649,10 +9649,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132059937</v>
+        <v>132059912</v>
       </c>
       <c r="B82" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9660,39 +9660,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>557086</v>
+        <v>557108</v>
       </c>
       <c r="R82" t="n">
-        <v>6710307</v>
+        <v>6710330</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9724,7 +9719,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9734,14 +9729,14 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="b">
         <v>0</v>
@@ -9761,10 +9756,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132059912</v>
+        <v>132059937</v>
       </c>
       <c r="B83" t="n">
-        <v>79315</v>
+        <v>57948</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9772,34 +9767,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>557108</v>
+        <v>557086</v>
       </c>
       <c r="R83" t="n">
-        <v>6710330</v>
+        <v>6710307</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9841,14 +9841,14 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG83" t="b">
         <v>0</v>
@@ -9983,7 +9983,7 @@
         <v>132059887</v>
       </c>
       <c r="B85" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>132059841</v>
       </c>
       <c r="B86" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>132059907</v>
       </c>
       <c r="B88" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10651,45 +10651,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132059902</v>
+        <v>132059885</v>
       </c>
       <c r="B91" t="n">
-        <v>79315</v>
+        <v>99098</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>557178</v>
+        <v>557308</v>
       </c>
       <c r="R91" t="n">
-        <v>6710089</v>
+        <v>6710165</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10721,7 +10730,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10731,7 +10740,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10758,10 +10767,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132059916</v>
+        <v>132059902</v>
       </c>
       <c r="B92" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10793,10 +10802,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>557268</v>
+        <v>557178</v>
       </c>
       <c r="R92" t="n">
-        <v>6710406</v>
+        <v>6710089</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10828,7 +10837,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10838,7 +10847,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10865,32 +10874,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132059837</v>
+        <v>132059916</v>
       </c>
       <c r="B93" t="n">
-        <v>91852</v>
+        <v>79317</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10900,10 +10909,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>556964</v>
+        <v>557268</v>
       </c>
       <c r="R93" t="n">
-        <v>6710397</v>
+        <v>6710406</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10935,7 +10944,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10945,7 +10954,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10972,54 +10981,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132059885</v>
+        <v>132059837</v>
       </c>
       <c r="B94" t="n">
-        <v>99095</v>
+        <v>91855</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>557308</v>
+        <v>556964</v>
       </c>
       <c r="R94" t="n">
-        <v>6710165</v>
+        <v>6710397</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11088,7 +11088,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132059936</v>
+        <v>132059928</v>
       </c>
       <c r="B95" t="n">
         <v>5179</v>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>557271</v>
+        <v>557196</v>
       </c>
       <c r="R95" t="n">
-        <v>6710331</v>
+        <v>6710215</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11200,7 +11200,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132059928</v>
+        <v>132059936</v>
       </c>
       <c r="B96" t="n">
         <v>5179</v>
@@ -11240,10 +11240,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>557196</v>
+        <v>557271</v>
       </c>
       <c r="R96" t="n">
-        <v>6710215</v>
+        <v>6710331</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11312,54 +11312,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132059886</v>
+        <v>132059901</v>
       </c>
       <c r="B97" t="n">
-        <v>99095</v>
+        <v>79317</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>557312</v>
+        <v>557218</v>
       </c>
       <c r="R97" t="n">
-        <v>6710224</v>
+        <v>6710093</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11391,7 +11382,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11401,7 +11392,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11431,7 +11422,7 @@
         <v>132059842</v>
       </c>
       <c r="B98" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11538,7 +11529,7 @@
         <v>132059865</v>
       </c>
       <c r="B99" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11643,45 +11634,54 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132059901</v>
+        <v>132059886</v>
       </c>
       <c r="B100" t="n">
-        <v>79315</v>
+        <v>99098</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>557218</v>
+        <v>557312</v>
       </c>
       <c r="R100" t="n">
-        <v>6710093</v>
+        <v>6710224</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11750,32 +11750,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132059866</v>
+        <v>132059904</v>
       </c>
       <c r="B101" t="n">
-        <v>92349</v>
+        <v>79317</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11785,10 +11785,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>557001</v>
+        <v>557202</v>
       </c>
       <c r="R101" t="n">
-        <v>6710392</v>
+        <v>6710100</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11839,7 +11839,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11858,10 +11857,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132059904</v>
+        <v>132059921</v>
       </c>
       <c r="B102" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11893,10 +11892,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>557202</v>
+        <v>557288</v>
       </c>
       <c r="R102" t="n">
-        <v>6710100</v>
+        <v>6710334</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11928,7 +11927,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11938,7 +11937,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11965,32 +11964,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132059921</v>
+        <v>132059866</v>
       </c>
       <c r="B103" t="n">
-        <v>79315</v>
+        <v>92352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12000,10 +11999,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>557288</v>
+        <v>557001</v>
       </c>
       <c r="R103" t="n">
-        <v>6710334</v>
+        <v>6710392</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12035,7 +12034,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12045,7 +12044,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12054,6 +12053,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -12075,7 +12075,7 @@
         <v>132059840</v>
       </c>
       <c r="B104" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>132059899</v>
       </c>
       <c r="B105" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>132059919</v>
       </c>
       <c r="B106" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>132059888</v>
       </c>
       <c r="B109" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>132059906</v>
       </c>
       <c r="B110" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>132059843</v>
       </c>
       <c r="B112" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -8351,10 +8351,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132059845</v>
+        <v>132059908</v>
       </c>
       <c r="B70" t="n">
-        <v>91892</v>
+        <v>79317</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8362,21 +8362,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>557066</v>
+        <v>557176</v>
       </c>
       <c r="R70" t="n">
-        <v>6710417</v>
+        <v>6710298</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8458,7 +8458,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132059908</v>
+        <v>132059909</v>
       </c>
       <c r="B71" t="n">
         <v>79317</v>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>557176</v>
+        <v>557110</v>
       </c>
       <c r="R71" t="n">
-        <v>6710298</v>
+        <v>6710241</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8565,7 +8565,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132059909</v>
+        <v>132059914</v>
       </c>
       <c r="B72" t="n">
         <v>79317</v>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>557110</v>
+        <v>556941</v>
       </c>
       <c r="R72" t="n">
-        <v>6710241</v>
+        <v>6710405</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8672,7 +8672,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132059914</v>
+        <v>132059911</v>
       </c>
       <c r="B73" t="n">
         <v>79317</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>556941</v>
+        <v>557115</v>
       </c>
       <c r="R73" t="n">
-        <v>6710405</v>
+        <v>6710327</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132059911</v>
+        <v>132059845</v>
       </c>
       <c r="B74" t="n">
-        <v>79317</v>
+        <v>91892</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8790,21 +8790,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>557115</v>
+        <v>557066</v>
       </c>
       <c r="R74" t="n">
-        <v>6710327</v>
+        <v>6710417</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9328,32 +9328,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132059918</v>
+        <v>132059881</v>
       </c>
       <c r="B79" t="n">
-        <v>79317</v>
+        <v>97963</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>557304</v>
+        <v>556939</v>
       </c>
       <c r="R79" t="n">
-        <v>6710354</v>
+        <v>6710405</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9435,7 +9435,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132059900</v>
+        <v>132059918</v>
       </c>
       <c r="B80" t="n">
         <v>79317</v>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>557283</v>
+        <v>557304</v>
       </c>
       <c r="R80" t="n">
-        <v>6710151</v>
+        <v>6710354</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9542,32 +9542,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132059881</v>
+        <v>132059900</v>
       </c>
       <c r="B81" t="n">
-        <v>97963</v>
+        <v>79317</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556939</v>
+        <v>557283</v>
       </c>
       <c r="R81" t="n">
-        <v>6710405</v>
+        <v>6710151</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10427,38 +10427,38 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132059931</v>
+        <v>132059922</v>
       </c>
       <c r="B89" t="n">
-        <v>5179</v>
+        <v>57948</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10467,10 +10467,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>557086</v>
+        <v>556923</v>
       </c>
       <c r="R89" t="n">
-        <v>6710307</v>
+        <v>6710425</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10512,14 +10512,14 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
@@ -10539,38 +10539,38 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132059922</v>
+        <v>132059931</v>
       </c>
       <c r="B90" t="n">
-        <v>57948</v>
+        <v>5179</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10579,10 +10579,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>556923</v>
+        <v>557086</v>
       </c>
       <c r="R90" t="n">
-        <v>6710425</v>
+        <v>6710307</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10624,14 +10624,14 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="b">
         <v>0</v>
@@ -10651,54 +10651,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132059885</v>
+        <v>132059902</v>
       </c>
       <c r="B91" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>557308</v>
+        <v>557178</v>
       </c>
       <c r="R91" t="n">
-        <v>6710165</v>
+        <v>6710089</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10730,7 +10721,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10740,7 +10731,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10767,7 +10758,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132059902</v>
+        <v>132059916</v>
       </c>
       <c r="B92" t="n">
         <v>79317</v>
@@ -10802,10 +10793,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>557178</v>
+        <v>557268</v>
       </c>
       <c r="R92" t="n">
-        <v>6710089</v>
+        <v>6710406</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10837,7 +10828,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10847,7 +10838,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10874,32 +10865,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132059916</v>
+        <v>132059837</v>
       </c>
       <c r="B93" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10909,10 +10900,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>557268</v>
+        <v>556964</v>
       </c>
       <c r="R93" t="n">
-        <v>6710406</v>
+        <v>6710397</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10944,7 +10935,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10954,7 +10945,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10981,45 +10972,54 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132059837</v>
+        <v>132059885</v>
       </c>
       <c r="B94" t="n">
-        <v>91855</v>
+        <v>99098</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>556964</v>
+        <v>557308</v>
       </c>
       <c r="R94" t="n">
-        <v>6710397</v>
+        <v>6710165</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11312,10 +11312,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132059901</v>
+        <v>132059842</v>
       </c>
       <c r="B97" t="n">
-        <v>79317</v>
+        <v>91892</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11323,21 +11323,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11347,10 +11347,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>557218</v>
+        <v>557050</v>
       </c>
       <c r="R97" t="n">
-        <v>6710093</v>
+        <v>6710330</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11419,32 +11419,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132059842</v>
+        <v>132059865</v>
       </c>
       <c r="B98" t="n">
-        <v>91892</v>
+        <v>92352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11454,10 +11454,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>557050</v>
+        <v>557190</v>
       </c>
       <c r="R98" t="n">
-        <v>6710330</v>
+        <v>6710236</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11508,6 +11508,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11526,32 +11527,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132059865</v>
+        <v>132059901</v>
       </c>
       <c r="B99" t="n">
-        <v>92352</v>
+        <v>79317</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11561,10 +11562,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>557190</v>
+        <v>557218</v>
       </c>
       <c r="R99" t="n">
-        <v>6710236</v>
+        <v>6710093</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11596,7 +11597,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11606,7 +11607,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11615,7 +11616,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11750,32 +11750,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132059904</v>
+        <v>132059866</v>
       </c>
       <c r="B101" t="n">
-        <v>79317</v>
+        <v>92352</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11785,10 +11785,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>557202</v>
+        <v>557001</v>
       </c>
       <c r="R101" t="n">
-        <v>6710100</v>
+        <v>6710392</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11839,6 +11839,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11857,7 +11858,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132059921</v>
+        <v>132059904</v>
       </c>
       <c r="B102" t="n">
         <v>79317</v>
@@ -11892,10 +11893,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>557288</v>
+        <v>557202</v>
       </c>
       <c r="R102" t="n">
-        <v>6710334</v>
+        <v>6710100</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11927,7 +11928,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11937,7 +11938,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11964,32 +11965,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132059866</v>
+        <v>132059921</v>
       </c>
       <c r="B103" t="n">
-        <v>92352</v>
+        <v>79317</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11999,10 +12000,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>557001</v>
+        <v>557288</v>
       </c>
       <c r="R103" t="n">
-        <v>6710392</v>
+        <v>6710334</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12034,7 +12035,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12044,7 +12045,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12053,7 +12054,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -8886,45 +8886,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132059920</v>
+        <v>132059884</v>
       </c>
       <c r="B75" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557294</v>
+        <v>557378</v>
       </c>
       <c r="R75" t="n">
-        <v>6710338</v>
+        <v>6710276</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8956,7 +8965,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8966,7 +8975,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8993,10 +9002,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132059924</v>
+        <v>132059934</v>
       </c>
       <c r="B76" t="n">
-        <v>93180</v>
+        <v>5179</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9004,34 +9013,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>557139</v>
+        <v>557044</v>
       </c>
       <c r="R76" t="n">
-        <v>6710146</v>
+        <v>6710462</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9063,7 +9077,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9073,7 +9087,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9100,54 +9114,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132059884</v>
+        <v>132059920</v>
       </c>
       <c r="B77" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557378</v>
+        <v>557294</v>
       </c>
       <c r="R77" t="n">
-        <v>6710276</v>
+        <v>6710338</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9179,7 +9184,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9189,7 +9194,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9216,10 +9221,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132059934</v>
+        <v>132059924</v>
       </c>
       <c r="B78" t="n">
-        <v>5179</v>
+        <v>93180</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9227,39 +9232,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>557044</v>
+        <v>557139</v>
       </c>
       <c r="R78" t="n">
-        <v>6710462</v>
+        <v>6710146</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9328,32 +9328,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132059881</v>
+        <v>132059918</v>
       </c>
       <c r="B79" t="n">
-        <v>97963</v>
+        <v>79317</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>556939</v>
+        <v>557304</v>
       </c>
       <c r="R79" t="n">
-        <v>6710405</v>
+        <v>6710354</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9435,7 +9435,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132059918</v>
+        <v>132059900</v>
       </c>
       <c r="B80" t="n">
         <v>79317</v>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>557304</v>
+        <v>557283</v>
       </c>
       <c r="R80" t="n">
-        <v>6710354</v>
+        <v>6710151</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9542,32 +9542,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132059900</v>
+        <v>132059881</v>
       </c>
       <c r="B81" t="n">
-        <v>79317</v>
+        <v>97963</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>557283</v>
+        <v>556939</v>
       </c>
       <c r="R81" t="n">
-        <v>6710151</v>
+        <v>6710405</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10651,45 +10651,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132059902</v>
+        <v>132059885</v>
       </c>
       <c r="B91" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>557178</v>
+        <v>557308</v>
       </c>
       <c r="R91" t="n">
-        <v>6710089</v>
+        <v>6710165</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10721,7 +10730,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10731,7 +10740,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10758,7 +10767,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132059916</v>
+        <v>132059902</v>
       </c>
       <c r="B92" t="n">
         <v>79317</v>
@@ -10793,10 +10802,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>557268</v>
+        <v>557178</v>
       </c>
       <c r="R92" t="n">
-        <v>6710406</v>
+        <v>6710089</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10828,7 +10837,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10838,7 +10847,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10865,32 +10874,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132059837</v>
+        <v>132059916</v>
       </c>
       <c r="B93" t="n">
-        <v>91855</v>
+        <v>79317</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10900,10 +10909,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>556964</v>
+        <v>557268</v>
       </c>
       <c r="R93" t="n">
-        <v>6710397</v>
+        <v>6710406</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10935,7 +10944,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10945,7 +10954,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10972,54 +10981,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132059885</v>
+        <v>132059837</v>
       </c>
       <c r="B94" t="n">
-        <v>99098</v>
+        <v>91855</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>557308</v>
+        <v>556964</v>
       </c>
       <c r="R94" t="n">
-        <v>6710165</v>
+        <v>6710397</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11312,10 +11312,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132059842</v>
+        <v>132059901</v>
       </c>
       <c r="B97" t="n">
-        <v>91892</v>
+        <v>79317</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11323,21 +11323,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11347,10 +11347,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>557050</v>
+        <v>557218</v>
       </c>
       <c r="R97" t="n">
-        <v>6710330</v>
+        <v>6710093</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11419,32 +11419,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132059865</v>
+        <v>132059842</v>
       </c>
       <c r="B98" t="n">
-        <v>92352</v>
+        <v>91892</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11454,10 +11454,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>557190</v>
+        <v>557050</v>
       </c>
       <c r="R98" t="n">
-        <v>6710236</v>
+        <v>6710330</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11508,7 +11508,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11527,32 +11526,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132059901</v>
+        <v>132059865</v>
       </c>
       <c r="B99" t="n">
-        <v>79317</v>
+        <v>92352</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11562,10 +11561,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>557218</v>
+        <v>557190</v>
       </c>
       <c r="R99" t="n">
-        <v>6710093</v>
+        <v>6710236</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11597,7 +11596,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11607,7 +11606,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11616,6 +11615,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -8030,7 +8030,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132059913</v>
+        <v>132059917</v>
       </c>
       <c r="B67" t="n">
         <v>79317</v>
@@ -8065,10 +8065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557094</v>
+        <v>557303</v>
       </c>
       <c r="R67" t="n">
-        <v>6710335</v>
+        <v>6710369</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8137,7 +8137,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132059917</v>
+        <v>132059913</v>
       </c>
       <c r="B68" t="n">
         <v>79317</v>
@@ -8172,10 +8172,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>557303</v>
+        <v>557094</v>
       </c>
       <c r="R68" t="n">
-        <v>6710369</v>
+        <v>6710335</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8351,10 +8351,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132059908</v>
+        <v>132059845</v>
       </c>
       <c r="B70" t="n">
-        <v>79317</v>
+        <v>91892</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8362,21 +8362,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>557176</v>
+        <v>557066</v>
       </c>
       <c r="R70" t="n">
-        <v>6710298</v>
+        <v>6710417</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8458,7 +8458,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132059909</v>
+        <v>132059908</v>
       </c>
       <c r="B71" t="n">
         <v>79317</v>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>557110</v>
+        <v>557176</v>
       </c>
       <c r="R71" t="n">
-        <v>6710241</v>
+        <v>6710298</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8565,7 +8565,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132059914</v>
+        <v>132059909</v>
       </c>
       <c r="B72" t="n">
         <v>79317</v>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556941</v>
+        <v>557110</v>
       </c>
       <c r="R72" t="n">
-        <v>6710405</v>
+        <v>6710241</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8672,7 +8672,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132059911</v>
+        <v>132059914</v>
       </c>
       <c r="B73" t="n">
         <v>79317</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>557115</v>
+        <v>556941</v>
       </c>
       <c r="R73" t="n">
-        <v>6710327</v>
+        <v>6710405</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132059845</v>
+        <v>132059911</v>
       </c>
       <c r="B74" t="n">
-        <v>91892</v>
+        <v>79317</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8790,21 +8790,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>557066</v>
+        <v>557115</v>
       </c>
       <c r="R74" t="n">
-        <v>6710417</v>
+        <v>6710327</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8886,54 +8886,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132059884</v>
+        <v>132059920</v>
       </c>
       <c r="B75" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557378</v>
+        <v>557294</v>
       </c>
       <c r="R75" t="n">
-        <v>6710276</v>
+        <v>6710338</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8965,7 +8956,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8975,7 +8966,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9002,10 +8993,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132059934</v>
+        <v>132059924</v>
       </c>
       <c r="B76" t="n">
-        <v>5179</v>
+        <v>93180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9013,39 +9004,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>557044</v>
+        <v>557139</v>
       </c>
       <c r="R76" t="n">
-        <v>6710462</v>
+        <v>6710146</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9077,7 +9063,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9087,7 +9073,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9114,45 +9100,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132059920</v>
+        <v>132059934</v>
       </c>
       <c r="B77" t="n">
-        <v>79317</v>
+        <v>5179</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557294</v>
+        <v>557044</v>
       </c>
       <c r="R77" t="n">
-        <v>6710338</v>
+        <v>6710462</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9184,7 +9175,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9194,7 +9185,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9221,45 +9212,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132059924</v>
+        <v>132059884</v>
       </c>
       <c r="B78" t="n">
-        <v>93180</v>
+        <v>99098</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>557139</v>
+        <v>557378</v>
       </c>
       <c r="R78" t="n">
-        <v>6710146</v>
+        <v>6710276</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9649,45 +9649,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132059912</v>
+        <v>132059887</v>
       </c>
       <c r="B82" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>557108</v>
+        <v>556973</v>
       </c>
       <c r="R82" t="n">
-        <v>6710330</v>
+        <v>6710417</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9719,7 +9728,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9729,7 +9738,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>5 m från kallkälla</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9756,38 +9770,38 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132059937</v>
+        <v>132059858</v>
       </c>
       <c r="B83" t="n">
-        <v>57948</v>
+        <v>4775</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9796,10 +9810,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>557086</v>
+        <v>557066</v>
       </c>
       <c r="R83" t="n">
-        <v>6710307</v>
+        <v>6710417</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9831,7 +9845,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9841,14 +9855,14 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="b">
         <v>0</v>
@@ -9868,50 +9882,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132059858</v>
+        <v>132059912</v>
       </c>
       <c r="B84" t="n">
-        <v>4775</v>
+        <v>79317</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>557066</v>
+        <v>557108</v>
       </c>
       <c r="R84" t="n">
-        <v>6710417</v>
+        <v>6710330</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9943,7 +9952,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9953,7 +9962,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9980,42 +9989,38 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132059887</v>
+        <v>132059937</v>
       </c>
       <c r="B85" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10024,10 +10029,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>556973</v>
+        <v>557086</v>
       </c>
       <c r="R85" t="n">
-        <v>6710417</v>
+        <v>6710307</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10059,7 +10064,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10069,19 +10074,14 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>5 m från kallkälla</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG85" t="b">
         <v>0</v>
@@ -10651,54 +10651,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132059885</v>
+        <v>132059902</v>
       </c>
       <c r="B91" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>557308</v>
+        <v>557178</v>
       </c>
       <c r="R91" t="n">
-        <v>6710165</v>
+        <v>6710089</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10730,7 +10721,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10740,7 +10731,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10767,7 +10758,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132059902</v>
+        <v>132059916</v>
       </c>
       <c r="B92" t="n">
         <v>79317</v>
@@ -10802,10 +10793,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>557178</v>
+        <v>557268</v>
       </c>
       <c r="R92" t="n">
-        <v>6710089</v>
+        <v>6710406</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10837,7 +10828,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10847,7 +10838,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10874,32 +10865,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132059916</v>
+        <v>132059837</v>
       </c>
       <c r="B93" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10909,10 +10900,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>557268</v>
+        <v>556964</v>
       </c>
       <c r="R93" t="n">
-        <v>6710406</v>
+        <v>6710397</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10944,7 +10935,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10954,7 +10945,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10981,45 +10972,54 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132059837</v>
+        <v>132059885</v>
       </c>
       <c r="B94" t="n">
-        <v>91855</v>
+        <v>99098</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>556964</v>
+        <v>557308</v>
       </c>
       <c r="R94" t="n">
-        <v>6710397</v>
+        <v>6710165</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11088,7 +11088,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132059928</v>
+        <v>132059936</v>
       </c>
       <c r="B95" t="n">
         <v>5179</v>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>557196</v>
+        <v>557271</v>
       </c>
       <c r="R95" t="n">
-        <v>6710215</v>
+        <v>6710331</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11200,7 +11200,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132059936</v>
+        <v>132059928</v>
       </c>
       <c r="B96" t="n">
         <v>5179</v>
@@ -11240,10 +11240,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>557271</v>
+        <v>557196</v>
       </c>
       <c r="R96" t="n">
-        <v>6710331</v>
+        <v>6710215</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11312,10 +11312,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132059901</v>
+        <v>132059842</v>
       </c>
       <c r="B97" t="n">
-        <v>79317</v>
+        <v>91892</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11323,21 +11323,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11347,10 +11347,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>557218</v>
+        <v>557050</v>
       </c>
       <c r="R97" t="n">
-        <v>6710093</v>
+        <v>6710330</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11419,32 +11419,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132059842</v>
+        <v>132059865</v>
       </c>
       <c r="B98" t="n">
-        <v>91892</v>
+        <v>92352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11454,10 +11454,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>557050</v>
+        <v>557190</v>
       </c>
       <c r="R98" t="n">
-        <v>6710330</v>
+        <v>6710236</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11508,6 +11508,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11526,32 +11527,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132059865</v>
+        <v>132059901</v>
       </c>
       <c r="B99" t="n">
-        <v>92352</v>
+        <v>79317</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11561,10 +11562,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>557190</v>
+        <v>557218</v>
       </c>
       <c r="R99" t="n">
-        <v>6710236</v>
+        <v>6710093</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11596,7 +11597,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11606,7 +11607,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11615,7 +11616,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -12179,7 +12179,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132059899</v>
+        <v>132059919</v>
       </c>
       <c r="B105" t="n">
         <v>79317</v>
@@ -12214,10 +12214,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>557291</v>
+        <v>557299</v>
       </c>
       <c r="R105" t="n">
-        <v>6710161</v>
+        <v>6710339</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12286,7 +12286,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132059919</v>
+        <v>132059899</v>
       </c>
       <c r="B106" t="n">
         <v>79317</v>
@@ -12321,10 +12321,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>557299</v>
+        <v>557291</v>
       </c>
       <c r="R106" t="n">
-        <v>6710339</v>
+        <v>6710161</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD106" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -12286,45 +12286,50 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132059899</v>
+        <v>132059929</v>
       </c>
       <c r="B106" t="n">
-        <v>79317</v>
+        <v>5179</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>557291</v>
+        <v>557206</v>
       </c>
       <c r="R106" t="n">
-        <v>6710161</v>
+        <v>6710235</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12356,7 +12361,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12366,7 +12371,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12393,50 +12398,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132059935</v>
+        <v>132059899</v>
       </c>
       <c r="B107" t="n">
-        <v>5179</v>
+        <v>79317</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>557267</v>
+        <v>557291</v>
       </c>
       <c r="R107" t="n">
-        <v>6710406</v>
+        <v>6710161</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12505,7 +12505,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132059929</v>
+        <v>132059935</v>
       </c>
       <c r="B108" t="n">
         <v>5179</v>
@@ -12545,10 +12545,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>557206</v>
+        <v>557267</v>
       </c>
       <c r="R108" t="n">
-        <v>6710235</v>
+        <v>6710406</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12580,7 +12580,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12590,7 +12590,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12733,45 +12733,64 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132059906</v>
+        <v>132059854</v>
       </c>
       <c r="B110" t="n">
-        <v>79317</v>
+        <v>57136</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>557164</v>
+        <v>557049</v>
       </c>
       <c r="R110" t="n">
-        <v>6710175</v>
+        <v>6710317</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12803,7 +12822,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12813,7 +12832,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12840,64 +12859,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132059854</v>
+        <v>132059906</v>
       </c>
       <c r="B111" t="n">
-        <v>57136</v>
+        <v>79317</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>557049</v>
+        <v>557164</v>
       </c>
       <c r="R111" t="n">
-        <v>6710317</v>
+        <v>6710175</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD111" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -9328,7 +9328,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132059918</v>
+        <v>132059900</v>
       </c>
       <c r="B79" t="n">
         <v>79317</v>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>557304</v>
+        <v>557283</v>
       </c>
       <c r="R79" t="n">
-        <v>6710354</v>
+        <v>6710151</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9435,32 +9435,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132059900</v>
+        <v>132059881</v>
       </c>
       <c r="B80" t="n">
-        <v>79317</v>
+        <v>97963</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>557283</v>
+        <v>556939</v>
       </c>
       <c r="R80" t="n">
-        <v>6710151</v>
+        <v>6710405</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9542,32 +9542,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132059881</v>
+        <v>132059918</v>
       </c>
       <c r="B81" t="n">
-        <v>97963</v>
+        <v>79317</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556939</v>
+        <v>557304</v>
       </c>
       <c r="R81" t="n">
-        <v>6710405</v>
+        <v>6710354</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9770,50 +9770,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132059858</v>
+        <v>132059912</v>
       </c>
       <c r="B83" t="n">
-        <v>4775</v>
+        <v>79317</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>557066</v>
+        <v>557108</v>
       </c>
       <c r="R83" t="n">
-        <v>6710417</v>
+        <v>6710330</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9845,7 +9840,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9855,7 +9850,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9882,10 +9877,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132059912</v>
+        <v>132059937</v>
       </c>
       <c r="B84" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9893,34 +9888,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>557108</v>
+        <v>557086</v>
       </c>
       <c r="R84" t="n">
-        <v>6710330</v>
+        <v>6710307</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9962,14 +9962,14 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG84" t="b">
         <v>0</v>
@@ -9989,38 +9989,38 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132059937</v>
+        <v>132059858</v>
       </c>
       <c r="B85" t="n">
-        <v>57948</v>
+        <v>4775</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10029,10 +10029,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>557086</v>
+        <v>557066</v>
       </c>
       <c r="R85" t="n">
-        <v>6710307</v>
+        <v>6710417</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10074,14 +10074,14 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="b">
         <v>0</v>
@@ -10427,38 +10427,38 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132059922</v>
+        <v>132059931</v>
       </c>
       <c r="B89" t="n">
-        <v>57948</v>
+        <v>5179</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10467,10 +10467,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>556923</v>
+        <v>557086</v>
       </c>
       <c r="R89" t="n">
-        <v>6710425</v>
+        <v>6710307</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10512,14 +10512,14 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
@@ -10539,38 +10539,38 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132059931</v>
+        <v>132059922</v>
       </c>
       <c r="B90" t="n">
-        <v>5179</v>
+        <v>57948</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10579,10 +10579,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>557086</v>
+        <v>556923</v>
       </c>
       <c r="R90" t="n">
-        <v>6710307</v>
+        <v>6710425</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10624,14 +10624,14 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG90" t="b">
         <v>0</v>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -9328,7 +9328,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132059900</v>
+        <v>132059918</v>
       </c>
       <c r="B79" t="n">
         <v>79317</v>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>557283</v>
+        <v>557304</v>
       </c>
       <c r="R79" t="n">
-        <v>6710151</v>
+        <v>6710354</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9435,32 +9435,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132059881</v>
+        <v>132059900</v>
       </c>
       <c r="B80" t="n">
-        <v>97963</v>
+        <v>79317</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>556939</v>
+        <v>557283</v>
       </c>
       <c r="R80" t="n">
-        <v>6710405</v>
+        <v>6710151</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9542,32 +9542,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132059918</v>
+        <v>132059881</v>
       </c>
       <c r="B81" t="n">
-        <v>79317</v>
+        <v>97963</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>557304</v>
+        <v>556939</v>
       </c>
       <c r="R81" t="n">
-        <v>6710354</v>
+        <v>6710405</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9770,45 +9770,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132059912</v>
+        <v>132059858</v>
       </c>
       <c r="B83" t="n">
-        <v>79317</v>
+        <v>4775</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>557108</v>
+        <v>557066</v>
       </c>
       <c r="R83" t="n">
-        <v>6710330</v>
+        <v>6710417</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9840,7 +9845,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9850,7 +9855,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9877,10 +9882,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132059937</v>
+        <v>132059912</v>
       </c>
       <c r="B84" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9888,39 +9893,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>557086</v>
+        <v>557108</v>
       </c>
       <c r="R84" t="n">
-        <v>6710307</v>
+        <v>6710330</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9962,14 +9962,14 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="b">
         <v>0</v>
@@ -9989,38 +9989,38 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132059858</v>
+        <v>132059937</v>
       </c>
       <c r="B85" t="n">
-        <v>4775</v>
+        <v>57948</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10029,10 +10029,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>557066</v>
+        <v>557086</v>
       </c>
       <c r="R85" t="n">
-        <v>6710417</v>
+        <v>6710307</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10074,14 +10074,14 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG85" t="b">
         <v>0</v>
@@ -12286,50 +12286,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132059929</v>
+        <v>132059899</v>
       </c>
       <c r="B106" t="n">
-        <v>5179</v>
+        <v>79317</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>557206</v>
+        <v>557291</v>
       </c>
       <c r="R106" t="n">
-        <v>6710235</v>
+        <v>6710161</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12361,7 +12356,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12371,7 +12366,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12398,45 +12393,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132059899</v>
+        <v>132059935</v>
       </c>
       <c r="B107" t="n">
-        <v>79317</v>
+        <v>5179</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>557291</v>
+        <v>557267</v>
       </c>
       <c r="R107" t="n">
-        <v>6710161</v>
+        <v>6710406</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12505,7 +12505,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132059935</v>
+        <v>132059929</v>
       </c>
       <c r="B108" t="n">
         <v>5179</v>
@@ -12545,10 +12545,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>557267</v>
+        <v>557206</v>
       </c>
       <c r="R108" t="n">
-        <v>6710406</v>
+        <v>6710235</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12580,7 +12580,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12590,7 +12590,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12733,64 +12733,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132059854</v>
+        <v>132059906</v>
       </c>
       <c r="B110" t="n">
-        <v>57136</v>
+        <v>79317</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>557049</v>
+        <v>557164</v>
       </c>
       <c r="R110" t="n">
-        <v>6710317</v>
+        <v>6710175</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12822,7 +12803,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12832,7 +12813,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12859,45 +12840,64 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132059906</v>
+        <v>132059854</v>
       </c>
       <c r="B111" t="n">
-        <v>79317</v>
+        <v>57136</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>557164</v>
+        <v>557049</v>
       </c>
       <c r="R111" t="n">
-        <v>6710175</v>
+        <v>6710317</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD111" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -7816,10 +7816,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132059903</v>
+        <v>132059915</v>
       </c>
       <c r="B65" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7851,10 +7851,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557183</v>
+        <v>557255</v>
       </c>
       <c r="R65" t="n">
-        <v>6710096</v>
+        <v>6710412</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7923,10 +7923,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132059915</v>
+        <v>132059903</v>
       </c>
       <c r="B66" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7958,10 +7958,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557255</v>
+        <v>557183</v>
       </c>
       <c r="R66" t="n">
-        <v>6710412</v>
+        <v>6710096</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8033,7 +8033,7 @@
         <v>132059917</v>
       </c>
       <c r="B67" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>132059913</v>
       </c>
       <c r="B68" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>132059846</v>
       </c>
       <c r="B69" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>132059845</v>
       </c>
       <c r="B70" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,10 +8458,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132059908</v>
+        <v>132059911</v>
       </c>
       <c r="B71" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>557176</v>
+        <v>557115</v>
       </c>
       <c r="R71" t="n">
-        <v>6710298</v>
+        <v>6710327</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8565,10 +8565,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132059909</v>
+        <v>132059914</v>
       </c>
       <c r="B72" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>557110</v>
+        <v>556941</v>
       </c>
       <c r="R72" t="n">
-        <v>6710241</v>
+        <v>6710405</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8672,10 +8672,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132059914</v>
+        <v>132059909</v>
       </c>
       <c r="B73" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>556941</v>
+        <v>557110</v>
       </c>
       <c r="R73" t="n">
-        <v>6710405</v>
+        <v>6710241</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132059911</v>
+        <v>132059908</v>
       </c>
       <c r="B74" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>557115</v>
+        <v>557176</v>
       </c>
       <c r="R74" t="n">
-        <v>6710327</v>
+        <v>6710298</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8886,32 +8886,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132059920</v>
+        <v>132059924</v>
       </c>
       <c r="B75" t="n">
-        <v>79317</v>
+        <v>93186</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557294</v>
+        <v>557139</v>
       </c>
       <c r="R75" t="n">
-        <v>6710338</v>
+        <v>6710146</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8993,32 +8993,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132059924</v>
+        <v>132059920</v>
       </c>
       <c r="B76" t="n">
-        <v>93180</v>
+        <v>79319</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>557139</v>
+        <v>557294</v>
       </c>
       <c r="R76" t="n">
-        <v>6710146</v>
+        <v>6710338</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9100,38 +9100,42 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132059934</v>
+        <v>132059884</v>
       </c>
       <c r="B77" t="n">
-        <v>5179</v>
+        <v>99106</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9140,10 +9144,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557044</v>
+        <v>557378</v>
       </c>
       <c r="R77" t="n">
-        <v>6710462</v>
+        <v>6710276</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9175,7 +9179,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9185,7 +9189,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9212,42 +9216,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132059884</v>
+        <v>132059934</v>
       </c>
       <c r="B78" t="n">
-        <v>99098</v>
+        <v>5179</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>557378</v>
+        <v>557044</v>
       </c>
       <c r="R78" t="n">
-        <v>6710276</v>
+        <v>6710462</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9328,32 +9328,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132059918</v>
+        <v>132059881</v>
       </c>
       <c r="B79" t="n">
-        <v>79317</v>
+        <v>97971</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>557304</v>
+        <v>556939</v>
       </c>
       <c r="R79" t="n">
-        <v>6710354</v>
+        <v>6710405</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9435,10 +9435,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132059900</v>
+        <v>132059918</v>
       </c>
       <c r="B80" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>557283</v>
+        <v>557304</v>
       </c>
       <c r="R80" t="n">
-        <v>6710151</v>
+        <v>6710354</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9542,32 +9542,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132059881</v>
+        <v>132059900</v>
       </c>
       <c r="B81" t="n">
-        <v>97963</v>
+        <v>79319</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556939</v>
+        <v>557283</v>
       </c>
       <c r="R81" t="n">
-        <v>6710405</v>
+        <v>6710151</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9652,7 +9652,7 @@
         <v>132059887</v>
       </c>
       <c r="B82" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9882,10 +9882,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132059912</v>
+        <v>132059937</v>
       </c>
       <c r="B84" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9893,34 +9893,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>557108</v>
+        <v>557086</v>
       </c>
       <c r="R84" t="n">
-        <v>6710330</v>
+        <v>6710307</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9952,7 +9957,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9962,14 +9967,14 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG84" t="b">
         <v>0</v>
@@ -9989,10 +9994,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132059937</v>
+        <v>132059912</v>
       </c>
       <c r="B85" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10000,39 +10005,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>557086</v>
+        <v>557108</v>
       </c>
       <c r="R85" t="n">
-        <v>6710307</v>
+        <v>6710330</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10074,14 +10074,14 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="b">
         <v>0</v>
@@ -10101,10 +10101,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132059841</v>
+        <v>132059862</v>
       </c>
       <c r="B86" t="n">
-        <v>91892</v>
+        <v>57946</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10112,34 +10112,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>557246</v>
+        <v>557268</v>
       </c>
       <c r="R86" t="n">
-        <v>6710104</v>
+        <v>6710406</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10171,7 +10176,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10181,7 +10186,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10208,10 +10213,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132059862</v>
+        <v>132059841</v>
       </c>
       <c r="B87" t="n">
-        <v>57945</v>
+        <v>91898</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10219,39 +10224,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>557268</v>
+        <v>557246</v>
       </c>
       <c r="R87" t="n">
-        <v>6710406</v>
+        <v>6710104</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10323,7 +10323,7 @@
         <v>132059907</v>
       </c>
       <c r="B88" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>132059922</v>
       </c>
       <c r="B90" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10651,45 +10651,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132059902</v>
+        <v>132059885</v>
       </c>
       <c r="B91" t="n">
-        <v>79317</v>
+        <v>99106</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>557178</v>
+        <v>557308</v>
       </c>
       <c r="R91" t="n">
-        <v>6710089</v>
+        <v>6710165</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10721,7 +10730,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10731,7 +10740,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10758,10 +10767,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132059916</v>
+        <v>132059902</v>
       </c>
       <c r="B92" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10793,10 +10802,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>557268</v>
+        <v>557178</v>
       </c>
       <c r="R92" t="n">
-        <v>6710406</v>
+        <v>6710089</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10828,7 +10837,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10838,7 +10847,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10868,7 +10877,7 @@
         <v>132059837</v>
       </c>
       <c r="B93" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10972,54 +10981,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132059885</v>
+        <v>132059916</v>
       </c>
       <c r="B94" t="n">
-        <v>99098</v>
+        <v>79319</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>557308</v>
+        <v>557268</v>
       </c>
       <c r="R94" t="n">
-        <v>6710165</v>
+        <v>6710406</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11088,7 +11088,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132059936</v>
+        <v>132059928</v>
       </c>
       <c r="B95" t="n">
         <v>5179</v>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>557271</v>
+        <v>557196</v>
       </c>
       <c r="R95" t="n">
-        <v>6710331</v>
+        <v>6710215</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11200,7 +11200,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132059928</v>
+        <v>132059936</v>
       </c>
       <c r="B96" t="n">
         <v>5179</v>
@@ -11240,10 +11240,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>557196</v>
+        <v>557271</v>
       </c>
       <c r="R96" t="n">
-        <v>6710215</v>
+        <v>6710331</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11312,10 +11312,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132059842</v>
+        <v>132059901</v>
       </c>
       <c r="B97" t="n">
-        <v>91892</v>
+        <v>79319</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11323,21 +11323,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11347,10 +11347,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>557050</v>
+        <v>557218</v>
       </c>
       <c r="R97" t="n">
-        <v>6710330</v>
+        <v>6710093</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11419,10 +11419,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132059865</v>
+        <v>132059886</v>
       </c>
       <c r="B98" t="n">
-        <v>92352</v>
+        <v>99106</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11430,34 +11430,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>557190</v>
+        <v>557312</v>
       </c>
       <c r="R98" t="n">
-        <v>6710236</v>
+        <v>6710224</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11489,7 +11498,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11499,7 +11508,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11508,7 +11517,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11527,10 +11535,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132059901</v>
+        <v>132059842</v>
       </c>
       <c r="B99" t="n">
-        <v>79317</v>
+        <v>91898</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11538,21 +11546,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11562,10 +11570,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>557218</v>
+        <v>557050</v>
       </c>
       <c r="R99" t="n">
-        <v>6710093</v>
+        <v>6710330</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11597,7 +11605,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11607,7 +11615,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11634,10 +11642,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132059886</v>
+        <v>132059865</v>
       </c>
       <c r="B100" t="n">
-        <v>99098</v>
+        <v>92358</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11645,43 +11653,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>557312</v>
+        <v>557190</v>
       </c>
       <c r="R100" t="n">
-        <v>6710224</v>
+        <v>6710236</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11713,7 +11712,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11723,7 +11722,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11732,6 +11731,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11753,7 +11753,7 @@
         <v>132059866</v>
       </c>
       <c r="B101" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>132059904</v>
       </c>
       <c r="B102" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>132059921</v>
       </c>
       <c r="B103" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>132059840</v>
       </c>
       <c r="B104" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12179,45 +12179,50 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132059919</v>
+        <v>132059935</v>
       </c>
       <c r="B105" t="n">
-        <v>79317</v>
+        <v>5179</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>557299</v>
+        <v>557267</v>
       </c>
       <c r="R105" t="n">
-        <v>6710339</v>
+        <v>6710406</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12249,7 +12254,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12259,7 +12264,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12286,45 +12291,50 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132059899</v>
+        <v>132059929</v>
       </c>
       <c r="B106" t="n">
-        <v>79317</v>
+        <v>5179</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>557291</v>
+        <v>557206</v>
       </c>
       <c r="R106" t="n">
-        <v>6710161</v>
+        <v>6710235</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12356,7 +12366,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12366,7 +12376,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12393,50 +12403,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132059935</v>
+        <v>132059899</v>
       </c>
       <c r="B107" t="n">
-        <v>5179</v>
+        <v>79319</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>557267</v>
+        <v>557291</v>
       </c>
       <c r="R107" t="n">
-        <v>6710406</v>
+        <v>6710161</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12468,7 +12473,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12478,7 +12483,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12505,50 +12510,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132059929</v>
+        <v>132059919</v>
       </c>
       <c r="B108" t="n">
-        <v>5179</v>
+        <v>79319</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>557206</v>
+        <v>557299</v>
       </c>
       <c r="R108" t="n">
-        <v>6710235</v>
+        <v>6710339</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12580,7 +12580,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12590,7 +12590,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12620,7 +12620,7 @@
         <v>132059888</v>
       </c>
       <c r="B109" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12733,45 +12733,64 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132059906</v>
+        <v>132059854</v>
       </c>
       <c r="B110" t="n">
-        <v>79317</v>
+        <v>57137</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>557164</v>
+        <v>557049</v>
       </c>
       <c r="R110" t="n">
-        <v>6710175</v>
+        <v>6710317</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12803,7 +12822,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12813,7 +12832,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12840,64 +12859,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132059854</v>
+        <v>132059906</v>
       </c>
       <c r="B111" t="n">
-        <v>57136</v>
+        <v>79319</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>557049</v>
+        <v>557164</v>
       </c>
       <c r="R111" t="n">
-        <v>6710317</v>
+        <v>6710175</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12969,7 +12969,7 @@
         <v>132059843</v>
       </c>
       <c r="B112" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -8886,10 +8886,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132059924</v>
+        <v>132059934</v>
       </c>
       <c r="B75" t="n">
-        <v>93186</v>
+        <v>5179</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8897,34 +8897,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557139</v>
+        <v>557044</v>
       </c>
       <c r="R75" t="n">
-        <v>6710146</v>
+        <v>6710462</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8956,7 +8961,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8966,7 +8971,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8993,32 +8998,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132059920</v>
+        <v>132059924</v>
       </c>
       <c r="B76" t="n">
-        <v>79319</v>
+        <v>93186</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9028,10 +9033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>557294</v>
+        <v>557139</v>
       </c>
       <c r="R76" t="n">
-        <v>6710338</v>
+        <v>6710146</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9063,7 +9068,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9073,7 +9078,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9100,54 +9105,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132059884</v>
+        <v>132059920</v>
       </c>
       <c r="B77" t="n">
-        <v>99106</v>
+        <v>79319</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557378</v>
+        <v>557294</v>
       </c>
       <c r="R77" t="n">
-        <v>6710276</v>
+        <v>6710338</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9179,7 +9175,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9189,7 +9185,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9216,38 +9212,42 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132059934</v>
+        <v>132059884</v>
       </c>
       <c r="B78" t="n">
-        <v>5179</v>
+        <v>99106</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>557044</v>
+        <v>557378</v>
       </c>
       <c r="R78" t="n">
-        <v>6710462</v>
+        <v>6710276</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9328,32 +9328,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132059881</v>
+        <v>132059918</v>
       </c>
       <c r="B79" t="n">
-        <v>97971</v>
+        <v>79319</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>556939</v>
+        <v>557304</v>
       </c>
       <c r="R79" t="n">
-        <v>6710405</v>
+        <v>6710354</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9435,7 +9435,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132059918</v>
+        <v>132059900</v>
       </c>
       <c r="B80" t="n">
         <v>79319</v>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>557304</v>
+        <v>557283</v>
       </c>
       <c r="R80" t="n">
-        <v>6710354</v>
+        <v>6710151</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9542,32 +9542,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132059900</v>
+        <v>132059881</v>
       </c>
       <c r="B81" t="n">
-        <v>79319</v>
+        <v>97971</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>557283</v>
+        <v>556939</v>
       </c>
       <c r="R81" t="n">
-        <v>6710151</v>
+        <v>6710405</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9649,42 +9649,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132059887</v>
+        <v>132059858</v>
       </c>
       <c r="B82" t="n">
-        <v>99106</v>
+        <v>4775</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9693,7 +9689,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>556973</v>
+        <v>557066</v>
       </c>
       <c r="R82" t="n">
         <v>6710417</v>
@@ -9728,7 +9724,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9738,12 +9734,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>5 m från kallkälla</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9770,38 +9761,38 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132059858</v>
+        <v>132059937</v>
       </c>
       <c r="B83" t="n">
-        <v>4775</v>
+        <v>57949</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9810,10 +9801,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>557066</v>
+        <v>557086</v>
       </c>
       <c r="R83" t="n">
-        <v>6710417</v>
+        <v>6710307</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9845,7 +9836,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9855,14 +9846,14 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG83" t="b">
         <v>0</v>
@@ -9882,38 +9873,42 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132059937</v>
+        <v>132059887</v>
       </c>
       <c r="B84" t="n">
-        <v>57949</v>
+        <v>99106</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9922,10 +9917,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>557086</v>
+        <v>556973</v>
       </c>
       <c r="R84" t="n">
-        <v>6710307</v>
+        <v>6710417</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9957,7 +9952,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9967,14 +9962,19 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>5 m från kallkälla</t>
         </is>
       </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="b">
         <v>0</v>
@@ -11088,7 +11088,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132059928</v>
+        <v>132059936</v>
       </c>
       <c r="B95" t="n">
         <v>5179</v>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>557196</v>
+        <v>557271</v>
       </c>
       <c r="R95" t="n">
-        <v>6710215</v>
+        <v>6710331</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11200,7 +11200,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132059936</v>
+        <v>132059928</v>
       </c>
       <c r="B96" t="n">
         <v>5179</v>
@@ -11240,10 +11240,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>557271</v>
+        <v>557196</v>
       </c>
       <c r="R96" t="n">
-        <v>6710331</v>
+        <v>6710215</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD96" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -7816,10 +7816,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132059915</v>
+        <v>132059903</v>
       </c>
       <c r="B65" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7851,10 +7851,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557255</v>
+        <v>557183</v>
       </c>
       <c r="R65" t="n">
-        <v>6710412</v>
+        <v>6710096</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7923,10 +7923,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132059903</v>
+        <v>132059915</v>
       </c>
       <c r="B66" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7958,10 +7958,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557183</v>
+        <v>557255</v>
       </c>
       <c r="R66" t="n">
-        <v>6710096</v>
+        <v>6710412</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8030,10 +8030,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132059917</v>
+        <v>132059913</v>
       </c>
       <c r="B67" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8065,10 +8065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557303</v>
+        <v>557094</v>
       </c>
       <c r="R67" t="n">
-        <v>6710369</v>
+        <v>6710335</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8137,10 +8137,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132059913</v>
+        <v>132059917</v>
       </c>
       <c r="B68" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8172,10 +8172,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>557094</v>
+        <v>557303</v>
       </c>
       <c r="R68" t="n">
-        <v>6710335</v>
+        <v>6710369</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8247,7 +8247,7 @@
         <v>132059846</v>
       </c>
       <c r="B69" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8351,10 +8351,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132059845</v>
+        <v>132059908</v>
       </c>
       <c r="B70" t="n">
-        <v>91898</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8362,21 +8362,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>557066</v>
+        <v>557176</v>
       </c>
       <c r="R70" t="n">
-        <v>6710417</v>
+        <v>6710298</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8458,10 +8458,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132059911</v>
+        <v>132059909</v>
       </c>
       <c r="B71" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>557115</v>
+        <v>557110</v>
       </c>
       <c r="R71" t="n">
-        <v>6710327</v>
+        <v>6710241</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8568,7 +8568,7 @@
         <v>132059914</v>
       </c>
       <c r="B72" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8672,10 +8672,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132059909</v>
+        <v>132059911</v>
       </c>
       <c r="B73" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>557110</v>
+        <v>557115</v>
       </c>
       <c r="R73" t="n">
-        <v>6710241</v>
+        <v>6710327</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132059908</v>
+        <v>132059845</v>
       </c>
       <c r="B74" t="n">
-        <v>79319</v>
+        <v>91908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8790,21 +8790,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>557176</v>
+        <v>557066</v>
       </c>
       <c r="R74" t="n">
-        <v>6710298</v>
+        <v>6710417</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8886,50 +8886,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132059934</v>
+        <v>132059920</v>
       </c>
       <c r="B75" t="n">
-        <v>5179</v>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557044</v>
+        <v>557294</v>
       </c>
       <c r="R75" t="n">
-        <v>6710462</v>
+        <v>6710338</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8961,7 +8956,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8971,7 +8966,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9001,7 +8996,7 @@
         <v>132059924</v>
       </c>
       <c r="B76" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9105,45 +9100,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132059920</v>
+        <v>132059934</v>
       </c>
       <c r="B77" t="n">
-        <v>79319</v>
+        <v>5179</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557294</v>
+        <v>557044</v>
       </c>
       <c r="R77" t="n">
-        <v>6710338</v>
+        <v>6710462</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9215,7 +9215,7 @@
         <v>132059884</v>
       </c>
       <c r="B78" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>132059918</v>
       </c>
       <c r="B79" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>132059900</v>
       </c>
       <c r="B80" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>132059881</v>
       </c>
       <c r="B81" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9761,38 +9761,42 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132059937</v>
+        <v>132059887</v>
       </c>
       <c r="B83" t="n">
-        <v>57949</v>
+        <v>99116</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9801,10 +9805,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>557086</v>
+        <v>556973</v>
       </c>
       <c r="R83" t="n">
-        <v>6710307</v>
+        <v>6710417</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9836,7 +9840,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9846,14 +9850,19 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>5 m från kallkälla</t>
         </is>
       </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="b">
         <v>0</v>
@@ -9873,54 +9882,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132059887</v>
+        <v>132059912</v>
       </c>
       <c r="B84" t="n">
-        <v>99106</v>
+        <v>79327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>556973</v>
+        <v>557108</v>
       </c>
       <c r="R84" t="n">
-        <v>6710417</v>
+        <v>6710330</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9962,12 +9962,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>5 m från kallkälla</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9994,10 +9989,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132059912</v>
+        <v>132059937</v>
       </c>
       <c r="B85" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10005,34 +10000,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>557108</v>
+        <v>557086</v>
       </c>
       <c r="R85" t="n">
-        <v>6710330</v>
+        <v>6710307</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10074,14 +10074,14 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG85" t="b">
         <v>0</v>
@@ -10101,10 +10101,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132059862</v>
+        <v>132059841</v>
       </c>
       <c r="B86" t="n">
-        <v>57946</v>
+        <v>91908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10112,39 +10112,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>557268</v>
+        <v>557246</v>
       </c>
       <c r="R86" t="n">
-        <v>6710406</v>
+        <v>6710104</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10176,7 +10171,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10186,7 +10181,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10213,10 +10208,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132059841</v>
+        <v>132059862</v>
       </c>
       <c r="B87" t="n">
-        <v>91898</v>
+        <v>57950</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10224,34 +10219,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>557246</v>
+        <v>557268</v>
       </c>
       <c r="R87" t="n">
-        <v>6710104</v>
+        <v>6710406</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10323,7 +10323,7 @@
         <v>132059907</v>
       </c>
       <c r="B88" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10427,38 +10427,38 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132059931</v>
+        <v>132059922</v>
       </c>
       <c r="B89" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10467,10 +10467,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>557086</v>
+        <v>556923</v>
       </c>
       <c r="R89" t="n">
-        <v>6710307</v>
+        <v>6710425</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10512,14 +10512,14 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
@@ -10539,38 +10539,38 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132059922</v>
+        <v>132059931</v>
       </c>
       <c r="B90" t="n">
-        <v>57949</v>
+        <v>5179</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10579,10 +10579,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>556923</v>
+        <v>557086</v>
       </c>
       <c r="R90" t="n">
-        <v>6710425</v>
+        <v>6710307</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10624,14 +10624,14 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="b">
         <v>0</v>
@@ -10651,54 +10651,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132059885</v>
+        <v>132059902</v>
       </c>
       <c r="B91" t="n">
-        <v>99106</v>
+        <v>79327</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>557308</v>
+        <v>557178</v>
       </c>
       <c r="R91" t="n">
-        <v>6710165</v>
+        <v>6710089</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10730,7 +10721,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10740,7 +10731,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10767,10 +10758,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132059902</v>
+        <v>132059916</v>
       </c>
       <c r="B92" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10802,10 +10793,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>557178</v>
+        <v>557268</v>
       </c>
       <c r="R92" t="n">
-        <v>6710089</v>
+        <v>6710406</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10837,7 +10828,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10847,7 +10838,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10877,7 +10868,7 @@
         <v>132059837</v>
       </c>
       <c r="B93" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10981,45 +10972,54 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132059916</v>
+        <v>132059885</v>
       </c>
       <c r="B94" t="n">
-        <v>79319</v>
+        <v>99116</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>557268</v>
+        <v>557308</v>
       </c>
       <c r="R94" t="n">
-        <v>6710406</v>
+        <v>6710165</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11315,7 +11315,7 @@
         <v>132059901</v>
       </c>
       <c r="B97" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11419,54 +11419,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132059886</v>
+        <v>132059842</v>
       </c>
       <c r="B98" t="n">
-        <v>99106</v>
+        <v>91908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>557312</v>
+        <v>557050</v>
       </c>
       <c r="R98" t="n">
-        <v>6710224</v>
+        <v>6710330</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11498,7 +11489,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11508,7 +11499,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11535,32 +11526,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132059842</v>
+        <v>132059865</v>
       </c>
       <c r="B99" t="n">
-        <v>91898</v>
+        <v>92368</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11570,10 +11561,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>557050</v>
+        <v>557190</v>
       </c>
       <c r="R99" t="n">
-        <v>6710330</v>
+        <v>6710236</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11605,7 +11596,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11615,7 +11606,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11624,6 +11615,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11642,10 +11634,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132059865</v>
+        <v>132059886</v>
       </c>
       <c r="B100" t="n">
-        <v>92358</v>
+        <v>99116</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11653,34 +11645,43 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>557190</v>
+        <v>557312</v>
       </c>
       <c r="R100" t="n">
-        <v>6710236</v>
+        <v>6710224</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11712,7 +11713,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11722,7 +11723,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11731,7 +11732,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11750,32 +11750,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132059866</v>
+        <v>132059904</v>
       </c>
       <c r="B101" t="n">
-        <v>92358</v>
+        <v>79327</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11785,10 +11785,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>557001</v>
+        <v>557202</v>
       </c>
       <c r="R101" t="n">
-        <v>6710392</v>
+        <v>6710100</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11839,7 +11839,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11858,10 +11857,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132059904</v>
+        <v>132059921</v>
       </c>
       <c r="B102" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11893,10 +11892,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>557202</v>
+        <v>557288</v>
       </c>
       <c r="R102" t="n">
-        <v>6710100</v>
+        <v>6710334</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11928,7 +11927,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11938,7 +11937,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11965,32 +11964,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132059921</v>
+        <v>132059866</v>
       </c>
       <c r="B103" t="n">
-        <v>79319</v>
+        <v>92368</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12000,10 +11999,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>557288</v>
+        <v>557001</v>
       </c>
       <c r="R103" t="n">
-        <v>6710334</v>
+        <v>6710392</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12035,7 +12034,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12045,7 +12044,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12054,6 +12053,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -12075,7 +12075,7 @@
         <v>132059840</v>
       </c>
       <c r="B104" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12403,45 +12403,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132059899</v>
+        <v>132059888</v>
       </c>
       <c r="B107" t="n">
-        <v>79319</v>
+        <v>99116</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>557291</v>
+        <v>557286</v>
       </c>
       <c r="R107" t="n">
-        <v>6710161</v>
+        <v>6710159</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12510,10 +12519,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132059919</v>
+        <v>132059899</v>
       </c>
       <c r="B108" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12545,10 +12554,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>557299</v>
+        <v>557291</v>
       </c>
       <c r="R108" t="n">
-        <v>6710339</v>
+        <v>6710161</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12580,7 +12589,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12590,7 +12599,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12617,54 +12626,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132059888</v>
+        <v>132059919</v>
       </c>
       <c r="B109" t="n">
-        <v>99106</v>
+        <v>79327</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>557286</v>
+        <v>557299</v>
       </c>
       <c r="R109" t="n">
-        <v>6710159</v>
+        <v>6710339</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12736,7 +12736,7 @@
         <v>132059854</v>
       </c>
       <c r="B110" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>132059906</v>
       </c>
       <c r="B111" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>132059843</v>
       </c>
       <c r="B112" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -8565,7 +8565,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132059914</v>
+        <v>132059911</v>
       </c>
       <c r="B72" t="n">
         <v>79327</v>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556941</v>
+        <v>557115</v>
       </c>
       <c r="R72" t="n">
-        <v>6710405</v>
+        <v>6710327</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8672,10 +8672,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132059911</v>
+        <v>132059845</v>
       </c>
       <c r="B73" t="n">
-        <v>79327</v>
+        <v>91908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8683,21 +8683,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>557115</v>
+        <v>557066</v>
       </c>
       <c r="R73" t="n">
-        <v>6710327</v>
+        <v>6710417</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132059845</v>
+        <v>132059914</v>
       </c>
       <c r="B74" t="n">
-        <v>91908</v>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8790,21 +8790,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>557066</v>
+        <v>556941</v>
       </c>
       <c r="R74" t="n">
-        <v>6710417</v>
+        <v>6710405</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9328,32 +9328,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132059918</v>
+        <v>132059881</v>
       </c>
       <c r="B79" t="n">
-        <v>79327</v>
+        <v>97981</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>557304</v>
+        <v>556939</v>
       </c>
       <c r="R79" t="n">
-        <v>6710354</v>
+        <v>6710405</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9435,7 +9435,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132059900</v>
+        <v>132059918</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>557283</v>
+        <v>557304</v>
       </c>
       <c r="R80" t="n">
-        <v>6710151</v>
+        <v>6710354</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9542,32 +9542,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132059881</v>
+        <v>132059900</v>
       </c>
       <c r="B81" t="n">
-        <v>97981</v>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556939</v>
+        <v>557283</v>
       </c>
       <c r="R81" t="n">
-        <v>6710405</v>
+        <v>6710151</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9649,50 +9649,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132059858</v>
+        <v>132059912</v>
       </c>
       <c r="B82" t="n">
-        <v>4775</v>
+        <v>79327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>557066</v>
+        <v>557108</v>
       </c>
       <c r="R82" t="n">
-        <v>6710417</v>
+        <v>6710330</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9724,7 +9719,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9734,7 +9729,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9882,10 +9877,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132059912</v>
+        <v>132059937</v>
       </c>
       <c r="B84" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9893,34 +9888,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>557108</v>
+        <v>557086</v>
       </c>
       <c r="R84" t="n">
-        <v>6710330</v>
+        <v>6710307</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9962,14 +9962,14 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG84" t="b">
         <v>0</v>
@@ -9989,38 +9989,38 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132059937</v>
+        <v>132059858</v>
       </c>
       <c r="B85" t="n">
-        <v>57953</v>
+        <v>4775</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10029,10 +10029,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>557086</v>
+        <v>557066</v>
       </c>
       <c r="R85" t="n">
-        <v>6710307</v>
+        <v>6710417</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10074,14 +10074,14 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="b">
         <v>0</v>
@@ -12179,50 +12179,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132059935</v>
+        <v>132059899</v>
       </c>
       <c r="B105" t="n">
-        <v>5179</v>
+        <v>79327</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>557267</v>
+        <v>557291</v>
       </c>
       <c r="R105" t="n">
-        <v>6710406</v>
+        <v>6710161</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12254,7 +12249,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12264,7 +12259,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12291,50 +12286,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132059929</v>
+        <v>132059919</v>
       </c>
       <c r="B106" t="n">
-        <v>5179</v>
+        <v>79327</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>557206</v>
+        <v>557299</v>
       </c>
       <c r="R106" t="n">
-        <v>6710235</v>
+        <v>6710339</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12366,7 +12356,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12376,7 +12366,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12403,42 +12393,38 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132059888</v>
+        <v>132059935</v>
       </c>
       <c r="B107" t="n">
-        <v>99116</v>
+        <v>5179</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12447,10 +12433,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>557286</v>
+        <v>557267</v>
       </c>
       <c r="R107" t="n">
-        <v>6710159</v>
+        <v>6710406</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12482,7 +12468,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12492,7 +12478,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12519,45 +12505,50 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132059899</v>
+        <v>132059929</v>
       </c>
       <c r="B108" t="n">
-        <v>79327</v>
+        <v>5179</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>557291</v>
+        <v>557206</v>
       </c>
       <c r="R108" t="n">
-        <v>6710161</v>
+        <v>6710235</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12589,7 +12580,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12599,7 +12590,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12626,45 +12617,54 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132059919</v>
+        <v>132059888</v>
       </c>
       <c r="B109" t="n">
-        <v>79327</v>
+        <v>99116</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>557299</v>
+        <v>557286</v>
       </c>
       <c r="R109" t="n">
-        <v>6710339</v>
+        <v>6710159</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -8247,7 +8247,7 @@
         <v>132059846</v>
       </c>
       <c r="B69" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8351,10 +8351,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132059908</v>
+        <v>132059845</v>
       </c>
       <c r="B70" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8362,21 +8362,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>557176</v>
+        <v>557066</v>
       </c>
       <c r="R70" t="n">
-        <v>6710298</v>
+        <v>6710417</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8458,7 +8458,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132059909</v>
+        <v>132059908</v>
       </c>
       <c r="B71" t="n">
         <v>79327</v>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>557110</v>
+        <v>557176</v>
       </c>
       <c r="R71" t="n">
-        <v>6710241</v>
+        <v>6710298</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8565,7 +8565,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132059911</v>
+        <v>132059909</v>
       </c>
       <c r="B72" t="n">
         <v>79327</v>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>557115</v>
+        <v>557110</v>
       </c>
       <c r="R72" t="n">
-        <v>6710327</v>
+        <v>6710241</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8672,10 +8672,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132059845</v>
+        <v>132059914</v>
       </c>
       <c r="B73" t="n">
-        <v>91908</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8683,21 +8683,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>557066</v>
+        <v>556941</v>
       </c>
       <c r="R73" t="n">
-        <v>6710417</v>
+        <v>6710405</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8779,7 +8779,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132059914</v>
+        <v>132059911</v>
       </c>
       <c r="B74" t="n">
         <v>79327</v>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>556941</v>
+        <v>557115</v>
       </c>
       <c r="R74" t="n">
-        <v>6710405</v>
+        <v>6710327</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8996,7 +8996,7 @@
         <v>132059924</v>
       </c>
       <c r="B76" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>132059884</v>
       </c>
       <c r="B78" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>132059881</v>
       </c>
       <c r="B79" t="n">
-        <v>97981</v>
+        <v>97983</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9756,42 +9756,38 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132059887</v>
+        <v>132059858</v>
       </c>
       <c r="B83" t="n">
-        <v>99116</v>
+        <v>4775</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9800,7 +9796,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>556973</v>
+        <v>557066</v>
       </c>
       <c r="R83" t="n">
         <v>6710417</v>
@@ -9835,7 +9831,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9845,12 +9841,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>5 m från kallkälla</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9989,38 +9980,42 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132059858</v>
+        <v>132059887</v>
       </c>
       <c r="B85" t="n">
-        <v>4775</v>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10029,7 +10024,7 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>557066</v>
+        <v>556973</v>
       </c>
       <c r="R85" t="n">
         <v>6710417</v>
@@ -10064,7 +10059,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10074,7 +10069,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>5 m från kallkälla</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10101,10 +10101,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132059841</v>
+        <v>132059862</v>
       </c>
       <c r="B86" t="n">
-        <v>91908</v>
+        <v>57950</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10112,34 +10112,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>557246</v>
+        <v>557268</v>
       </c>
       <c r="R86" t="n">
-        <v>6710104</v>
+        <v>6710406</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10171,7 +10176,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10181,7 +10186,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10208,10 +10213,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132059862</v>
+        <v>132059841</v>
       </c>
       <c r="B87" t="n">
-        <v>57950</v>
+        <v>91909</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10219,39 +10224,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>557268</v>
+        <v>557246</v>
       </c>
       <c r="R87" t="n">
-        <v>6710406</v>
+        <v>6710104</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10427,38 +10427,38 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132059922</v>
+        <v>132059931</v>
       </c>
       <c r="B89" t="n">
-        <v>57953</v>
+        <v>5179</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10467,10 +10467,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>556923</v>
+        <v>557086</v>
       </c>
       <c r="R89" t="n">
-        <v>6710425</v>
+        <v>6710307</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10512,14 +10512,14 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
@@ -10539,38 +10539,38 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132059931</v>
+        <v>132059922</v>
       </c>
       <c r="B90" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10579,10 +10579,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>557086</v>
+        <v>556923</v>
       </c>
       <c r="R90" t="n">
-        <v>6710307</v>
+        <v>6710425</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10624,14 +10624,14 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG90" t="b">
         <v>0</v>
@@ -10868,7 +10868,7 @@
         <v>132059837</v>
       </c>
       <c r="B93" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>132059885</v>
       </c>
       <c r="B94" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>132059842</v>
       </c>
       <c r="B98" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>132059865</v>
       </c>
       <c r="B99" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>132059886</v>
       </c>
       <c r="B100" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>132059866</v>
       </c>
       <c r="B103" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>132059840</v>
       </c>
       <c r="B104" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>132059888</v>
       </c>
       <c r="B109" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12733,64 +12733,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132059854</v>
+        <v>132059906</v>
       </c>
       <c r="B110" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>557049</v>
+        <v>557164</v>
       </c>
       <c r="R110" t="n">
-        <v>6710317</v>
+        <v>6710175</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12822,7 +12803,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12832,7 +12813,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12859,45 +12840,64 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132059906</v>
+        <v>132059854</v>
       </c>
       <c r="B111" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>557164</v>
+        <v>557049</v>
       </c>
       <c r="R111" t="n">
-        <v>6710175</v>
+        <v>6710317</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12969,7 +12969,7 @@
         <v>132059843</v>
       </c>
       <c r="B112" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -8351,10 +8351,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132059845</v>
+        <v>132059908</v>
       </c>
       <c r="B70" t="n">
-        <v>91909</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8362,21 +8362,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>557066</v>
+        <v>557176</v>
       </c>
       <c r="R70" t="n">
-        <v>6710417</v>
+        <v>6710298</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8458,7 +8458,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132059908</v>
+        <v>132059909</v>
       </c>
       <c r="B71" t="n">
         <v>79327</v>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>557176</v>
+        <v>557110</v>
       </c>
       <c r="R71" t="n">
-        <v>6710298</v>
+        <v>6710241</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8565,7 +8565,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132059909</v>
+        <v>132059914</v>
       </c>
       <c r="B72" t="n">
         <v>79327</v>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>557110</v>
+        <v>556941</v>
       </c>
       <c r="R72" t="n">
-        <v>6710241</v>
+        <v>6710405</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8672,7 +8672,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132059914</v>
+        <v>132059911</v>
       </c>
       <c r="B73" t="n">
         <v>79327</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>556941</v>
+        <v>557115</v>
       </c>
       <c r="R73" t="n">
-        <v>6710405</v>
+        <v>6710327</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132059911</v>
+        <v>132059845</v>
       </c>
       <c r="B74" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8790,21 +8790,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>557115</v>
+        <v>557066</v>
       </c>
       <c r="R74" t="n">
-        <v>6710327</v>
+        <v>6710417</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8886,45 +8886,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132059920</v>
+        <v>132059934</v>
       </c>
       <c r="B75" t="n">
-        <v>79327</v>
+        <v>5179</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557294</v>
+        <v>557044</v>
       </c>
       <c r="R75" t="n">
-        <v>6710338</v>
+        <v>6710462</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8956,7 +8961,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8966,7 +8971,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8993,45 +8998,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132059924</v>
+        <v>132059884</v>
       </c>
       <c r="B76" t="n">
-        <v>93197</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>557139</v>
+        <v>557378</v>
       </c>
       <c r="R76" t="n">
-        <v>6710146</v>
+        <v>6710276</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9063,7 +9077,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9073,7 +9087,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9100,50 +9114,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132059934</v>
+        <v>132059920</v>
       </c>
       <c r="B77" t="n">
-        <v>5179</v>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557044</v>
+        <v>557294</v>
       </c>
       <c r="R77" t="n">
-        <v>6710462</v>
+        <v>6710338</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9175,7 +9184,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9185,7 +9194,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9212,54 +9221,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132059884</v>
+        <v>132059924</v>
       </c>
       <c r="B78" t="n">
-        <v>99118</v>
+        <v>93197</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>557378</v>
+        <v>557139</v>
       </c>
       <c r="R78" t="n">
-        <v>6710276</v>
+        <v>6710146</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9328,32 +9328,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132059881</v>
+        <v>132059918</v>
       </c>
       <c r="B79" t="n">
-        <v>97983</v>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>556939</v>
+        <v>557304</v>
       </c>
       <c r="R79" t="n">
-        <v>6710405</v>
+        <v>6710354</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9435,7 +9435,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132059918</v>
+        <v>132059900</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>557304</v>
+        <v>557283</v>
       </c>
       <c r="R80" t="n">
-        <v>6710354</v>
+        <v>6710151</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9542,32 +9542,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132059900</v>
+        <v>132059881</v>
       </c>
       <c r="B81" t="n">
-        <v>79327</v>
+        <v>97983</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>557283</v>
+        <v>556939</v>
       </c>
       <c r="R81" t="n">
-        <v>6710151</v>
+        <v>6710405</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10101,10 +10101,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132059862</v>
+        <v>132059841</v>
       </c>
       <c r="B86" t="n">
-        <v>57950</v>
+        <v>91909</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10112,39 +10112,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>557268</v>
+        <v>557246</v>
       </c>
       <c r="R86" t="n">
-        <v>6710406</v>
+        <v>6710104</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10176,7 +10171,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10186,7 +10181,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10213,10 +10208,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132059841</v>
+        <v>132059862</v>
       </c>
       <c r="B87" t="n">
-        <v>91909</v>
+        <v>57950</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10224,34 +10219,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>557246</v>
+        <v>557268</v>
       </c>
       <c r="R87" t="n">
-        <v>6710104</v>
+        <v>6710406</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10651,7 +10651,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132059902</v>
+        <v>132059916</v>
       </c>
       <c r="B91" t="n">
         <v>79327</v>
@@ -10686,10 +10686,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>557178</v>
+        <v>557268</v>
       </c>
       <c r="R91" t="n">
-        <v>6710089</v>
+        <v>6710406</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10758,45 +10758,54 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132059916</v>
+        <v>132059885</v>
       </c>
       <c r="B92" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>557268</v>
+        <v>557308</v>
       </c>
       <c r="R92" t="n">
-        <v>6710406</v>
+        <v>6710165</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10828,7 +10837,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10838,7 +10847,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10865,32 +10874,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132059837</v>
+        <v>132059902</v>
       </c>
       <c r="B93" t="n">
-        <v>91872</v>
+        <v>79327</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10900,10 +10909,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>556964</v>
+        <v>557178</v>
       </c>
       <c r="R93" t="n">
-        <v>6710397</v>
+        <v>6710089</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10935,7 +10944,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10945,7 +10954,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10972,54 +10981,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132059885</v>
+        <v>132059837</v>
       </c>
       <c r="B94" t="n">
-        <v>99118</v>
+        <v>91872</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>557308</v>
+        <v>556964</v>
       </c>
       <c r="R94" t="n">
-        <v>6710165</v>
+        <v>6710397</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11750,32 +11750,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132059904</v>
+        <v>132059866</v>
       </c>
       <c r="B101" t="n">
-        <v>79327</v>
+        <v>92369</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11785,10 +11785,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>557202</v>
+        <v>557001</v>
       </c>
       <c r="R101" t="n">
-        <v>6710100</v>
+        <v>6710392</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11839,6 +11839,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11857,7 +11858,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132059921</v>
+        <v>132059904</v>
       </c>
       <c r="B102" t="n">
         <v>79327</v>
@@ -11892,10 +11893,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>557288</v>
+        <v>557202</v>
       </c>
       <c r="R102" t="n">
-        <v>6710334</v>
+        <v>6710100</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11927,7 +11928,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11937,7 +11938,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11964,32 +11965,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132059866</v>
+        <v>132059921</v>
       </c>
       <c r="B103" t="n">
-        <v>92369</v>
+        <v>79327</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11999,10 +12000,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>557001</v>
+        <v>557288</v>
       </c>
       <c r="R103" t="n">
-        <v>6710392</v>
+        <v>6710334</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12034,7 +12035,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12044,7 +12045,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12053,7 +12054,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -8351,10 +8351,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132059908</v>
+        <v>132059845</v>
       </c>
       <c r="B70" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8362,21 +8362,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>557176</v>
+        <v>557066</v>
       </c>
       <c r="R70" t="n">
-        <v>6710298</v>
+        <v>6710417</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8458,7 +8458,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132059909</v>
+        <v>132059908</v>
       </c>
       <c r="B71" t="n">
         <v>79327</v>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>557110</v>
+        <v>557176</v>
       </c>
       <c r="R71" t="n">
-        <v>6710241</v>
+        <v>6710298</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8565,7 +8565,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132059914</v>
+        <v>132059909</v>
       </c>
       <c r="B72" t="n">
         <v>79327</v>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556941</v>
+        <v>557110</v>
       </c>
       <c r="R72" t="n">
-        <v>6710405</v>
+        <v>6710241</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8672,7 +8672,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132059911</v>
+        <v>132059914</v>
       </c>
       <c r="B73" t="n">
         <v>79327</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>557115</v>
+        <v>556941</v>
       </c>
       <c r="R73" t="n">
-        <v>6710327</v>
+        <v>6710405</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132059845</v>
+        <v>132059911</v>
       </c>
       <c r="B74" t="n">
-        <v>91909</v>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8790,21 +8790,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>557066</v>
+        <v>557115</v>
       </c>
       <c r="R74" t="n">
-        <v>6710417</v>
+        <v>6710327</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8886,38 +8886,42 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132059934</v>
+        <v>132059884</v>
       </c>
       <c r="B75" t="n">
-        <v>5179</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8926,10 +8930,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557044</v>
+        <v>557378</v>
       </c>
       <c r="R75" t="n">
-        <v>6710462</v>
+        <v>6710276</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8961,7 +8965,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8971,7 +8975,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8998,54 +9002,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132059884</v>
+        <v>132059920</v>
       </c>
       <c r="B76" t="n">
-        <v>99118</v>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>557378</v>
+        <v>557294</v>
       </c>
       <c r="R76" t="n">
-        <v>6710276</v>
+        <v>6710338</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9077,7 +9072,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9087,7 +9082,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9114,32 +9109,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132059920</v>
+        <v>132059924</v>
       </c>
       <c r="B77" t="n">
-        <v>79327</v>
+        <v>93197</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9149,10 +9144,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557294</v>
+        <v>557139</v>
       </c>
       <c r="R77" t="n">
-        <v>6710338</v>
+        <v>6710146</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9184,7 +9179,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9194,7 +9189,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9221,10 +9216,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132059924</v>
+        <v>132059934</v>
       </c>
       <c r="B78" t="n">
-        <v>93197</v>
+        <v>5179</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9232,34 +9227,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>557139</v>
+        <v>557044</v>
       </c>
       <c r="R78" t="n">
-        <v>6710146</v>
+        <v>6710462</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9328,32 +9328,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132059918</v>
+        <v>132059881</v>
       </c>
       <c r="B79" t="n">
-        <v>79327</v>
+        <v>97983</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>557304</v>
+        <v>556939</v>
       </c>
       <c r="R79" t="n">
-        <v>6710354</v>
+        <v>6710405</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9435,7 +9435,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132059900</v>
+        <v>132059918</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>557283</v>
+        <v>557304</v>
       </c>
       <c r="R80" t="n">
-        <v>6710151</v>
+        <v>6710354</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9542,32 +9542,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132059881</v>
+        <v>132059900</v>
       </c>
       <c r="B81" t="n">
-        <v>97983</v>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556939</v>
+        <v>557283</v>
       </c>
       <c r="R81" t="n">
-        <v>6710405</v>
+        <v>6710151</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9649,10 +9649,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132059912</v>
+        <v>132059937</v>
       </c>
       <c r="B82" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9660,34 +9660,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>557108</v>
+        <v>557086</v>
       </c>
       <c r="R82" t="n">
-        <v>6710330</v>
+        <v>6710307</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9719,7 +9724,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9729,14 +9734,14 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG82" t="b">
         <v>0</v>
@@ -9756,50 +9761,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132059858</v>
+        <v>132059912</v>
       </c>
       <c r="B83" t="n">
-        <v>4775</v>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>557066</v>
+        <v>557108</v>
       </c>
       <c r="R83" t="n">
-        <v>6710417</v>
+        <v>6710330</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9868,38 +9868,38 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132059937</v>
+        <v>132059858</v>
       </c>
       <c r="B84" t="n">
-        <v>57953</v>
+        <v>4775</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9908,10 +9908,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>557086</v>
+        <v>557066</v>
       </c>
       <c r="R84" t="n">
-        <v>6710307</v>
+        <v>6710417</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9953,14 +9953,14 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="b">
         <v>0</v>
@@ -10651,45 +10651,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132059916</v>
+        <v>132059885</v>
       </c>
       <c r="B91" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>557268</v>
+        <v>557308</v>
       </c>
       <c r="R91" t="n">
-        <v>6710406</v>
+        <v>6710165</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10721,7 +10730,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10731,7 +10740,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10758,54 +10767,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132059885</v>
+        <v>132059837</v>
       </c>
       <c r="B92" t="n">
-        <v>99118</v>
+        <v>91872</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>557308</v>
+        <v>556964</v>
       </c>
       <c r="R92" t="n">
-        <v>6710165</v>
+        <v>6710397</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10847,7 +10847,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10981,32 +10981,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132059837</v>
+        <v>132059916</v>
       </c>
       <c r="B94" t="n">
-        <v>91872</v>
+        <v>79327</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11016,10 +11016,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>556964</v>
+        <v>557268</v>
       </c>
       <c r="R94" t="n">
-        <v>6710397</v>
+        <v>6710406</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11312,10 +11312,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132059901</v>
+        <v>132059842</v>
       </c>
       <c r="B97" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11323,21 +11323,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11347,10 +11347,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>557218</v>
+        <v>557050</v>
       </c>
       <c r="R97" t="n">
-        <v>6710093</v>
+        <v>6710330</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11419,32 +11419,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132059842</v>
+        <v>132059865</v>
       </c>
       <c r="B98" t="n">
-        <v>91909</v>
+        <v>92369</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11454,10 +11454,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>557050</v>
+        <v>557190</v>
       </c>
       <c r="R98" t="n">
-        <v>6710330</v>
+        <v>6710236</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11508,6 +11508,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11526,10 +11527,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132059865</v>
+        <v>132059886</v>
       </c>
       <c r="B99" t="n">
-        <v>92369</v>
+        <v>99118</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11537,34 +11538,43 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>557190</v>
+        <v>557312</v>
       </c>
       <c r="R99" t="n">
-        <v>6710236</v>
+        <v>6710224</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11596,7 +11606,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11606,7 +11616,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11615,7 +11625,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11634,54 +11643,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132059886</v>
+        <v>132059901</v>
       </c>
       <c r="B100" t="n">
-        <v>99118</v>
+        <v>79327</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>557312</v>
+        <v>557218</v>
       </c>
       <c r="R100" t="n">
-        <v>6710224</v>
+        <v>6710093</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12179,45 +12179,50 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132059899</v>
+        <v>132059935</v>
       </c>
       <c r="B105" t="n">
-        <v>79327</v>
+        <v>5179</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>557291</v>
+        <v>557267</v>
       </c>
       <c r="R105" t="n">
-        <v>6710161</v>
+        <v>6710406</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12249,7 +12254,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12259,7 +12264,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12286,45 +12291,50 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132059919</v>
+        <v>132059929</v>
       </c>
       <c r="B106" t="n">
-        <v>79327</v>
+        <v>5179</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>557299</v>
+        <v>557206</v>
       </c>
       <c r="R106" t="n">
-        <v>6710339</v>
+        <v>6710235</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12356,7 +12366,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12366,7 +12376,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12393,50 +12403,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132059935</v>
+        <v>132059899</v>
       </c>
       <c r="B107" t="n">
-        <v>5179</v>
+        <v>79327</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>557267</v>
+        <v>557291</v>
       </c>
       <c r="R107" t="n">
-        <v>6710406</v>
+        <v>6710161</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12468,7 +12473,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12478,7 +12483,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12505,50 +12510,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132059929</v>
+        <v>132059919</v>
       </c>
       <c r="B108" t="n">
-        <v>5179</v>
+        <v>79327</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>557206</v>
+        <v>557299</v>
       </c>
       <c r="R108" t="n">
-        <v>6710235</v>
+        <v>6710339</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12580,7 +12580,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12590,7 +12590,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -8886,54 +8886,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132059884</v>
+        <v>132059920</v>
       </c>
       <c r="B75" t="n">
-        <v>99118</v>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557378</v>
+        <v>557294</v>
       </c>
       <c r="R75" t="n">
-        <v>6710276</v>
+        <v>6710338</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8965,7 +8956,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8975,7 +8966,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9002,32 +8993,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132059920</v>
+        <v>132059924</v>
       </c>
       <c r="B76" t="n">
-        <v>79327</v>
+        <v>93197</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9037,10 +9028,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>557294</v>
+        <v>557139</v>
       </c>
       <c r="R76" t="n">
-        <v>6710338</v>
+        <v>6710146</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9072,7 +9063,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9082,7 +9073,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9109,10 +9100,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132059924</v>
+        <v>132059934</v>
       </c>
       <c r="B77" t="n">
-        <v>93197</v>
+        <v>5179</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9120,34 +9111,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557139</v>
+        <v>557044</v>
       </c>
       <c r="R77" t="n">
-        <v>6710146</v>
+        <v>6710462</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9179,7 +9175,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9189,7 +9185,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9216,38 +9212,42 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132059934</v>
+        <v>132059884</v>
       </c>
       <c r="B78" t="n">
-        <v>5179</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>557044</v>
+        <v>557378</v>
       </c>
       <c r="R78" t="n">
-        <v>6710462</v>
+        <v>6710276</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9328,32 +9328,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132059881</v>
+        <v>132059918</v>
       </c>
       <c r="B79" t="n">
-        <v>97983</v>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>556939</v>
+        <v>557304</v>
       </c>
       <c r="R79" t="n">
-        <v>6710405</v>
+        <v>6710354</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9435,7 +9435,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132059918</v>
+        <v>132059900</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>557304</v>
+        <v>557283</v>
       </c>
       <c r="R80" t="n">
-        <v>6710354</v>
+        <v>6710151</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9542,32 +9542,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132059900</v>
+        <v>132059881</v>
       </c>
       <c r="B81" t="n">
-        <v>79327</v>
+        <v>97983</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>557283</v>
+        <v>556939</v>
       </c>
       <c r="R81" t="n">
-        <v>6710151</v>
+        <v>6710405</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10101,10 +10101,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132059841</v>
+        <v>132059862</v>
       </c>
       <c r="B86" t="n">
-        <v>91909</v>
+        <v>57950</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10112,34 +10112,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>557246</v>
+        <v>557268</v>
       </c>
       <c r="R86" t="n">
-        <v>6710104</v>
+        <v>6710406</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10171,7 +10176,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10181,7 +10186,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10208,10 +10213,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132059862</v>
+        <v>132059841</v>
       </c>
       <c r="B87" t="n">
-        <v>57950</v>
+        <v>91909</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10219,39 +10224,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>557268</v>
+        <v>557246</v>
       </c>
       <c r="R87" t="n">
-        <v>6710406</v>
+        <v>6710104</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10651,54 +10651,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132059885</v>
+        <v>132059837</v>
       </c>
       <c r="B91" t="n">
-        <v>99118</v>
+        <v>91872</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>557308</v>
+        <v>556964</v>
       </c>
       <c r="R91" t="n">
-        <v>6710165</v>
+        <v>6710397</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10730,7 +10721,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10740,7 +10731,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10767,32 +10758,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132059837</v>
+        <v>132059902</v>
       </c>
       <c r="B92" t="n">
-        <v>91872</v>
+        <v>79327</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10802,10 +10793,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>556964</v>
+        <v>557178</v>
       </c>
       <c r="R92" t="n">
-        <v>6710397</v>
+        <v>6710089</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10837,7 +10828,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10847,7 +10838,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10874,7 +10865,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132059902</v>
+        <v>132059916</v>
       </c>
       <c r="B93" t="n">
         <v>79327</v>
@@ -10909,10 +10900,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>557178</v>
+        <v>557268</v>
       </c>
       <c r="R93" t="n">
-        <v>6710089</v>
+        <v>6710406</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10944,7 +10935,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10954,7 +10945,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10981,45 +10972,54 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132059916</v>
+        <v>132059885</v>
       </c>
       <c r="B94" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>557268</v>
+        <v>557308</v>
       </c>
       <c r="R94" t="n">
-        <v>6710406</v>
+        <v>6710165</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12403,45 +12403,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132059899</v>
+        <v>132059888</v>
       </c>
       <c r="B107" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>557291</v>
+        <v>557286</v>
       </c>
       <c r="R107" t="n">
-        <v>6710161</v>
+        <v>6710159</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12510,7 +12519,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132059919</v>
+        <v>132059899</v>
       </c>
       <c r="B108" t="n">
         <v>79327</v>
@@ -12545,10 +12554,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>557299</v>
+        <v>557291</v>
       </c>
       <c r="R108" t="n">
-        <v>6710339</v>
+        <v>6710161</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12580,7 +12589,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12590,7 +12599,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12617,54 +12626,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132059888</v>
+        <v>132059919</v>
       </c>
       <c r="B109" t="n">
-        <v>99118</v>
+        <v>79327</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>557286</v>
+        <v>557299</v>
       </c>
       <c r="R109" t="n">
-        <v>6710159</v>
+        <v>6710339</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12733,45 +12733,64 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132059906</v>
+        <v>132059854</v>
       </c>
       <c r="B110" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>557164</v>
+        <v>557049</v>
       </c>
       <c r="R110" t="n">
-        <v>6710175</v>
+        <v>6710317</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12803,7 +12822,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12813,7 +12832,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12840,64 +12859,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132059854</v>
+        <v>132059906</v>
       </c>
       <c r="B111" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>557049</v>
+        <v>557164</v>
       </c>
       <c r="R111" t="n">
-        <v>6710317</v>
+        <v>6710175</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD111" t="b">

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -7819,7 +7819,7 @@
         <v>132059903</v>
       </c>
       <c r="B65" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>132059915</v>
       </c>
       <c r="B66" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>132059913</v>
       </c>
       <c r="B67" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>132059917</v>
       </c>
       <c r="B68" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>132059846</v>
       </c>
       <c r="B69" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>132059845</v>
       </c>
       <c r="B70" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>132059908</v>
       </c>
       <c r="B71" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>132059909</v>
       </c>
       <c r="B72" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>132059914</v>
       </c>
       <c r="B73" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>132059911</v>
       </c>
       <c r="B74" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8886,32 +8886,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132059920</v>
+        <v>132059924</v>
       </c>
       <c r="B75" t="n">
-        <v>79327</v>
+        <v>93198</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557294</v>
+        <v>557139</v>
       </c>
       <c r="R75" t="n">
-        <v>6710338</v>
+        <v>6710146</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8993,32 +8993,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132059924</v>
+        <v>132059920</v>
       </c>
       <c r="B76" t="n">
-        <v>93197</v>
+        <v>79328</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>557139</v>
+        <v>557294</v>
       </c>
       <c r="R76" t="n">
-        <v>6710146</v>
+        <v>6710338</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9100,38 +9100,42 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132059934</v>
+        <v>132059884</v>
       </c>
       <c r="B77" t="n">
-        <v>5179</v>
+        <v>99119</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9140,10 +9144,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557044</v>
+        <v>557378</v>
       </c>
       <c r="R77" t="n">
-        <v>6710462</v>
+        <v>6710276</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9175,7 +9179,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9185,7 +9189,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9212,42 +9216,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132059884</v>
+        <v>132059934</v>
       </c>
       <c r="B78" t="n">
-        <v>99118</v>
+        <v>5179</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>557378</v>
+        <v>557044</v>
       </c>
       <c r="R78" t="n">
-        <v>6710276</v>
+        <v>6710462</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9328,32 +9328,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132059918</v>
+        <v>132059881</v>
       </c>
       <c r="B79" t="n">
-        <v>79327</v>
+        <v>97984</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>557304</v>
+        <v>556939</v>
       </c>
       <c r="R79" t="n">
-        <v>6710354</v>
+        <v>6710405</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9435,10 +9435,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132059900</v>
+        <v>132059918</v>
       </c>
       <c r="B80" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>557283</v>
+        <v>557304</v>
       </c>
       <c r="R80" t="n">
-        <v>6710151</v>
+        <v>6710354</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9542,32 +9542,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132059881</v>
+        <v>132059900</v>
       </c>
       <c r="B81" t="n">
-        <v>97983</v>
+        <v>79328</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556939</v>
+        <v>557283</v>
       </c>
       <c r="R81" t="n">
-        <v>6710405</v>
+        <v>6710151</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9652,7 +9652,7 @@
         <v>132059937</v>
       </c>
       <c r="B82" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>132059912</v>
       </c>
       <c r="B83" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>132059887</v>
       </c>
       <c r="B85" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10101,10 +10101,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132059862</v>
+        <v>132059841</v>
       </c>
       <c r="B86" t="n">
-        <v>57950</v>
+        <v>91910</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10112,39 +10112,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>557268</v>
+        <v>557246</v>
       </c>
       <c r="R86" t="n">
-        <v>6710406</v>
+        <v>6710104</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10176,7 +10171,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10186,7 +10181,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10213,10 +10208,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132059841</v>
+        <v>132059862</v>
       </c>
       <c r="B87" t="n">
-        <v>91909</v>
+        <v>57951</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10224,34 +10219,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>557246</v>
+        <v>557268</v>
       </c>
       <c r="R87" t="n">
-        <v>6710104</v>
+        <v>6710406</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10323,7 +10323,7 @@
         <v>132059907</v>
       </c>
       <c r="B88" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10427,38 +10427,38 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132059931</v>
+        <v>132059922</v>
       </c>
       <c r="B89" t="n">
-        <v>5179</v>
+        <v>57954</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10467,10 +10467,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>557086</v>
+        <v>556923</v>
       </c>
       <c r="R89" t="n">
-        <v>6710307</v>
+        <v>6710425</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10512,14 +10512,14 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
@@ -10539,38 +10539,38 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132059922</v>
+        <v>132059931</v>
       </c>
       <c r="B90" t="n">
-        <v>57953</v>
+        <v>5179</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10579,10 +10579,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>556923</v>
+        <v>557086</v>
       </c>
       <c r="R90" t="n">
-        <v>6710425</v>
+        <v>6710307</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10624,14 +10624,14 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="b">
         <v>0</v>
@@ -10651,45 +10651,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132059837</v>
+        <v>132059885</v>
       </c>
       <c r="B91" t="n">
-        <v>91872</v>
+        <v>99119</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>556964</v>
+        <v>557308</v>
       </c>
       <c r="R91" t="n">
-        <v>6710397</v>
+        <v>6710165</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10721,7 +10730,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10731,7 +10740,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10761,7 +10770,7 @@
         <v>132059902</v>
       </c>
       <c r="B92" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10868,7 +10877,7 @@
         <v>132059916</v>
       </c>
       <c r="B93" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10972,54 +10981,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132059885</v>
+        <v>132059837</v>
       </c>
       <c r="B94" t="n">
-        <v>99118</v>
+        <v>91873</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>557308</v>
+        <v>556964</v>
       </c>
       <c r="R94" t="n">
-        <v>6710165</v>
+        <v>6710397</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11315,7 +11315,7 @@
         <v>132059842</v>
       </c>
       <c r="B97" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>132059865</v>
       </c>
       <c r="B98" t="n">
-        <v>92369</v>
+        <v>92370</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11527,54 +11527,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132059886</v>
+        <v>132059901</v>
       </c>
       <c r="B99" t="n">
-        <v>99118</v>
+        <v>79328</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>557312</v>
+        <v>557218</v>
       </c>
       <c r="R99" t="n">
-        <v>6710224</v>
+        <v>6710093</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11606,7 +11597,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11616,7 +11607,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11643,45 +11634,54 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132059901</v>
+        <v>132059886</v>
       </c>
       <c r="B100" t="n">
-        <v>79327</v>
+        <v>99119</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Högåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>557218</v>
+        <v>557312</v>
       </c>
       <c r="R100" t="n">
-        <v>6710093</v>
+        <v>6710224</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11753,7 +11753,7 @@
         <v>132059866</v>
       </c>
       <c r="B101" t="n">
-        <v>92369</v>
+        <v>92370</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>132059904</v>
       </c>
       <c r="B102" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>132059921</v>
       </c>
       <c r="B103" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>132059840</v>
       </c>
       <c r="B104" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>132059888</v>
       </c>
       <c r="B107" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>132059899</v>
       </c>
       <c r="B108" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>132059919</v>
       </c>
       <c r="B109" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>132059854</v>
       </c>
       <c r="B110" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>132059906</v>
       </c>
       <c r="B111" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>132059843</v>
       </c>
       <c r="B112" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 60987-2025 artfynd.xlsx
+++ b/artfynd/A 60987-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY115"/>
+  <dimension ref="A1:AZ115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059870</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671345</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840121</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840123</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840125</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1386,6 +1416,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840126</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1511,6 +1546,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840132</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1618,6 +1658,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671329</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1725,6 +1770,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671330</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671331</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1939,6 +1994,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671332</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2046,6 +2106,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059840</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2153,6 +2218,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059841</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2260,6 +2330,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059842</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2367,6 +2442,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059843</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2474,6 +2554,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059845</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2581,6 +2666,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059846</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2706,6 +2796,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840113</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2813,6 +2908,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671344</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2921,6 +3021,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059865</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3029,6 +3134,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059866</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3136,6 +3246,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671328</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3243,6 +3358,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059857</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3350,6 +3470,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059924</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3475,6 +3600,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840131</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3582,6 +3712,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671335</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3689,6 +3824,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671327</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3796,6 +3936,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059837</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3921,6 +4066,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840114</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4028,6 +4178,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671355</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4135,6 +4290,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671356</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4242,6 +4402,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671357</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4349,6 +4514,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671358</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4456,6 +4626,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671359</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4563,6 +4738,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671360</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4670,6 +4850,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671361</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4777,6 +4962,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671362</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4884,6 +5074,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671363</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4991,6 +5186,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671365</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5098,6 +5298,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059899</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5205,6 +5410,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059900</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5312,6 +5522,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059901</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5419,6 +5634,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059902</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5526,6 +5746,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059903</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5633,6 +5858,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059904</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5740,6 +5970,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059906</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5847,6 +6082,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059907</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5954,6 +6194,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059908</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6061,6 +6306,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059909</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6168,6 +6418,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059910</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6275,6 +6530,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059911</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6382,6 +6642,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059912</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6489,6 +6754,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059913</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6596,6 +6866,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059914</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6703,6 +6978,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059915</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6810,6 +7090,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059916</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6917,6 +7202,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059917</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7024,6 +7314,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059918</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7131,6 +7426,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059919</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7238,6 +7538,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059920</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7345,6 +7650,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059921</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7470,6 +7780,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840116</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7582,6 +7897,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671336</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7694,6 +8014,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671337</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7806,6 +8131,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671338</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7918,6 +8248,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671339</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8030,6 +8365,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671340</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8142,6 +8482,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671341</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8254,6 +8599,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671342</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8366,6 +8716,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671343</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8478,6 +8833,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059862</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8598,6 +8958,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840118</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8723,6 +9088,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840127</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8848,6 +9218,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840128</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8973,6 +9348,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840130</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9090,6 +9470,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059878</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9202,6 +9587,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059922</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9314,6 +9704,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059937</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9440,6 +9835,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059854</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9552,6 +9952,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059858</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9664,6 +10069,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671367</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9776,6 +10186,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671368</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9888,6 +10303,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671370</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10000,6 +10420,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671371</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10112,6 +10537,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671372</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10224,6 +10654,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671373</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10336,6 +10771,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059928</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10448,6 +10888,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059929</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10560,6 +11005,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059930</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10672,6 +11122,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059931</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10784,6 +11239,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059932</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10896,6 +11356,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059934</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11008,6 +11473,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059935</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11120,6 +11590,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059936</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11232,6 +11707,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671334</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11343,6 +11823,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059853</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11455,6 +11940,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671324</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11567,6 +12057,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671325</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11679,6 +12174,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671326</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11782,6 +12282,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131134868</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11885,6 +12390,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131134870</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11988,6 +12498,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131134867</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12113,6 +12628,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840115</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12238,6 +12758,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840117</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12363,6 +12888,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840119</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12488,6 +13018,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840120</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12618,6 +13153,11 @@
           <t>Vindpark Högåsberget</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129840129</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12734,6 +13274,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059884</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12850,6 +13395,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059885</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12966,6 +13516,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059886</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13087,6 +13642,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059887</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13203,6 +13763,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059888</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13310,6 +13875,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059881</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13413,8 +13983,129 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059859</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>